--- a/docs/downloads/2026-10-08/bursa-report-2026-10-08.xlsx
+++ b/docs/downloads/2026-10-08/bursa-report-2026-10-08.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-08" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-08'!$A$1:$M$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-08'!$A$1:$M$53</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -35,10 +35,10 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <color rgb="000CA30C"/>
+      <color rgb="00D03B3B"/>
     </font>
     <font>
-      <color rgb="00D03B3B"/>
+      <color rgb="000CA30C"/>
     </font>
     <font>
       <color rgb="00898781"/>
@@ -69,7 +69,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -82,6 +82,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -449,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -542,39 +543,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.395</v>
+        <v>0.075</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.0533</v>
+        <v>-0.0625</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>47838900</v>
+        <v>40654900</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>1.15</v>
+        <v>0.09</v>
       </c>
       <c r="H2" t="n">
-        <v>72.45999999999999</v>
+        <v>20.64</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.351</v>
+        <v>0.182</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.228</v>
+        <v>0.401</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" s="7" t="inlineStr"/>
@@ -587,39 +588,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>0.0625</v>
+        <v>0.885</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>0.0351</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>13302800</v>
+        <v>34515200</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.03</v>
+        <v>0.48</v>
       </c>
       <c r="H3" t="n">
-        <v>22.46</v>
-      </c>
-      <c r="I3" s="8" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.42</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.183</v>
+        <v>0.776</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.401</v>
+        <v>0.707</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" s="7" t="inlineStr"/>
@@ -632,39 +633,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <v>0</v>
+        <v>0.455</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>0.0225</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>1874000</v>
+        <v>7215700</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.28</v>
       </c>
       <c r="H4" t="n">
-        <v>63.03</v>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
+        <v>66.17</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.576</v>
+        <v>0.408</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.503</v>
+        <v>0.345</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
@@ -677,39 +678,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>0.0175</v>
+        <v>0.465</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>0.0449</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1694700</v>
+        <v>6425000</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.02</v>
+        <v>0.99</v>
       </c>
       <c r="H5" t="n">
-        <v>69.97</v>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
+        <v>63.59</v>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.775</v>
+        <v>0.423</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.706</v>
+        <v>0.412</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -722,39 +723,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0.0337</v>
+        <v>1.93</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>0.03759999999999999</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1587000</v>
+        <v>6269800</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="H6" t="n">
-        <v>62.6</v>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
+        <v>67.09</v>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.423</v>
+        <v>1.789</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.412</v>
+        <v>1.633</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -767,45 +768,2101 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>0</v>
+        <v>0.4</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>0.0127</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>985300</v>
+        <v>6173300</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.04</v>
+        <v>0.15</v>
       </c>
       <c r="H7" t="n">
-        <v>61.53</v>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
+        <v>73.34999999999999</v>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.486</v>
+        <v>0.356</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.479</v>
+        <v>0.234</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>4456</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DNEX</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>-0.0098</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>5788100</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H8" t="n">
+        <v>59.22</v>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>0.486</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>5168</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>HARTA</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>5465400</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H9" t="n">
+        <v>54.66</v>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>1.075</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>7192</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>GIIB</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>5253900</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H10" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0476</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SLGC Berhad</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>0.0196</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>4986700</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="2" t="n"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0193</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>KINERGY</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>4929300</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H12" t="n">
+        <v>38.38</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>5099</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CAPITALA</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>0.0222</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>3710700</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H13" t="n">
+        <v>34.28</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>7153</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>KOSSAN</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>0.0435</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>3649000</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H14" t="n">
+        <v>54.81</v>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>6963</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>-0.0154</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>3421700</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H15" t="n">
+        <v>72.59</v>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0.242</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0473</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EVOCOM</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>3169500</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>5398</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>GAMUDA</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-0.0177</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>2367400</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H17" t="n">
+        <v>58.23</v>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>4.912</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>4.645</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5309</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ITMAX</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>-0.0128</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>2216400</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H18" t="n">
+        <v>58.34</v>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>4.538</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>4.489</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0457</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PENTECH</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>-0.0145</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>2063300</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H19" t="n">
+        <v>51.84</v>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CIMB</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>-0.0177</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>2047200</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H20" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>7.675</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>7.741</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>4677</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>YTL</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>-0.0186</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>2028400</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H21" t="n">
+        <v>38.62</v>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>2.233</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>2.227</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0120</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>VIS</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>1711300</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H22" t="n">
+        <v>88.56999999999999</v>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>MAYBANK</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>1693100</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H23" t="n">
+        <v>32.13</v>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>10.048</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>5151</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>HEXTAR</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>1586500</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H24" t="n">
+        <v>53.15</v>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0340</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NORTHERN</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>0.0431</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>1497600</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H25" t="n">
+        <v>66.23999999999999</v>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>1.066</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>UUE</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>-0.0242</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>1450800</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H26" t="n">
+        <v>68.16</v>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0455</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>BUSCAP</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>-0.0123</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>1307000</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H27" t="n">
+        <v>78.83</v>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0166</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>INARI</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>-0.0072</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>1269400</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H28" t="n">
+        <v>63.09</v>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>2.612</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>2.501</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0275</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>OPPSTAR</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>-0.0071</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>1208200</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H29" t="n">
+        <v>53.39</v>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>7225</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>1187800</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H30" t="n">
+        <v>47.06</v>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>7204</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>D&amp;O</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>1178500</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H31" t="n">
+        <v>57.53</v>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>0.436</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>4715</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>GENM</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>1141200</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H32" t="n">
+        <v>28.24</v>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>1.509</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>1.623</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0368</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>OXB</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>0.0196</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>1081700</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H33" t="n">
+        <v>67.25</v>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>0.449</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>7943</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>GREENTEC</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>0.06059999999999999</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>1078400</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="H34" t="n">
+        <v>94.88</v>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>0.242</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>0.204</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>5161</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>JCY</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>1068600</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H35" t="n">
+        <v>65.56999999999999</v>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>1055900</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H36" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>5238</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AAGB</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>0.0105</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>1023700</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H37" t="n">
+        <v>27.89</v>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>6742</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>YTLPOWR</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>-0.0142</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>959200</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H38" t="n">
+        <v>47.65</v>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>5.645</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>5.332</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0259</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SNS</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>896500</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H39" t="n">
+        <v>51.83</v>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1295</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>PBBANK</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>-0.008699999999999999</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>881500</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H40" t="n">
+        <v>25.72</v>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>4.737</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>4.896</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" s="7" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>8907</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>-0.0114</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>858000</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H41" t="n">
+        <v>47.19</v>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>1.751</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>1.781</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" s="7" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0248</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>YEWLEE</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>843000</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H42" t="n">
+        <v>55.75</v>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0236</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>RAMSSOL</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>819700</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H43" t="n">
+        <v>51.62</v>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0339</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CBHB</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>-0.0089</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>732700</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H44" t="n">
+        <v>64.39</v>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>1.065</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" s="7" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0083</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>NOTION</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>-0.0069</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>730600</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H45" t="n">
+        <v>64.58</v>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>0.668</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" s="7" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0453</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>EIPOWER</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>727600</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H46" t="n">
+        <v>58.55</v>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" s="7" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>7134</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>PWF</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>719100</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>34.19</v>
+      </c>
+      <c r="H47" t="n">
+        <v>56.96</v>
+      </c>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" s="7" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>5327</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>MEGAFB</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>708900</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H48" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>2.608</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>2.272</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" s="7" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>RHBBANK</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>695400</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H49" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>7.648</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" s="7" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>GENTING</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="E50" s="8" t="n">
+        <v>0.0167</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>662600</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H50" t="n">
+        <v>35.19</v>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>1.899</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>2.028</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" s="7" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0196</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>QES</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>635600</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H51" t="n">
+        <v>64.17</v>
+      </c>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>0.581</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" s="7" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0318</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ELRIDGE</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>-0.0054</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>603100</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H52" t="n">
+        <v>61.53</v>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" s="7" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0391</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>AMBEST</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>-0.0149</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>518600</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H53" t="n">
+        <v>48.86</v>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>1.232</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M7"/>
+  <autoFilter ref="A1:M53"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-08/bursa-report-2026-10-08.xlsx
+++ b/docs/downloads/2026-10-08/bursa-report-2026-10-08.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-08" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-08'!$A$1:$M$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-08'!$A$1:$M$73</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -35,13 +35,13 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
+      <color rgb="00898781"/>
+    </font>
+    <font>
       <color rgb="00D03B3B"/>
     </font>
     <font>
       <color rgb="000CA30C"/>
-    </font>
-    <font>
-      <color rgb="00898781"/>
     </font>
   </fonts>
   <fills count="3">
@@ -78,13 +78,13 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -552,19 +552,19 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.075</v>
+        <v>0.08</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-0.0625</v>
+        <v>0</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>40654900</v>
+        <v>42630100</v>
       </c>
       <c r="G2" s="5" t="n">
         <v>0.09</v>
       </c>
       <c r="H2" t="n">
-        <v>20.64</v>
+        <v>21.03</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.182</v>
+        <v>0.183</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0.401</v>
@@ -597,19 +597,19 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.885</v>
+        <v>0.88</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>0.0351</v>
+        <v>0.0292</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>34515200</v>
+        <v>36423100</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="H3" t="n">
-        <v>71.42</v>
+        <v>70.95</v>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
@@ -633,28 +633,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.455</v>
+        <v>1.95</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>0.0225</v>
+        <v>0.0484</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>7215700</v>
+        <v>15711000</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.28</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>66.17</v>
+        <v>68.23</v>
       </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
@@ -662,10 +662,10 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.408</v>
+        <v>1.791</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.345</v>
+        <v>1.633</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
@@ -678,28 +678,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>0.0449</v>
+        <v>0.39</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>-0.0127</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>6425000</v>
+        <v>11507000</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.99</v>
+        <v>0.27</v>
       </c>
       <c r="H5" t="n">
-        <v>63.59</v>
+        <v>70.12</v>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.423</v>
+        <v>0.355</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.412</v>
+        <v>0.234</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -723,28 +723,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1.93</v>
+        <v>0.33</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>0.03759999999999999</v>
+        <v>0.0154</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>6269800</v>
+        <v>8947000</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.27</v>
+        <v>0.17</v>
       </c>
       <c r="H6" t="n">
-        <v>67.09</v>
+        <v>76.23</v>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
@@ -752,10 +752,10 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.789</v>
+        <v>0.272</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>1.633</v>
+        <v>0.242</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -768,28 +768,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.4</v>
+        <v>0.595</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>0.0127</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>6173300</v>
+        <v>8003000</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.15</v>
+        <v>0.31</v>
       </c>
       <c r="H7" t="n">
-        <v>73.34999999999999</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
@@ -797,10 +797,10 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.356</v>
+        <v>0.576</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.234</v>
+        <v>0.503</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -813,28 +813,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>-0.0098</v>
+        <v>0.455</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>0.0225</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>5788100</v>
+        <v>7899100</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.22</v>
+        <v>0.31</v>
       </c>
       <c r="H8" t="n">
-        <v>59.22</v>
+        <v>66.17</v>
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.486</v>
+        <v>0.408</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.479</v>
+        <v>0.345</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -858,28 +858,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1.1</v>
+        <v>0.465</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>0.028</v>
+        <v>0.0449</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5465400</v>
+        <v>6999700</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.39</v>
+        <v>1.08</v>
       </c>
       <c r="H9" t="n">
-        <v>54.66</v>
+        <v>63.59</v>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.075</v>
+        <v>0.423</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>1.036</v>
+        <v>0.412</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
@@ -903,28 +903,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.51</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>5253900</v>
+        <v>5939400</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="H10" t="n">
-        <v>64.59999999999999</v>
+        <v>61.53</v>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.576</v>
+        <v>0.486</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.503</v>
+        <v>0.479</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
@@ -948,33 +948,40 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SLGC Berhad</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.26</v>
+        <v>1.09</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>0.0196</v>
+        <v>0.0187</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>4986700</v>
+        <v>5765200</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.08</v>
+        <v>0.41</v>
+      </c>
+      <c r="H11" t="n">
+        <v>53.37</v>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J11" s="2" t="n"/>
-      <c r="K11" s="2" t="n"/>
+      <c r="J11" s="2" t="n">
+        <v>1.074</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>1.035</v>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
     </row>
@@ -986,40 +993,33 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>SLGC Berhad</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E12" s="10" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="E12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>4929300</v>
+        <v>5253000</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="H12" t="n">
-        <v>38.38</v>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>0.403</v>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>0.41</v>
-      </c>
+        <v>0.09</v>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
     </row>
@@ -1031,28 +1031,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>0.0222</v>
+        <v>0.395</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>3710700</v>
+        <v>4939300</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.14</v>
+        <v>0.44</v>
       </c>
       <c r="H13" t="n">
-        <v>34.28</v>
+        <v>38.38</v>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.252</v>
+        <v>0.403</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.305</v>
+        <v>0.41</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
@@ -1091,10 +1091,10 @@
         <v>0.0435</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3649000</v>
+        <v>3784900</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="H14" t="n">
         <v>54.81</v>
@@ -1121,39 +1121,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>-0.0154</v>
+        <v>0.23</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>0.0222</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>3421700</v>
+        <v>3725300</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.06</v>
+        <v>0.14</v>
       </c>
       <c r="H15" t="n">
-        <v>72.59</v>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.28</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.271</v>
+        <v>0.252</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.242</v>
+        <v>0.305</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
@@ -1166,33 +1166,40 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0473</t>
+          <t>0131</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>EVOCOM</t>
+          <t>DFX</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.105</v>
+        <v>0.14</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>0</v>
+        <v>-0.0345</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>3169500</v>
+        <v>3403900</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="n"/>
+        <v>0.45</v>
+      </c>
+      <c r="H16" t="n">
+        <v>70.08</v>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>0.093</v>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
     </row>
@@ -1204,40 +1211,33 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>EVOCOM</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>4.99</v>
+        <v>0.105</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0.0177</v>
+        <v>0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2367400</v>
+        <v>3339900</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="H17" t="n">
-        <v>58.23</v>
-      </c>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="n">
-        <v>4.912</v>
-      </c>
-      <c r="K17" s="2" t="n">
-        <v>4.645</v>
-      </c>
+        <v>0.19</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
     </row>
@@ -1249,28 +1249,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ITMAX</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>-0.0128</v>
+        <v>4.99</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>-0.0177</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2216400</v>
+        <v>3150600</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>1.04</v>
+        <v>0.12</v>
       </c>
       <c r="H18" t="n">
-        <v>58.34</v>
+        <v>58.23</v>
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
@@ -1278,10 +1278,10 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>4.538</v>
+        <v>4.912</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>4.489</v>
+        <v>4.645</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1294,39 +1294,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>-0.0145</v>
+        <v>2.13</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2063300</v>
+        <v>2956400</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="H19" t="n">
-        <v>51.84</v>
-      </c>
-      <c r="I19" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.95</v>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.342</v>
+        <v>2.235</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.324</v>
+        <v>2.227</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1348,19 +1348,19 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>-0.0177</v>
+        <v>7.19</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>-0.0191</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2047200</v>
+        <v>2800700</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="H20" t="n">
-        <v>29.8</v>
+        <v>29.57</v>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>7.675</v>
+        <v>7.674</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>7.741</v>
@@ -1384,39 +1384,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>-0.0186</v>
+        <v>2.77</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>-0.0036</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2028400</v>
+        <v>2799000</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="H21" t="n">
-        <v>38.62</v>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64</v>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>2.233</v>
+        <v>2.613</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>2.227</v>
+        <v>2.501</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1429,28 +1429,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>0.0152</v>
+        <v>0.34</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>-0.0145</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1711300</v>
+        <v>2398800</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.41</v>
+        <v>0.3</v>
       </c>
       <c r="H22" t="n">
-        <v>88.56999999999999</v>
+        <v>51.84</v>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
@@ -1458,10 +1458,10 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.502</v>
+        <v>0.342</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.438</v>
+        <v>0.324</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1474,39 +1474,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>9.85</v>
+        <v>0.78</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>-0.002</v>
+        <v>0</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1693100</v>
+        <v>2326000</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="H23" t="n">
-        <v>32.13</v>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.15</v>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>10.048</v>
+        <v>0.776</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>10.22</v>
+        <v>0.776</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1519,28 +1519,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>0</v>
+        <v>0.675</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>0.0227</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1586500</v>
+        <v>2311900</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.11</v>
+        <v>0.55</v>
       </c>
       <c r="H24" t="n">
-        <v>53.15</v>
+        <v>88.78</v>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.776</v>
+        <v>0.502</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.776</v>
+        <v>0.438</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1564,28 +1564,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>ITMAX</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="E25" s="8" t="n">
-        <v>0.0431</v>
+        <v>4.63</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>-0.0128</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1497600</v>
+        <v>2216400</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.2</v>
+        <v>1.04</v>
       </c>
       <c r="H25" t="n">
-        <v>66.23999999999999</v>
+        <v>58.34</v>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.066</v>
+        <v>4.538</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.819</v>
+        <v>4.489</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1609,39 +1609,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>-0.0242</v>
+        <v>9.83</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>-0.004099999999999999</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1450800</v>
+        <v>2129900</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.21</v>
+        <v>0.17</v>
       </c>
       <c r="H26" t="n">
-        <v>68.16</v>
-      </c>
-      <c r="I26" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.26</v>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.731</v>
+        <v>10.046</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.648</v>
+        <v>10.219</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1654,28 +1654,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.805</v>
+        <v>0.825</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.0123</v>
+        <v>0</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1307000</v>
+        <v>2081100</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.47</v>
+        <v>0.3</v>
       </c>
       <c r="H27" t="n">
-        <v>78.83</v>
+        <v>73.44</v>
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.604</v>
+        <v>0.733</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.465</v>
+        <v>0.649</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1699,39 +1699,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>TUNEPRO</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>-0.0072</v>
+        <v>0.265</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>0.0392</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1269400</v>
+        <v>1804200</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>2.14</v>
       </c>
       <c r="H28" t="n">
-        <v>63.09</v>
-      </c>
-      <c r="I28" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.23</v>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>2.612</v>
+        <v>0.25</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>2.501</v>
+        <v>0.259</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1744,28 +1744,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>-0.0071</v>
+        <v>0.525</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>0.0294</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1208200</v>
+        <v>1678800</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.15</v>
+        <v>0.43</v>
       </c>
       <c r="H29" t="n">
-        <v>53.39</v>
+        <v>68.11</v>
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.468</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.678</v>
+        <v>0.449</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1789,28 +1789,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>0</v>
+        <v>1.22</v>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>0.0517</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1187800</v>
+        <v>1561400</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="H30" t="n">
-        <v>47.06</v>
+        <v>66.73</v>
       </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
@@ -1818,10 +1818,10 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.208</v>
+        <v>1.067</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.209</v>
+        <v>0.82</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1834,39 +1834,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>7943</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>GREENTEC</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>0</v>
+        <v>0.37</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>0.1212</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1178500</v>
+        <v>1453400</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.87</v>
       </c>
       <c r="H31" t="n">
-        <v>57.53</v>
-      </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>95.51000000000001</v>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.512</v>
+        <v>0.244</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.436</v>
+        <v>0.204</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1879,39 +1879,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1.45</v>
+        <v>0.7</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>0</v>
+        <v>-0.0071</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1141200</v>
+        <v>1451800</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.53</v>
+        <v>0.19</v>
       </c>
       <c r="H32" t="n">
-        <v>28.24</v>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.39</v>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.509</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>1.623</v>
+        <v>0.678</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1924,39 +1924,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E33" s="8" t="n">
-        <v>0.0196</v>
+        <v>0.49</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1081700</v>
+        <v>1428200</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="H33" t="n">
-        <v>67.25</v>
-      </c>
-      <c r="I33" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.21</v>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.467</v>
+        <v>0.528</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.449</v>
+        <v>0.573</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1969,28 +1969,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GREENTEC</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E34" s="8" t="n">
-        <v>0.06059999999999999</v>
+        <v>0.645</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1078400</v>
+        <v>1425500</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>1.39</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H34" t="n">
-        <v>94.88</v>
+        <v>66.8</v>
       </c>
       <c r="I34" s="9" t="inlineStr">
         <is>
@@ -1998,10 +1998,10 @@
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.242</v>
+        <v>0.577</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.204</v>
+        <v>0.516</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2014,28 +2014,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.44</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>0.0115</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1068600</v>
+        <v>1380400</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.05</v>
+        <v>0.13</v>
       </c>
       <c r="H35" t="n">
-        <v>65.56999999999999</v>
+        <v>48.53</v>
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.577</v>
+        <v>0.451</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.516</v>
+        <v>0.425</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2059,39 +2059,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E36" s="10" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="E36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>1055900</v>
+        <v>1351000</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.96</v>
+        <v>0.29</v>
       </c>
       <c r="H36" t="n">
-        <v>8.08</v>
-      </c>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.06</v>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.586</v>
+        <v>0.208</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.624</v>
+        <v>0.209</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2104,39 +2104,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E37" s="8" t="n">
-        <v>0.0105</v>
+        <v>0.78</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>1023700</v>
+        <v>1344700</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.03</v>
+        <v>0.17</v>
       </c>
       <c r="H37" t="n">
-        <v>27.89</v>
-      </c>
-      <c r="I37" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.62</v>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.776</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.755</v>
+        <v>0.772</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2149,39 +2149,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>5.54</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>-0.0142</v>
+        <v>0.805</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>-0.0123</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>959200</v>
+        <v>1341000</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="H38" t="n">
-        <v>47.65</v>
-      </c>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>78.83</v>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>5.645</v>
+        <v>0.604</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>5.332</v>
+        <v>0.465</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2194,28 +2194,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="E39" s="10" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>896500</v>
+        <v>1337700</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="H39" t="n">
-        <v>51.83</v>
+        <v>57.53</v>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.52</v>
+        <v>0.512</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.53</v>
+        <v>0.436</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2239,28 +2239,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>-0.008699999999999999</v>
+        <v>5.56</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>-0.0107</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>881500</v>
+        <v>1285900</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="H40" t="n">
-        <v>25.72</v>
+        <v>48.46</v>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>4.737</v>
+        <v>5.647</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>4.896</v>
+        <v>5.332</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2284,39 +2284,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>1.74</v>
+        <v>0.295</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>-0.0114</v>
+        <v>0</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>858000</v>
+        <v>1235600</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.16</v>
+        <v>0.46</v>
       </c>
       <c r="H41" t="n">
-        <v>47.19</v>
-      </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.23</v>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.751</v>
+        <v>0.295</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>1.781</v>
+        <v>0.296</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2329,39 +2329,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E42" s="10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="E42" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>843000</v>
+        <v>1231700</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.08</v>
+        <v>0.57</v>
       </c>
       <c r="H42" t="n">
-        <v>55.75</v>
-      </c>
-      <c r="I42" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.24</v>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.61</v>
+        <v>1.509</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.611</v>
+        <v>1.623</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2374,39 +2374,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E43" s="10" t="n">
-        <v>0</v>
+        <v>0.53</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>0.0095</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>819700</v>
+        <v>1226000</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.1</v>
+        <v>0.17</v>
       </c>
       <c r="H43" t="n">
-        <v>51.62</v>
-      </c>
-      <c r="I43" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.51</v>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.776</v>
+        <v>0.52</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.772</v>
+        <v>0.53</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2419,39 +2419,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>-0.0089</v>
+        <v>0.485</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>0.0211</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>732700</v>
+        <v>1201300</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="H44" t="n">
-        <v>64.39</v>
-      </c>
-      <c r="I44" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.13</v>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.065</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.912</v>
+        <v>0.756</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2464,39 +2464,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0023</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>IFCAMSC</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>-0.0069</v>
+        <v>0.2</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>-0.0244</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>730600</v>
+        <v>1173300</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.08</v>
+        <v>2.11</v>
       </c>
       <c r="H45" t="n">
-        <v>64.58</v>
-      </c>
-      <c r="I45" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.38</v>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.668</v>
+        <v>0.204</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.604</v>
+        <v>0.214</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2509,28 +2509,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0.985</v>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>-0.015</v>
+        <v>1.75</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>727600</v>
+        <v>1154600</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.09</v>
+        <v>0.22</v>
       </c>
       <c r="H46" t="n">
-        <v>58.55</v>
+        <v>48.61</v>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
@@ -2538,10 +2538,10 @@
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.963</v>
+        <v>1.752</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.8159999999999999</v>
+        <v>1.781</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2554,28 +2554,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>7134</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PWF</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="E47" s="8" t="n">
-        <v>0.027</v>
+        <v>0.62</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>719100</v>
+        <v>1093300</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>34.19</v>
+        <v>0.1</v>
       </c>
       <c r="H47" t="n">
-        <v>56.96</v>
+        <v>55.75</v>
       </c>
       <c r="I47" s="9" t="inlineStr">
         <is>
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.742</v>
+        <v>0.61</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.744</v>
+        <v>0.611</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2599,39 +2599,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="E48" s="10" t="n">
-        <v>0</v>
+        <v>0.535</v>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>0.009399999999999999</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>708900</v>
+        <v>1086800</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.23</v>
+        <v>0.3</v>
       </c>
       <c r="H48" t="n">
-        <v>71.09999999999999</v>
-      </c>
-      <c r="I48" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.53</v>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>2.608</v>
+        <v>0.554</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>2.272</v>
+        <v>0.583</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2644,28 +2644,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>7.17</v>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>-0.011</v>
+        <v>4.54</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>-0.0109</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>695400</v>
+        <v>1063200</v>
       </c>
       <c r="G49" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="H49" t="n">
-        <v>19.36</v>
+        <v>25.2</v>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>7.648</v>
+        <v>4.736</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>8.119999999999999</v>
+        <v>4.896</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2689,28 +2689,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="E50" s="8" t="n">
-        <v>0.0167</v>
+        <v>0.5</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>662600</v>
+        <v>1055900</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.15</v>
+        <v>0.96</v>
       </c>
       <c r="H50" t="n">
-        <v>35.19</v>
+        <v>8.08</v>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.899</v>
+        <v>0.586</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>2.028</v>
+        <v>0.624</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2734,39 +2734,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E51" s="3" t="n">
-        <v>-0.007800000000000001</v>
+        <v>7.14</v>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>-0.0152</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>635600</v>
+        <v>1008700</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.17</v>
+        <v>0.11</v>
       </c>
       <c r="H51" t="n">
-        <v>64.17</v>
-      </c>
-      <c r="I51" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>18.8</v>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.592</v>
+        <v>7.645</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.581</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2779,39 +2779,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.925</v>
+        <v>0.72</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>-0.0054</v>
+        <v>0</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>603100</v>
+        <v>895600</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="H52" t="n">
-        <v>61.53</v>
-      </c>
-      <c r="I52" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.03</v>
+      </c>
+      <c r="I52" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.906</v>
+        <v>0.669</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.862</v>
+        <v>0.604</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2824,45 +2824,945 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>-0.0149</v>
+        <v>0.64</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>518600</v>
+        <v>890300</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="H53" t="n">
-        <v>48.86</v>
-      </c>
-      <c r="I53" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.17</v>
+      </c>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.35</v>
+        <v>0.592</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>1.232</v>
+        <v>0.581</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>3336</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>IJM</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>-0.0105</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>838600</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H54" t="n">
+        <v>54.52</v>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>2.795</v>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>2.698</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" s="7" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>5327</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>MEGAFB</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>811200</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H55" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="I55" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>2.609</v>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>2.272</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" s="7" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0339</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>CBHB</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>810600</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H56" t="n">
+        <v>66.77</v>
+      </c>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>1.066</v>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" s="7" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0453</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>EIPOWER</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E57" s="10" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>805200</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H57" t="n">
+        <v>59.42</v>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" s="7" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>5180</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>CLMT</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>-0.0089</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>799800</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H58" t="n">
+        <v>32.96</v>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" s="7" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>GENTING</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="E59" s="8" t="n">
+        <v>0.0167</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>737300</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H59" t="n">
+        <v>35.19</v>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>1.899</v>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>2.028</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" s="7" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>7134</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>PWF</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E60" s="8" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>719100</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>34.19</v>
+      </c>
+      <c r="H60" t="n">
+        <v>56.96</v>
+      </c>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" s="7" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>0318</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ELRIDGE</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E61" s="8" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>711700</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H61" t="n">
+        <v>65.36</v>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" s="7" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>8052</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>CGB</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>-0.005699999999999999</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>680200</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H62" t="n">
+        <v>46.72</v>
+      </c>
+      <c r="I62" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" s="7" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0127</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>JHM</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>655200</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H63" t="n">
+        <v>70.68000000000001</v>
+      </c>
+      <c r="I63" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>0.544</v>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" s="7" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>5248</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>BAUTO</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>-0.0164</v>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>653600</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H64" t="n">
+        <v>37.43</v>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>0.9370000000000001</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" s="7" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>7121</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>650700</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H65" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>0.8070000000000001</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" s="7" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0391</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>AMBEST</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="E66" s="10" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>648500</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H66" t="n">
+        <v>50.06</v>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>1.351</v>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>1.232</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" s="7" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="E67" s="10" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>627100</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H67" t="n">
+        <v>57.58</v>
+      </c>
+      <c r="I67" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>5.745</v>
+      </c>
+      <c r="K67" s="2" t="n">
+        <v>5.777</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" s="7" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>0167</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>MCLEAN</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="E68" s="10" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>610000</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H68" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>0.747</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" s="7" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="E69" s="10" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>579300</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H69" t="n">
+        <v>58.23</v>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="K69" s="2" t="n">
+        <v>1.063</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" s="7" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>0321</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>SDCG</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>558400</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H70" t="n">
+        <v>70.23</v>
+      </c>
+      <c r="I70" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>0.763</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" s="7" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>0045</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>SSB8</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="4" t="n">
+        <v>551500</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H71" t="n">
+        <v>57.53</v>
+      </c>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>0.601</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" s="7" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0246</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>CNERGEN</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>-0.0345</v>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>509100</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H72" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="I72" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" s="7" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>0245</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>MNHLDG</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="E73" s="10" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="F73" s="4" t="n">
+        <v>500200</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H73" t="n">
+        <v>54.58</v>
+      </c>
+      <c r="I73" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>3.854</v>
+      </c>
+      <c r="K73" s="2" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M53"/>
+  <autoFilter ref="A1:M73"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-08/bursa-report-2026-10-08.xlsx
+++ b/docs/downloads/2026-10-08/bursa-report-2026-10-08.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-08" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-08'!$A$1:$M$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-08'!$A$1:$M$144</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,10 +38,10 @@
       <color rgb="000CA30C"/>
     </font>
     <font>
-      <color rgb="00898781"/>
+      <color rgb="00D03B3B"/>
     </font>
     <font>
-      <color rgb="00D03B3B"/>
+      <color rgb="00898781"/>
     </font>
   </fonts>
   <fills count="4">
@@ -92,7 +92,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M112"/>
+  <dimension ref="A1:M144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -572,10 +572,10 @@
         <v>0.0357</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>3758900</v>
+        <v>4023900</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.93</v>
+        <v>0.99</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>55.82</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多，RSI 55.82处中性偏上，未超买；现价0.145高于50日均线0.131，技术面信号偏正面。</t>
+          <t>SAR转多，现价0.145高于50日均线0.131，RSI 55.82处中性偏上，未超买，信号可靠性尚可。</t>
         </is>
       </c>
     </row>
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>0</v>
+        <v>-0.0625</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>51741700</v>
+        <v>66238500</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="H3" t="n">
-        <v>21.03</v>
+        <v>20.64</v>
       </c>
       <c r="I3" s="13" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="J3" s="9" t="n">
-        <v>0.183</v>
+        <v>0.182</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>0.401</v>
@@ -664,19 +664,19 @@
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="E4" s="15" t="n">
-        <v>0.0292</v>
+        <v>0.0175</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>47241300</v>
+        <v>52137400</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="H4" t="n">
-        <v>70.95</v>
+        <v>69.97</v>
       </c>
       <c r="I4" s="16" t="inlineStr">
         <is>
@@ -684,10 +684,10 @@
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.776</v>
+        <v>0.775</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.707</v>
+        <v>0.706</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="14" t="inlineStr"/>
@@ -709,19 +709,19 @@
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.345</v>
+        <v>0.34</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>0.06150000000000001</v>
+        <v>0.0462</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>31001900</v>
+        <v>45783700</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.58</v>
+        <v>0.85</v>
       </c>
       <c r="H5" t="n">
-        <v>78.56999999999999</v>
+        <v>77.84</v>
       </c>
       <c r="I5" s="16" t="inlineStr">
         <is>
@@ -745,39 +745,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>1.95</v>
+        <v>0.185</v>
       </c>
       <c r="E6" s="15" t="n">
-        <v>0.0484</v>
+        <v>0.0571</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>23615300</v>
+        <v>37826800</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>1.03</v>
+        <v>0.59</v>
       </c>
       <c r="H6" t="n">
-        <v>68.23</v>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>62.96</v>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>1.791</v>
+        <v>0.166</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>1.633</v>
+        <v>0.131</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
@@ -790,39 +790,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.185</v>
+        <v>1.94</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>0.0571</v>
+        <v>0.043</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>18983400</v>
+        <v>28464900</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.3</v>
+        <v>1.24</v>
       </c>
       <c r="H7" t="n">
-        <v>62.96</v>
-      </c>
-      <c r="I7" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.67</v>
+      </c>
+      <c r="I7" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.166</v>
+        <v>1.79</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.131</v>
+        <v>1.633</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -850,10 +850,10 @@
         <v>0.0169</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>15373900</v>
+        <v>18559100</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="H8" t="n">
         <v>66.04000000000001</v>
@@ -895,10 +895,10 @@
         <v>0.0127</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>14868600</v>
+        <v>15271800</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="H9" t="n">
         <v>73.34999999999999</v>
@@ -934,19 +934,19 @@
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>0.0112</v>
+        <v>0.445</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>11186800</v>
+        <v>14164300</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.43</v>
+        <v>0.55</v>
       </c>
       <c r="H10" t="n">
-        <v>65.29000000000001</v>
+        <v>64.36</v>
       </c>
       <c r="I10" s="16" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.408</v>
+        <v>0.407</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>0.345</v>
@@ -985,10 +985,10 @@
         <v>0.0337</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>9424600</v>
+        <v>11891200</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1.45</v>
+        <v>1.83</v>
       </c>
       <c r="H11" t="n">
         <v>62.6</v>
@@ -1026,14 +1026,14 @@
       <c r="D12" s="9" t="n">
         <v>0.51</v>
       </c>
-      <c r="E12" s="10" t="n">
+      <c r="E12" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>9001900</v>
+        <v>10234200</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.34</v>
+        <v>0.38</v>
       </c>
       <c r="H12" t="n">
         <v>61.53</v>
@@ -1060,39 +1060,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>1.09</v>
+        <v>0.535</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>0.0187</v>
+        <v>0.019</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>6204600</v>
+        <v>9947100</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.44</v>
+        <v>1.41</v>
       </c>
       <c r="H13" t="n">
-        <v>53.37</v>
-      </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.08</v>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>1.074</v>
+        <v>0.521</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>1.035</v>
+        <v>0.53</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1105,33 +1105,40 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SLGC Berhad</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>0</v>
+        <v>1.08</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>0.009300000000000001</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>6110400</v>
+        <v>7304300</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.1</v>
+        <v>0.52</v>
+      </c>
+      <c r="H14" t="n">
+        <v>52.01</v>
       </c>
       <c r="I14" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J14" s="9" t="n"/>
-      <c r="K14" s="9" t="n"/>
+      <c r="J14" s="9" t="n">
+        <v>1.073</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>1.035</v>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
     </row>
@@ -1143,28 +1150,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SYSTECH</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.19</v>
+        <v>0.965</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>0.0857</v>
+        <v>0.184</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>5341100</v>
+        <v>7263200</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>1.05</v>
+        <v>2.62</v>
       </c>
       <c r="H15" t="n">
-        <v>67.62</v>
+        <v>85.7</v>
       </c>
       <c r="I15" s="16" t="inlineStr">
         <is>
@@ -1172,10 +1179,10 @@
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.165</v>
+        <v>0.62</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.165</v>
+        <v>0.469</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1188,40 +1195,33 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>SLGC Berhad</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.395</v>
+        <v>0.25</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>0</v>
+        <v>-0.0196</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>5278900</v>
+        <v>7011500</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="H16" t="n">
-        <v>38.38</v>
-      </c>
-      <c r="I16" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J16" s="9" t="n">
-        <v>0.403</v>
-      </c>
-      <c r="K16" s="9" t="n">
-        <v>0.41</v>
-      </c>
+        <v>0.12</v>
+      </c>
+      <c r="I16" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="n"/>
+      <c r="K16" s="9" t="n"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
     </row>
@@ -1233,39 +1233,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E17" s="15" t="n">
-        <v>0.019</v>
+        <v>4.94</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>-0.0276</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>5061700</v>
+        <v>6373600</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.72</v>
+        <v>0.25</v>
       </c>
       <c r="H17" t="n">
-        <v>55.08</v>
-      </c>
-      <c r="I17" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.14</v>
+      </c>
+      <c r="I17" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.521</v>
+        <v>4.908</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.53</v>
+        <v>4.644</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1278,28 +1278,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E18" s="15" t="n">
-        <v>0.0435</v>
+        <v>0.31</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>4866600</v>
+        <v>6026200</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.43</v>
+        <v>0.32</v>
       </c>
       <c r="H18" t="n">
-        <v>54.81</v>
+        <v>57.61</v>
       </c>
       <c r="I18" s="16" t="inlineStr">
         <is>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>1.167</v>
+        <v>0.305</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>1.12</v>
+        <v>0.295</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1323,28 +1323,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>SYSTECH</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="E19" s="17" t="n">
-        <v>-0.0217</v>
+        <v>0.19</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>0.0857</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>4793400</v>
+        <v>5829100</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.19</v>
+        <v>1.15</v>
       </c>
       <c r="H19" t="n">
-        <v>56.95</v>
+        <v>67.62</v>
       </c>
       <c r="I19" s="16" t="inlineStr">
         <is>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>4.911</v>
+        <v>0.165</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>4.645</v>
+        <v>0.165</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1368,28 +1368,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0131</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DFX</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.14</v>
+        <v>0.78</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>-0.0345</v>
+        <v>0</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>4575900</v>
+        <v>5639800</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.61</v>
+        <v>0.39</v>
       </c>
       <c r="H20" t="n">
-        <v>70.08</v>
+        <v>53.15</v>
       </c>
       <c r="I20" s="16" t="inlineStr">
         <is>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.113</v>
+        <v>0.776</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.093</v>
+        <v>0.776</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1413,28 +1413,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.91</v>
+        <v>1.18</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>0.1166</v>
+        <v>0.0261</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>4357200</v>
+        <v>5450100</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>1.57</v>
+        <v>0.48</v>
       </c>
       <c r="H21" t="n">
-        <v>84.19</v>
+        <v>52.79</v>
       </c>
       <c r="I21" s="16" t="inlineStr">
         <is>
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.614</v>
+        <v>1.165</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.467</v>
+        <v>1.12</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1458,39 +1458,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0131</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>DFX</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="E22" s="17" t="n">
-        <v>-0.0022</v>
+        <v>0.14</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>-0.0345</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>4150500</v>
+        <v>5344600</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.26</v>
+        <v>0.71</v>
       </c>
       <c r="H22" t="n">
-        <v>27.42</v>
-      </c>
-      <c r="I22" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.08</v>
+      </c>
+      <c r="I22" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>4.739</v>
+        <v>0.113</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>4.896</v>
+        <v>0.093</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1503,28 +1503,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>7.19</v>
+        <v>0.395</v>
       </c>
       <c r="E23" s="17" t="n">
-        <v>-0.0191</v>
+        <v>0</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>4054200</v>
+        <v>5289000</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.3</v>
+        <v>0.47</v>
       </c>
       <c r="H23" t="n">
-        <v>29.57</v>
+        <v>38.38</v>
       </c>
       <c r="I23" s="13" t="inlineStr">
         <is>
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>7.674</v>
+        <v>0.403</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>7.741</v>
+        <v>0.41</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1548,28 +1548,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.35</v>
+        <v>0.535</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>0.0145</v>
+        <v>0.049</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>3858300</v>
+        <v>5146200</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.49</v>
+        <v>1.3</v>
       </c>
       <c r="H24" t="n">
-        <v>56.39</v>
+        <v>69.7</v>
       </c>
       <c r="I24" s="16" t="inlineStr">
         <is>
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.343</v>
+        <v>0.469</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.324</v>
+        <v>0.449</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1593,28 +1593,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E25" s="15" t="n">
-        <v>0.0222</v>
+        <v>7.19</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>-0.0191</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>3854500</v>
+        <v>4947100</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.15</v>
+        <v>0.37</v>
       </c>
       <c r="H25" t="n">
-        <v>34.28</v>
+        <v>29.57</v>
       </c>
       <c r="I25" s="13" t="inlineStr">
         <is>
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.252</v>
+        <v>7.674</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.305</v>
+        <v>7.741</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1638,39 +1638,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="E26" s="15" t="n">
-        <v>0.0076</v>
+        <v>4.58</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>-0.0022</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>3797000</v>
+        <v>4665200</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.91</v>
+        <v>0.29</v>
       </c>
       <c r="H26" t="n">
-        <v>88.34999999999999</v>
-      </c>
-      <c r="I26" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.42</v>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.501</v>
+        <v>4.739</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.438</v>
+        <v>4.896</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1683,28 +1683,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>0</v>
+        <v>0.35</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>0.0145</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>3617200</v>
+        <v>4584600</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.19</v>
+        <v>0.58</v>
       </c>
       <c r="H27" t="n">
-        <v>57.61</v>
+        <v>56.39</v>
       </c>
       <c r="I27" s="16" t="inlineStr">
         <is>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.305</v>
+        <v>0.343</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.295</v>
+        <v>0.324</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1728,28 +1728,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E28" s="10" t="n">
-        <v>0</v>
+        <v>0.44</v>
+      </c>
+      <c r="E28" s="15" t="n">
+        <v>0.0115</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>3514100</v>
+        <v>4487700</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.24</v>
+        <v>0.44</v>
       </c>
       <c r="H28" t="n">
-        <v>53.15</v>
+        <v>48.53</v>
       </c>
       <c r="I28" s="16" t="inlineStr">
         <is>
@@ -1757,10 +1757,10 @@
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.776</v>
+        <v>0.451</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.776</v>
+        <v>0.425</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1773,28 +1773,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>TUNEPRO</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.275</v>
+        <v>0.67</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>0.0784</v>
+        <v>0.0152</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>3494300</v>
+        <v>4369600</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>4.15</v>
+        <v>1.04</v>
       </c>
       <c r="H29" t="n">
-        <v>65.11</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="I29" s="16" t="inlineStr">
         <is>
@@ -1802,10 +1802,10 @@
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.251</v>
+        <v>0.502</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.259</v>
+        <v>0.438</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1818,33 +1818,40 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0473</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>EVOCOM</t>
+          <t>TUNEPRO</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.11</v>
+        <v>0.265</v>
       </c>
       <c r="E30" s="15" t="n">
-        <v>0.0476</v>
+        <v>0.0392</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>3479700</v>
+        <v>4359000</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I30" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J30" s="9" t="n"/>
-      <c r="K30" s="9" t="n"/>
+        <v>5.18</v>
+      </c>
+      <c r="H30" t="n">
+        <v>60.23</v>
+      </c>
+      <c r="I30" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K30" s="9" t="n">
+        <v>0.259</v>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
     </row>
@@ -1865,19 +1872,19 @@
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>0</v>
+        <v>-0.0036</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3323400</v>
+        <v>4249400</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="H31" t="n">
-        <v>64.94</v>
+        <v>64</v>
       </c>
       <c r="I31" s="16" t="inlineStr">
         <is>
@@ -1885,7 +1892,7 @@
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>2.614</v>
+        <v>2.613</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>2.501</v>
@@ -1901,28 +1908,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.62</v>
+        <v>0.865</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>0</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3303400</v>
+        <v>3999500</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.31</v>
+        <v>0.22</v>
       </c>
       <c r="H32" t="n">
-        <v>55.75</v>
+        <v>46.72</v>
       </c>
       <c r="I32" s="16" t="inlineStr">
         <is>
@@ -1930,10 +1937,10 @@
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.61</v>
+        <v>0.868</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.611</v>
+        <v>0.869</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1946,39 +1953,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E33" s="15" t="n">
-        <v>0.0115</v>
+        <v>7.17</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>-0.011</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>3282500</v>
+        <v>3997400</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.32</v>
+        <v>0.42</v>
       </c>
       <c r="H33" t="n">
-        <v>48.53</v>
-      </c>
-      <c r="I33" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>19.36</v>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.451</v>
+        <v>7.648</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.425</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1991,39 +1998,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.53</v>
+        <v>0.23</v>
       </c>
       <c r="E34" s="15" t="n">
-        <v>0.0392</v>
+        <v>0.0222</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>3258900</v>
+        <v>3962900</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.83</v>
+        <v>0.15</v>
       </c>
       <c r="H34" t="n">
-        <v>68.93000000000001</v>
-      </c>
-      <c r="I34" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.28</v>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.468</v>
+        <v>0.252</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.449</v>
+        <v>0.305</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2036,28 +2043,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="E35" s="17" t="n">
-        <v>-0.009300000000000001</v>
+        <v>9.84</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>-0.003</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>3164100</v>
+        <v>3746300</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="H35" t="n">
-        <v>39.95</v>
+        <v>31.69</v>
       </c>
       <c r="I35" s="13" t="inlineStr">
         <is>
@@ -2065,10 +2072,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>2.235</v>
+        <v>10.047</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>2.227</v>
+        <v>10.219</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2081,28 +2088,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>9.84</v>
-      </c>
-      <c r="E36" s="17" t="n">
-        <v>-0.003</v>
+        <v>0.195</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>-0.025</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>3041200</v>
+        <v>3722800</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.24</v>
+        <v>0.16</v>
       </c>
       <c r="H36" t="n">
-        <v>31.69</v>
+        <v>50.82</v>
       </c>
       <c r="I36" s="13" t="inlineStr">
         <is>
@@ -2110,10 +2117,10 @@
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>10.047</v>
+        <v>0.196</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>10.219</v>
+        <v>0.183</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2137,14 +2144,14 @@
       <c r="D37" s="9" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="E37" s="10" t="n">
+      <c r="E37" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>2687700</v>
+        <v>3669700</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="H37" t="n">
         <v>50.2</v>
@@ -2171,40 +2178,33 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>EVOCOM</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E38" s="10" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="E38" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>2521000</v>
+        <v>3592900</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="H38" t="n">
-        <v>47.06</v>
-      </c>
-      <c r="I38" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J38" s="9" t="n">
-        <v>0.208</v>
-      </c>
-      <c r="K38" s="9" t="n">
-        <v>0.209</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J38" s="9" t="n"/>
+      <c r="K38" s="9" t="n"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
     </row>
@@ -2216,39 +2216,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0209</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>AIMFLEX</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E39" s="17" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.105</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>-0.0455</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>2470900</v>
+        <v>3496300</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.13</v>
+        <v>0.51</v>
       </c>
       <c r="H39" t="n">
-        <v>46.72</v>
-      </c>
-      <c r="I39" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.5</v>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.868</v>
+        <v>0.115</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.869</v>
+        <v>0.123</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2261,39 +2261,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.78</v>
+        <v>2.13</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>0</v>
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2347000</v>
+        <v>3386800</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.3</v>
+        <v>0.23</v>
       </c>
       <c r="H40" t="n">
-        <v>51.62</v>
-      </c>
-      <c r="I40" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.95</v>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.776</v>
+        <v>2.235</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.772</v>
+        <v>2.227</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2306,28 +2306,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.805</v>
+        <v>0.62</v>
       </c>
       <c r="E41" s="17" t="n">
-        <v>-0.0242</v>
+        <v>0</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>2346200</v>
+        <v>3303400</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="H41" t="n">
-        <v>68.16</v>
+        <v>55.75</v>
       </c>
       <c r="I41" s="16" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.731</v>
+        <v>0.61</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.648</v>
+        <v>0.611</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2351,28 +2351,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ITMAX</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>4.64</v>
+        <v>0.205</v>
       </c>
       <c r="E42" s="17" t="n">
-        <v>-0.0107</v>
+        <v>0</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>2227500</v>
+        <v>3165000</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>1.05</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>59.2</v>
+        <v>47.06</v>
       </c>
       <c r="I42" s="16" t="inlineStr">
         <is>
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>4.539</v>
+        <v>0.208</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>4.489</v>
+        <v>0.209</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2396,39 +2396,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E43" s="17" t="n">
-        <v>-0.0189</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>-0.0182</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2044200</v>
+        <v>3013400</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.12</v>
+        <v>0.44</v>
       </c>
       <c r="H43" t="n">
-        <v>55.23</v>
-      </c>
-      <c r="I43" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.41</v>
+      </c>
+      <c r="I43" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.511</v>
+        <v>0.732</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.436</v>
+        <v>0.649</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2441,39 +2441,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>7.15</v>
+        <v>0.645</v>
       </c>
       <c r="E44" s="17" t="n">
-        <v>-0.0138</v>
+        <v>0</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>2042900</v>
+        <v>2847000</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.22</v>
+        <v>0.78</v>
       </c>
       <c r="H44" t="n">
-        <v>18.98</v>
-      </c>
-      <c r="I44" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.53</v>
+      </c>
+      <c r="I44" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>7.646</v>
+        <v>0.632</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>8.119999999999999</v>
+        <v>0.601</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2486,39 +2486,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="E45" s="17" t="n">
-        <v>-0.0089</v>
+        <v>0.785</v>
+      </c>
+      <c r="E45" s="15" t="n">
+        <v>0.068</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>1963100</v>
+        <v>2832200</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.14</v>
+        <v>1.72</v>
       </c>
       <c r="H45" t="n">
-        <v>48.87</v>
-      </c>
-      <c r="I45" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>79.68000000000001</v>
+      </c>
+      <c r="I45" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>5.648</v>
+        <v>0.663</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>5.332</v>
+        <v>0.618</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2531,28 +2531,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E46" s="17" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.295</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>-0.0167</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>1962300</v>
+        <v>2727600</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H46" t="n">
-        <v>65.56999999999999</v>
+        <v>52.62</v>
       </c>
       <c r="I46" s="16" t="inlineStr">
         <is>
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.577</v>
+        <v>0.291</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.516</v>
+        <v>0.28</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2576,28 +2576,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1.2</v>
+        <v>0.785</v>
       </c>
       <c r="E47" s="15" t="n">
-        <v>0.0345</v>
+        <v>0.0064</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1892100</v>
+        <v>2697000</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.25</v>
+        <v>0.34</v>
       </c>
       <c r="H47" t="n">
-        <v>65.72</v>
+        <v>52.99</v>
       </c>
       <c r="I47" s="16" t="inlineStr">
         <is>
@@ -2605,10 +2605,10 @@
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>1.065</v>
+        <v>0.777</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.819</v>
+        <v>0.772</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2621,39 +2621,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E48" s="10" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E48" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1827600</v>
+        <v>2689300</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="H48" t="n">
-        <v>49.23</v>
-      </c>
-      <c r="I48" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.6</v>
+      </c>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.295</v>
+        <v>0.367</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.296</v>
+        <v>0.368</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2666,39 +2666,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="E49" s="17" t="n">
-        <v>-0.0102</v>
+        <v>0.65</v>
+      </c>
+      <c r="E49" s="15" t="n">
+        <v>0.007800000000000001</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>1782500</v>
+        <v>2683500</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.24</v>
+        <v>0.73</v>
       </c>
       <c r="H49" t="n">
-        <v>25.06</v>
-      </c>
-      <c r="I49" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.64</v>
+      </c>
+      <c r="I49" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.527</v>
+        <v>0.593</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.573</v>
+        <v>0.581</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2711,28 +2711,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.37</v>
+        <v>0.525</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>0</v>
+        <v>-0.009399999999999999</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>1764000</v>
+        <v>2564600</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="H50" t="n">
-        <v>53.6</v>
+        <v>56.36</v>
       </c>
       <c r="I50" s="13" t="inlineStr">
         <is>
@@ -2740,10 +2740,10 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.367</v>
+        <v>0.512</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.368</v>
+        <v>0.436</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2756,28 +2756,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.705</v>
+        <v>0.64</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>0</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>1740300</v>
+        <v>2506400</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.22</v>
+        <v>0.13</v>
       </c>
       <c r="H51" t="n">
-        <v>54.63</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="I51" s="16" t="inlineStr">
         <is>
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.577</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.679</v>
+        <v>0.516</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2801,39 +2801,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GREENTEC</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E52" s="15" t="n">
-        <v>0.1061</v>
+        <v>5.54</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>-0.0142</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>1597500</v>
+        <v>2400600</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>2.06</v>
+        <v>0.17</v>
       </c>
       <c r="H52" t="n">
-        <v>95.37</v>
-      </c>
-      <c r="I52" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.65</v>
+      </c>
+      <c r="I52" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.244</v>
+        <v>5.645</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.204</v>
+        <v>5.332</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2846,39 +2846,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>ITMAX</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E53" s="15" t="n">
-        <v>0.0189</v>
+        <v>4.63</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>-0.0128</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>1584900</v>
+        <v>2260600</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.43</v>
+        <v>1.06</v>
       </c>
       <c r="H53" t="n">
-        <v>38.82</v>
-      </c>
-      <c r="I53" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.34</v>
+      </c>
+      <c r="I53" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.554</v>
+        <v>4.538</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.583</v>
+        <v>4.489</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2891,39 +2891,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E54" s="15" t="n">
-        <v>0.0147</v>
+        <v>0.475</v>
+      </c>
+      <c r="E54" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>1553000</v>
+        <v>2178800</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.28</v>
+        <v>0.06</v>
       </c>
       <c r="H54" t="n">
-        <v>60.08</v>
-      </c>
-      <c r="I54" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.61</v>
+      </c>
+      <c r="I54" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.326</v>
+        <v>0.556</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.339</v>
+        <v>0.755</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2936,28 +2936,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>6.08</v>
-      </c>
-      <c r="E55" s="17" t="n">
-        <v>-0.047</v>
+        <v>0.345</v>
+      </c>
+      <c r="E55" s="15" t="n">
+        <v>0.0147</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>1546600</v>
+        <v>2103400</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="H55" t="n">
-        <v>56.94</v>
+        <v>60.08</v>
       </c>
       <c r="I55" s="16" t="inlineStr">
         <is>
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>5.742</v>
+        <v>0.326</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>5.776</v>
+        <v>0.339</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2981,28 +2981,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="E56" s="10" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="E56" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>1527000</v>
+        <v>2096600</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="H56" t="n">
-        <v>28.24</v>
+        <v>50.11</v>
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>1.509</v>
+        <v>1.753</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>1.623</v>
+        <v>1.782</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3026,39 +3026,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>1.29</v>
+        <v>0.385</v>
       </c>
       <c r="E57" s="15" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.0405</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>1497900</v>
+        <v>2059200</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.13</v>
+        <v>0.24</v>
       </c>
       <c r="H57" t="n">
-        <v>44.27</v>
-      </c>
-      <c r="I57" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.48999999999999</v>
+      </c>
+      <c r="I57" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>1.329</v>
+        <v>0.352</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>1.309</v>
+        <v>0.319</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3071,28 +3071,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E58" s="10" t="n">
-        <v>0</v>
+        <v>1.21</v>
+      </c>
+      <c r="E58" s="15" t="n">
+        <v>0.0431</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>1488900</v>
+        <v>2025500</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.41</v>
+        <v>0.26</v>
       </c>
       <c r="H58" t="n">
-        <v>65.8</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="I58" s="16" t="inlineStr">
         <is>
@@ -3100,10 +3100,10 @@
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.592</v>
+        <v>1.066</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.581</v>
+        <v>0.819</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3116,28 +3116,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E59" s="17" t="n">
-        <v>-0.0179</v>
+        <v>6.05</v>
+      </c>
+      <c r="E59" s="10" t="n">
+        <v>-0.0517</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>1468000</v>
+        <v>1999700</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.14</v>
+        <v>0.47</v>
       </c>
       <c r="H59" t="n">
-        <v>62.18</v>
+        <v>56.32</v>
       </c>
       <c r="I59" s="16" t="inlineStr">
         <is>
@@ -3145,10 +3145,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>1.065</v>
+        <v>5.739</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0.912</v>
+        <v>5.776</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3161,28 +3161,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>7943</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>GREENTEC</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.38</v>
+        <v>0.345</v>
       </c>
       <c r="E60" s="15" t="n">
-        <v>0.027</v>
+        <v>0.0455</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>1467700</v>
+        <v>1976600</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.17</v>
+        <v>2.55</v>
       </c>
       <c r="H60" t="n">
-        <v>68.08</v>
+        <v>94.69</v>
       </c>
       <c r="I60" s="16" t="inlineStr">
         <is>
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.351</v>
+        <v>0.242</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.319</v>
+        <v>0.204</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3206,39 +3206,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1.75</v>
+        <v>0.705</v>
       </c>
       <c r="E61" s="17" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>1462900</v>
+        <v>1839100</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.28</v>
+        <v>0.23</v>
       </c>
       <c r="H61" t="n">
-        <v>48.61</v>
-      </c>
-      <c r="I61" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.63</v>
+      </c>
+      <c r="I61" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>1.752</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>1.781</v>
+        <v>0.679</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3251,39 +3251,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="E62" s="15" t="n">
-        <v>0.0211</v>
+        <v>0.29</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>-0.0169</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1411200</v>
+        <v>1838600</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.04</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H62" t="n">
-        <v>29.13</v>
-      </c>
-      <c r="I62" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>33.43</v>
+      </c>
+      <c r="I62" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.295</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.756</v>
+        <v>0.296</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3296,28 +3296,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>BNASTRA</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E63" s="17" t="n">
-        <v>-0.0122</v>
+        <v>2.71</v>
+      </c>
+      <c r="E63" s="15" t="n">
+        <v>0.08400000000000001</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>1387600</v>
+        <v>1801700</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.1</v>
+        <v>1.61</v>
       </c>
       <c r="H63" t="n">
-        <v>60.44</v>
+        <v>86.66</v>
       </c>
       <c r="I63" s="16" t="inlineStr">
         <is>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0.767</v>
+        <v>2.466</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0.711</v>
+        <v>2.348</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3341,28 +3341,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>EMETALL</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E64" s="10" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="E64" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>1275200</v>
+        <v>1793500</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>2.91</v>
+        <v>0.25</v>
       </c>
       <c r="H64" t="n">
-        <v>57.26</v>
+        <v>26.21</v>
       </c>
       <c r="I64" s="13" t="inlineStr">
         <is>
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>0.44</v>
+        <v>0.528</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.437</v>
+        <v>0.573</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3386,28 +3386,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E65" s="17" t="n">
-        <v>-0.0104</v>
+        <v>1.18</v>
+      </c>
+      <c r="E65" s="15" t="n">
+        <v>0.0172</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>1268500</v>
+        <v>1792800</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H65" t="n">
-        <v>73.43000000000001</v>
+        <v>73.17</v>
       </c>
       <c r="I65" s="16" t="inlineStr">
         <is>
@@ -3415,10 +3415,10 @@
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>0.414</v>
+        <v>0.999</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.367</v>
+        <v>0.852</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3431,39 +3431,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="E66" s="15" t="n">
-        <v>0.0162</v>
+        <v>2.81</v>
+      </c>
+      <c r="E66" s="10" t="n">
+        <v>-0.014</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>1268200</v>
+        <v>1787800</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.32</v>
+        <v>0.13</v>
       </c>
       <c r="H66" t="n">
-        <v>39.34</v>
-      </c>
-      <c r="I66" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.57</v>
+      </c>
+      <c r="I66" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>3.193</v>
+        <v>2.794</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>3.393</v>
+        <v>2.698</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3476,28 +3476,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0148</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>SUNZEN</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="E67" s="10" t="n">
-        <v>0</v>
+        <v>0.235</v>
+      </c>
+      <c r="E67" s="15" t="n">
+        <v>0.0444</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>1216700</v>
+        <v>1731100</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.39</v>
+        <v>7.52</v>
       </c>
       <c r="H67" t="n">
-        <v>71.09999999999999</v>
+        <v>65.84</v>
       </c>
       <c r="I67" s="16" t="inlineStr">
         <is>
@@ -3505,10 +3505,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>2.608</v>
+        <v>0.226</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>2.272</v>
+        <v>0.225</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3521,28 +3521,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.72</v>
+        <v>1.11</v>
       </c>
       <c r="E68" s="10" t="n">
-        <v>0</v>
+        <v>-0.0089</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>1211100</v>
+        <v>1730600</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="H68" t="n">
-        <v>66.03</v>
+        <v>64.39</v>
       </c>
       <c r="I68" s="16" t="inlineStr">
         <is>
@@ -3550,10 +3550,10 @@
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.669</v>
+        <v>1.065</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.604</v>
+        <v>0.912</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3566,28 +3566,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E69" s="17" t="n">
-        <v>-0.0227</v>
+        <v>0.535</v>
+      </c>
+      <c r="E69" s="15" t="n">
+        <v>0.009399999999999999</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1201200</v>
+        <v>1726400</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="H69" t="n">
-        <v>60.08</v>
+        <v>35.53</v>
       </c>
       <c r="I69" s="13" t="inlineStr">
         <is>
@@ -3595,10 +3595,10 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>0.619</v>
+        <v>0.554</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>0.526</v>
+        <v>0.583</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3611,39 +3611,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MFLOUR</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.59</v>
+        <v>2.76</v>
       </c>
       <c r="E70" s="17" t="n">
-        <v>-0.0167</v>
+        <v>0</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>1197200</v>
+        <v>1709600</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="H70" t="n">
-        <v>32.88</v>
-      </c>
-      <c r="I70" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.09999999999999</v>
+      </c>
+      <c r="I70" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.619</v>
+        <v>2.608</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.638</v>
+        <v>2.272</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3656,39 +3656,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0023</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>IFCAMSC</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.205</v>
+        <v>0.805</v>
       </c>
       <c r="E71" s="10" t="n">
-        <v>0</v>
+        <v>-0.0183</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1173500</v>
+        <v>1667100</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>2.11</v>
+        <v>0.12</v>
       </c>
       <c r="H71" t="n">
-        <v>48.37</v>
-      </c>
-      <c r="I71" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.45</v>
+      </c>
+      <c r="I71" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.205</v>
+        <v>0.766</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.214</v>
+        <v>0.711</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3701,39 +3701,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.3</v>
+        <v>1.36</v>
       </c>
       <c r="E72" s="10" t="n">
-        <v>0</v>
+        <v>-0.0423</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>1144000</v>
+        <v>1654000</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.19</v>
+        <v>0.51</v>
       </c>
       <c r="H72" t="n">
-        <v>65.41</v>
-      </c>
-      <c r="I72" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>70.73</v>
+      </c>
+      <c r="I72" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.289</v>
+        <v>1.222</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0.274</v>
+        <v>0.999</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3746,28 +3746,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>1.36</v>
+        <v>0.805</v>
       </c>
       <c r="E73" s="17" t="n">
-        <v>-0.0423</v>
+        <v>0</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>1138700</v>
+        <v>1642400</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.35</v>
+        <v>0.27</v>
       </c>
       <c r="H73" t="n">
-        <v>70.73</v>
+        <v>70.23</v>
       </c>
       <c r="I73" s="16" t="inlineStr">
         <is>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>1.222</v>
+        <v>0.783</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.999</v>
+        <v>0.763</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3791,39 +3791,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>1.83</v>
+        <v>3.12</v>
       </c>
       <c r="E74" s="15" t="n">
-        <v>0.0167</v>
+        <v>0.013</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>1103500</v>
+        <v>1619900</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="H74" t="n">
-        <v>35.19</v>
-      </c>
-      <c r="I74" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>38.16</v>
+      </c>
+      <c r="I74" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>1.899</v>
+        <v>3.192</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>2.028</v>
+        <v>3.393</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3836,28 +3836,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="E75" s="17" t="n">
-        <v>-0.0105</v>
+        <v>1.29</v>
+      </c>
+      <c r="E75" s="15" t="n">
+        <v>0.007800000000000001</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1097600</v>
+        <v>1604900</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="H75" t="n">
-        <v>54.52</v>
+        <v>44.27</v>
       </c>
       <c r="I75" s="13" t="inlineStr">
         <is>
@@ -3865,10 +3865,10 @@
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>2.795</v>
+        <v>1.329</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>2.698</v>
+        <v>1.309</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3881,39 +3881,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>7195</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BNASTRA</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>2.83</v>
+        <v>3.44</v>
       </c>
       <c r="E76" s="15" t="n">
-        <v>0.132</v>
+        <v>0.0424</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1081600</v>
+        <v>1604600</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.97</v>
+        <v>0.26</v>
       </c>
       <c r="H76" t="n">
-        <v>89.76000000000001</v>
-      </c>
-      <c r="I76" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.32</v>
+      </c>
+      <c r="I76" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>2.478</v>
+        <v>3.486</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>2.35</v>
+        <v>3.663</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3926,39 +3926,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>2.74</v>
+        <v>1.45</v>
       </c>
       <c r="E77" s="17" t="n">
-        <v>-0.0284</v>
+        <v>0</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1069400</v>
+        <v>1603000</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.19</v>
+        <v>0.74</v>
       </c>
       <c r="H77" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="I77" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.24</v>
+      </c>
+      <c r="I77" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>2.627</v>
+        <v>1.509</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>2.58</v>
+        <v>1.623</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3971,39 +3971,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E78" s="15" t="n">
-        <v>0.0145</v>
+        <v>0.6</v>
+      </c>
+      <c r="E78" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>1056600</v>
+        <v>1585300</v>
       </c>
       <c r="G78" s="12" t="n">
         <v>0.28</v>
       </c>
       <c r="H78" t="n">
-        <v>37.71</v>
-      </c>
-      <c r="I78" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.68000000000001</v>
+      </c>
+      <c r="I78" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.366</v>
+        <v>0.544</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.385</v>
+        <v>0.493</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4016,39 +4016,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="E79" s="10" t="n">
-        <v>0</v>
+        <v>-0.0139</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>1055900</v>
+        <v>1568100</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.96</v>
+        <v>0.17</v>
       </c>
       <c r="H79" t="n">
-        <v>8.08</v>
-      </c>
-      <c r="I79" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.19</v>
+      </c>
+      <c r="I79" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.586</v>
+        <v>0.668</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.624</v>
+        <v>0.603</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4061,28 +4061,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="E80" s="17" t="n">
-        <v>-0.01</v>
+        <v>1.3</v>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>-0.0299</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>1054700</v>
+        <v>1545100</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.13</v>
+        <v>0.55</v>
       </c>
       <c r="H80" t="n">
-        <v>59.42</v>
+        <v>46.63</v>
       </c>
       <c r="I80" s="13" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.963</v>
+        <v>1.348</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.8159999999999999</v>
+        <v>1.231</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4106,39 +4106,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="E81" s="15" t="n">
-        <v>0.0364</v>
+        <v>0.295</v>
+      </c>
+      <c r="E81" s="10" t="n">
+        <v>-0.0167</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>984400</v>
+        <v>1527900</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.16</v>
+        <v>0.25</v>
       </c>
       <c r="H81" t="n">
-        <v>41.65</v>
-      </c>
-      <c r="I81" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.8</v>
+      </c>
+      <c r="I81" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>3.485</v>
+        <v>0.288</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>3.663</v>
+        <v>0.274</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4151,28 +4151,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>1.16</v>
+        <v>2.71</v>
       </c>
       <c r="E82" s="10" t="n">
-        <v>0</v>
+        <v>-0.039</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>953000</v>
+        <v>1498000</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="H82" t="n">
-        <v>72.05</v>
+        <v>58.65</v>
       </c>
       <c r="I82" s="16" t="inlineStr">
         <is>
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.997</v>
+        <v>2.624</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.851</v>
+        <v>2.579</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4196,28 +4196,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E83" s="10" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E83" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>938400</v>
+        <v>1477800</v>
       </c>
       <c r="G83" s="12" t="n">
         <v>0.15</v>
       </c>
       <c r="H83" t="n">
-        <v>70.23</v>
+        <v>55.35</v>
       </c>
       <c r="I83" s="16" t="inlineStr">
         <is>
@@ -4225,10 +4225,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.783</v>
+        <v>0.276</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.763</v>
+        <v>0.304</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4241,28 +4241,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E84" s="17" t="n">
-        <v>-0.025</v>
+        <v>0.83</v>
+      </c>
+      <c r="E84" s="10" t="n">
+        <v>-0.006</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>933200</v>
+        <v>1458400</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.3</v>
+        <v>0.22</v>
       </c>
       <c r="H84" t="n">
-        <v>55.67</v>
+        <v>73.27</v>
       </c>
       <c r="I84" s="16" t="inlineStr">
         <is>
@@ -4270,10 +4270,10 @@
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>3.856</v>
+        <v>0.741</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>3.561</v>
+        <v>0.659</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4286,39 +4286,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>7173</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>TOYOVEN</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="E85" s="17" t="n">
-        <v>-0.0075</v>
+        <v>0.225</v>
+      </c>
+      <c r="E85" s="15" t="n">
+        <v>0.1538</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>905100</v>
+        <v>1362100</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.32</v>
+        <v>9.85</v>
       </c>
       <c r="H85" t="n">
-        <v>50.06</v>
-      </c>
-      <c r="I85" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.16</v>
+      </c>
+      <c r="I85" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>1.351</v>
+        <v>0.201</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>1.232</v>
+        <v>0.206</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4331,28 +4331,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E86" s="17" t="n">
-        <v>-0.018</v>
+        <v>0.475</v>
+      </c>
+      <c r="E86" s="10" t="n">
+        <v>-0.0104</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>836100</v>
+        <v>1333300</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.13</v>
+        <v>0.4</v>
       </c>
       <c r="H86" t="n">
-        <v>70.51000000000001</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="I86" s="16" t="inlineStr">
         <is>
@@ -4360,10 +4360,10 @@
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>0.74</v>
+        <v>0.414</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.659</v>
+        <v>0.367</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4376,39 +4376,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.6</v>
+        <v>0.645</v>
       </c>
       <c r="E87" s="10" t="n">
-        <v>0</v>
+        <v>-0.0227</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>832100</v>
+        <v>1330300</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.15</v>
+        <v>0.59</v>
       </c>
       <c r="H87" t="n">
-        <v>70.68000000000001</v>
-      </c>
-      <c r="I87" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.08</v>
+      </c>
+      <c r="I87" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>0.544</v>
+        <v>0.619</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>0.493</v>
+        <v>0.526</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4421,39 +4421,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E88" s="17" t="n">
-        <v>-0.0179</v>
+        <v>3.89</v>
+      </c>
+      <c r="E88" s="10" t="n">
+        <v>-0.0275</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>830200</v>
+        <v>1306400</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.2</v>
+        <v>0.42</v>
       </c>
       <c r="H88" t="n">
-        <v>30.62</v>
-      </c>
-      <c r="I88" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.12</v>
+      </c>
+      <c r="I88" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>0.572</v>
+        <v>3.855</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0.583</v>
+        <v>3.561</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4466,39 +4466,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>EMETALL</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>12.98</v>
-      </c>
-      <c r="E89" s="15" t="n">
-        <v>0.009300000000000001</v>
+        <v>0.44</v>
+      </c>
+      <c r="E89" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>780700</v>
+        <v>1275200</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.09</v>
+        <v>2.91</v>
       </c>
       <c r="H89" t="n">
-        <v>43.04</v>
-      </c>
-      <c r="I89" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.26</v>
+      </c>
+      <c r="I89" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>13.049</v>
+        <v>0.44</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>13.586</v>
+        <v>0.437</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4511,28 +4511,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E90" s="17" t="n">
-        <v>-0.0109</v>
+        <v>0.985</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>-0.015</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>746800</v>
+        <v>1259600</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.34</v>
+        <v>0.15</v>
       </c>
       <c r="H90" t="n">
-        <v>39.18</v>
+        <v>58.55</v>
       </c>
       <c r="I90" s="13" t="inlineStr">
         <is>
@@ -4540,10 +4540,10 @@
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.923</v>
+        <v>0.963</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4556,39 +4556,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>MFLOUR</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E91" s="17" t="n">
-        <v>-0.0138</v>
+        <v>0.59</v>
+      </c>
+      <c r="E91" s="10" t="n">
+        <v>-0.0167</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>739700</v>
+        <v>1223600</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.08</v>
+        <v>0.55</v>
       </c>
       <c r="H91" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="I91" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.88</v>
+      </c>
+      <c r="I91" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>2.771</v>
+        <v>0.619</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>2.594</v>
+        <v>0.638</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4601,39 +4601,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E92" s="17" t="n">
-        <v>-0.007800000000000001</v>
+        <v>6.11</v>
+      </c>
+      <c r="E92" s="10" t="n">
+        <v>-0.0113</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>732500</v>
+        <v>1221600</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.2</v>
+        <v>0.28</v>
       </c>
       <c r="H92" t="n">
-        <v>55.55</v>
-      </c>
-      <c r="I92" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>23</v>
+      </c>
+      <c r="I92" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>0.631</v>
+        <v>6.513</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>0.6</v>
+        <v>6.853</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4646,28 +4646,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="E93" s="10" t="n">
-        <v>0</v>
+        <v>1.82</v>
+      </c>
+      <c r="E93" s="15" t="n">
+        <v>0.0111</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>732200</v>
+        <v>1207200</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.14</v>
+        <v>0.27</v>
       </c>
       <c r="H93" t="n">
-        <v>63.98</v>
+        <v>33.28</v>
       </c>
       <c r="I93" s="13" t="inlineStr">
         <is>
@@ -4675,10 +4675,10 @@
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>0.906</v>
+        <v>1.898</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0.862</v>
+        <v>2.028</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4691,28 +4691,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>7134</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>PWF</t>
+          <t>ALPHA</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="E94" s="15" t="n">
-        <v>0.027</v>
+        <v>0.28</v>
+      </c>
+      <c r="E94" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>719100</v>
+        <v>1196600</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>34.19</v>
+        <v>0.51</v>
       </c>
       <c r="H94" t="n">
-        <v>56.96</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="I94" s="16" t="inlineStr">
         <is>
@@ -4720,10 +4720,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>0.742</v>
+        <v>0.258</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.744</v>
+        <v>0.257</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4736,28 +4736,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>0023</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>IFCAMSC</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>6.1</v>
+        <v>0.205</v>
       </c>
       <c r="E95" s="17" t="n">
-        <v>-0.0129</v>
+        <v>0</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>692300</v>
+        <v>1173500</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.16</v>
+        <v>2.11</v>
       </c>
       <c r="H95" t="n">
-        <v>22.76</v>
+        <v>48.37</v>
       </c>
       <c r="I95" s="13" t="inlineStr">
         <is>
@@ -4765,10 +4765,10 @@
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>6.512</v>
+        <v>0.205</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>6.852</v>
+        <v>0.214</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4781,28 +4781,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="E96" s="17" t="n">
-        <v>-0.0131</v>
+        <v>0.355</v>
+      </c>
+      <c r="E96" s="15" t="n">
+        <v>0.029</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>682200</v>
+        <v>1171700</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.22</v>
+        <v>0.31</v>
       </c>
       <c r="H96" t="n">
-        <v>48.4</v>
+        <v>41.09</v>
       </c>
       <c r="I96" s="13" t="inlineStr">
         <is>
@@ -4810,10 +4810,10 @@
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.765</v>
+        <v>0.366</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.747</v>
+        <v>0.385</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4826,39 +4826,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E97" s="17" t="n">
-        <v>-0.0167</v>
+        <v>0.355</v>
+      </c>
+      <c r="E97" s="15" t="n">
+        <v>0.029</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>677800</v>
+        <v>1127000</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.16</v>
+        <v>0.89</v>
       </c>
       <c r="H97" t="n">
-        <v>60.52</v>
-      </c>
-      <c r="I97" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.46</v>
+      </c>
+      <c r="I97" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>1.151</v>
+        <v>0.339</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>1.064</v>
+        <v>0.345</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4871,39 +4871,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>2.51</v>
+        <v>13.02</v>
       </c>
       <c r="E98" s="15" t="n">
-        <v>0.004</v>
+        <v>0.0124</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>666900</v>
+        <v>1103400</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.05</v>
+        <v>0.13</v>
       </c>
       <c r="H98" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="I98" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.74</v>
+      </c>
+      <c r="I98" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>2.464</v>
+        <v>13.053</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>2.351</v>
+        <v>13.587</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4916,39 +4916,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="E99" s="15" t="n">
-        <v>0.005699999999999999</v>
+        <v>1.4</v>
+      </c>
+      <c r="E99" s="10" t="n">
+        <v>-0.021</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>646100</v>
+        <v>1089300</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.06</v>
+        <v>0.39</v>
       </c>
       <c r="H99" t="n">
-        <v>53.16</v>
-      </c>
-      <c r="I99" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.53</v>
+      </c>
+      <c r="I99" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>3.568</v>
+        <v>1.2</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>2.71</v>
+        <v>1.146</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4961,28 +4961,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E100" s="15" t="n">
-        <v>0.0053</v>
+        <v>1.16</v>
+      </c>
+      <c r="E100" s="10" t="n">
+        <v>-0.0333</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>634200</v>
+        <v>1068500</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.09</v>
+        <v>0.25</v>
       </c>
       <c r="H100" t="n">
-        <v>43.29</v>
+        <v>56.1</v>
       </c>
       <c r="I100" s="13" t="inlineStr">
         <is>
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>1.93</v>
+        <v>1.149</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>1.958</v>
+        <v>1.063</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -5006,28 +5006,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>OSK</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>1.63</v>
+        <v>0.5</v>
       </c>
       <c r="E101" s="17" t="n">
-        <v>-0.0181</v>
+        <v>0</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>576300</v>
+        <v>1065900</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.4</v>
+        <v>0.96</v>
       </c>
       <c r="H101" t="n">
-        <v>19.88</v>
+        <v>8.08</v>
       </c>
       <c r="I101" s="13" t="inlineStr">
         <is>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>1.802</v>
+        <v>0.586</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>1.928</v>
+        <v>0.624</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5051,28 +5051,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>JTIASA</t>
+          <t>TALIWRK</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="E102" s="17" t="n">
-        <v>-0.0161</v>
+        <v>0.245</v>
+      </c>
+      <c r="E102" s="10" t="n">
+        <v>-0.0392</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>572400</v>
+        <v>1024100</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.16</v>
+        <v>0.41</v>
       </c>
       <c r="H102" t="n">
-        <v>30.66</v>
+        <v>43.51</v>
       </c>
       <c r="I102" s="13" t="inlineStr">
         <is>
@@ -5080,10 +5080,10 @@
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>0.97</v>
+        <v>0.253</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>1.025</v>
+        <v>0.262</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5096,39 +5096,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>7.91</v>
-      </c>
-      <c r="E103" s="17" t="n">
-        <v>-0.0162</v>
+        <v>0.75</v>
+      </c>
+      <c r="E103" s="10" t="n">
+        <v>-0.0196</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>570700</v>
+        <v>989900</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.14</v>
+        <v>0.32</v>
       </c>
       <c r="H103" t="n">
-        <v>71.03</v>
-      </c>
-      <c r="I103" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.39</v>
+      </c>
+      <c r="I103" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>7.163</v>
+        <v>0.765</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>6.731</v>
+        <v>0.747</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5141,39 +5141,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="E104" s="17" t="n">
-        <v>-0.013</v>
+        <v>0.905</v>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>-0.0109</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>568700</v>
+        <v>964900</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.14</v>
+        <v>0.44</v>
       </c>
       <c r="H104" t="n">
-        <v>69.48</v>
-      </c>
-      <c r="I104" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.18</v>
+      </c>
+      <c r="I104" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>2.658</v>
+        <v>0.923</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>2.016</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5186,28 +5186,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>4.34</v>
+        <v>0.93</v>
       </c>
       <c r="E105" s="15" t="n">
-        <v>0.014</v>
+        <v>0.0054</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>554700</v>
+        <v>950100</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.11</v>
+        <v>0.51</v>
       </c>
       <c r="H105" t="n">
-        <v>32.17</v>
+        <v>32.53</v>
       </c>
       <c r="I105" s="13" t="inlineStr">
         <is>
@@ -5215,10 +5215,10 @@
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>4.504</v>
+        <v>0.966</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>4.855</v>
+        <v>0.995</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5231,39 +5231,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E106" s="17" t="n">
-        <v>-0.008</v>
+        <v>4.54</v>
+      </c>
+      <c r="E106" s="10" t="n">
+        <v>-0.0173</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>540800</v>
+        <v>938300</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="H106" t="n">
-        <v>51.54</v>
-      </c>
-      <c r="I106" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.06</v>
+      </c>
+      <c r="I106" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>0.616</v>
+        <v>4.685</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>0.609</v>
+        <v>4.627</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5276,39 +5276,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E107" s="17" t="n">
-        <v>-0.0189</v>
+        <v>0.555</v>
+      </c>
+      <c r="E107" s="10" t="n">
+        <v>-0.0089</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>538600</v>
+        <v>932900</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.3</v>
+        <v>0.23</v>
       </c>
       <c r="H107" t="n">
-        <v>66.37</v>
-      </c>
-      <c r="I107" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.96</v>
+      </c>
+      <c r="I107" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>0.708</v>
+        <v>0.573</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.583</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5321,28 +5321,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E108" s="15" t="n">
-        <v>0.0068</v>
+        <v>2.85</v>
+      </c>
+      <c r="E108" s="10" t="n">
+        <v>-0.0138</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>533100</v>
+        <v>896100</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.32</v>
+        <v>0.09</v>
       </c>
       <c r="H108" t="n">
-        <v>75.02</v>
+        <v>57.4</v>
       </c>
       <c r="I108" s="16" t="inlineStr">
         <is>
@@ -5350,10 +5350,10 @@
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>0.658</v>
+        <v>2.771</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>0.617</v>
+        <v>2.594</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5366,28 +5366,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E109" s="17" t="n">
-        <v>-0.0177</v>
+        <v>1.9</v>
+      </c>
+      <c r="E109" s="15" t="n">
+        <v>0.0053</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>529700</v>
+        <v>873200</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="H109" t="n">
-        <v>34.11</v>
+        <v>43.29</v>
       </c>
       <c r="I109" s="13" t="inlineStr">
         <is>
@@ -5395,10 +5395,10 @@
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>0.597</v>
+        <v>1.93</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>0.644</v>
+        <v>1.958</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5411,28 +5411,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>2.1</v>
+        <v>3.52</v>
       </c>
       <c r="E110" s="15" t="n">
-        <v>0.0048</v>
+        <v>0.0028</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>520400</v>
+        <v>861200</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H110" t="n">
-        <v>50.56</v>
+        <v>52.92</v>
       </c>
       <c r="I110" s="13" t="inlineStr">
         <is>
@@ -5440,10 +5440,10 @@
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>2.098</v>
+        <v>3.568</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>2.081</v>
+        <v>2.71</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5456,28 +5456,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>0.955</v>
+        <v>1.37</v>
       </c>
       <c r="E111" s="17" t="n">
-        <v>-0.0155</v>
+        <v>0</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>510500</v>
+        <v>844900</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.21</v>
+        <v>0.43</v>
       </c>
       <c r="H111" t="n">
-        <v>23.74</v>
+        <v>53.6</v>
       </c>
       <c r="I111" s="13" t="inlineStr">
         <is>
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>1.052</v>
+        <v>1.369</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>1.125</v>
+        <v>1.336</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5501,28 +5501,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E112" s="17" t="n">
-        <v>-0.008800000000000001</v>
+        <v>4.34</v>
+      </c>
+      <c r="E112" s="15" t="n">
+        <v>0.014</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>504400</v>
+        <v>844000</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="H112" t="n">
-        <v>46.32</v>
+        <v>32.17</v>
       </c>
       <c r="I112" s="13" t="inlineStr">
         <is>
@@ -5530,16 +5530,1456 @@
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>1.148</v>
+        <v>4.504</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>1.166</v>
+        <v>4.855</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
     </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>5285</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>SDG</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="E113" s="10" t="n">
+        <v>-0.0182</v>
+      </c>
+      <c r="F113" s="11" t="n">
+        <v>831100</v>
+      </c>
+      <c r="G113" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H113" t="n">
+        <v>33.32</v>
+      </c>
+      <c r="I113" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J113" s="9" t="n">
+        <v>6.168</v>
+      </c>
+      <c r="K113" s="9" t="n">
+        <v>6.406</v>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" s="14" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>5053</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>OSK</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="E114" s="10" t="n">
+        <v>-0.0241</v>
+      </c>
+      <c r="F114" s="11" t="n">
+        <v>823100</v>
+      </c>
+      <c r="G114" s="12" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H114" t="n">
+        <v>19.34</v>
+      </c>
+      <c r="I114" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J114" s="9" t="n">
+        <v>1.801</v>
+      </c>
+      <c r="K114" s="9" t="n">
+        <v>1.928</v>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" s="14" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>0318</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>ELRIDGE</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E115" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="11" t="n">
+        <v>820000</v>
+      </c>
+      <c r="G115" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H115" t="n">
+        <v>63.98</v>
+      </c>
+      <c r="I115" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J115" s="9" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="K115" s="9" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" s="14" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>0296</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>HEGROUP</t>
+        </is>
+      </c>
+      <c r="D116" s="9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E116" s="10" t="n">
+        <v>-0.0256</v>
+      </c>
+      <c r="F116" s="11" t="n">
+        <v>786600</v>
+      </c>
+      <c r="G116" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H116" t="n">
+        <v>71.20999999999999</v>
+      </c>
+      <c r="I116" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J116" s="9" t="n">
+        <v>1.051</v>
+      </c>
+      <c r="K116" s="9" t="n">
+        <v>0.886</v>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" s="14" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>5356</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>STRATUS</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E117" s="10" t="n">
+        <v>-0.0291</v>
+      </c>
+      <c r="F117" s="11" t="n">
+        <v>770700</v>
+      </c>
+      <c r="G117" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H117" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="I117" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J117" s="9" t="n">
+        <v>2.984</v>
+      </c>
+      <c r="K117" s="9" t="n">
+        <v>2.822</v>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" s="14" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>5292</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>UWC</t>
+        </is>
+      </c>
+      <c r="D118" s="9" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="E118" s="10" t="n">
+        <v>-0.0236</v>
+      </c>
+      <c r="F118" s="11" t="n">
+        <v>757900</v>
+      </c>
+      <c r="G118" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H118" t="n">
+        <v>69.18000000000001</v>
+      </c>
+      <c r="I118" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J118" s="9" t="n">
+        <v>7.157</v>
+      </c>
+      <c r="K118" s="9" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" s="14" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>8869</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>PMETAL</t>
+        </is>
+      </c>
+      <c r="D119" s="9" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="E119" s="10" t="n">
+        <v>-0.0097</v>
+      </c>
+      <c r="F119" s="11" t="n">
+        <v>756800</v>
+      </c>
+      <c r="G119" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H119" t="n">
+        <v>29.53</v>
+      </c>
+      <c r="I119" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J119" s="9" t="n">
+        <v>7.432</v>
+      </c>
+      <c r="K119" s="9" t="n">
+        <v>7.739</v>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" s="14" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>5357</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>SKYECHIP</t>
+        </is>
+      </c>
+      <c r="D120" s="9" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="E120" s="10" t="n">
+        <v>-0.0168</v>
+      </c>
+      <c r="F120" s="11" t="n">
+        <v>748700</v>
+      </c>
+      <c r="G120" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H120" t="n">
+        <v>44.84</v>
+      </c>
+      <c r="I120" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J120" s="9" t="n">
+        <v>2.979</v>
+      </c>
+      <c r="K120" s="9" t="n">
+        <v>3.037</v>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" s="14" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>7134</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>PWF</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E121" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="11" t="n">
+        <v>719200</v>
+      </c>
+      <c r="G121" s="12" t="n">
+        <v>34.19</v>
+      </c>
+      <c r="H121" t="n">
+        <v>49.91</v>
+      </c>
+      <c r="I121" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J121" s="9" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="K121" s="9" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" s="14" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>0146</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>JFTECH</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E122" s="10" t="n">
+        <v>-0.0314</v>
+      </c>
+      <c r="F122" s="11" t="n">
+        <v>706300</v>
+      </c>
+      <c r="G122" s="12" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H122" t="n">
+        <v>63.96</v>
+      </c>
+      <c r="I122" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J122" s="9" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="K122" s="9" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" s="14" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>7252</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>TEOSENG</t>
+        </is>
+      </c>
+      <c r="D123" s="9" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E123" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="11" t="n">
+        <v>704100</v>
+      </c>
+      <c r="G123" s="12" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="H123" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="I123" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J123" s="9" t="n">
+        <v>0.821</v>
+      </c>
+      <c r="K123" s="9" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" s="14" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>4197</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>SIME</t>
+        </is>
+      </c>
+      <c r="D124" s="9" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="E124" s="15" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="F124" s="11" t="n">
+        <v>701300</v>
+      </c>
+      <c r="G124" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H124" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="I124" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J124" s="9" t="n">
+        <v>2.464</v>
+      </c>
+      <c r="K124" s="9" t="n">
+        <v>2.351</v>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" s="14" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>SLVEST</t>
+        </is>
+      </c>
+      <c r="D125" s="9" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="E125" s="10" t="n">
+        <v>-0.0071</v>
+      </c>
+      <c r="F125" s="11" t="n">
+        <v>692600</v>
+      </c>
+      <c r="G125" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H125" t="n">
+        <v>63.76</v>
+      </c>
+      <c r="I125" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J125" s="9" t="n">
+        <v>3.939</v>
+      </c>
+      <c r="K125" s="9" t="n">
+        <v>3.421</v>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" s="14" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>0223</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>SAMAIDEN</t>
+        </is>
+      </c>
+      <c r="D126" s="9" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="E126" s="10" t="n">
+        <v>-0.0098</v>
+      </c>
+      <c r="F126" s="11" t="n">
+        <v>671600</v>
+      </c>
+      <c r="G126" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H126" t="n">
+        <v>69.97</v>
+      </c>
+      <c r="I126" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J126" s="9" t="n">
+        <v>2.659</v>
+      </c>
+      <c r="K126" s="9" t="n">
+        <v>2.016</v>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" s="14" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>5555</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>SUNMED</t>
+        </is>
+      </c>
+      <c r="D127" s="9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E127" s="15" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="F127" s="11" t="n">
+        <v>648900</v>
+      </c>
+      <c r="G127" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H127" t="n">
+        <v>50.56</v>
+      </c>
+      <c r="I127" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J127" s="9" t="n">
+        <v>2.098</v>
+      </c>
+      <c r="K127" s="9" t="n">
+        <v>2.081</v>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" s="14" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>6971</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>KOBAY</t>
+        </is>
+      </c>
+      <c r="D128" s="9" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="E128" s="15" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="F128" s="11" t="n">
+        <v>639000</v>
+      </c>
+      <c r="G128" s="12" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H128" t="n">
+        <v>41.04</v>
+      </c>
+      <c r="I128" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J128" s="9" t="n">
+        <v>2.231</v>
+      </c>
+      <c r="K128" s="9" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" s="14" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>5352</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>MTTSL</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="E129" s="10" t="n">
+        <v>-0.008800000000000001</v>
+      </c>
+      <c r="F129" s="11" t="n">
+        <v>625100</v>
+      </c>
+      <c r="G129" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H129" t="n">
+        <v>46.32</v>
+      </c>
+      <c r="I129" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J129" s="9" t="n">
+        <v>1.148</v>
+      </c>
+      <c r="K129" s="9" t="n">
+        <v>1.166</v>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" s="14" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>4383</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>JTIASA</t>
+        </is>
+      </c>
+      <c r="D130" s="9" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E130" s="10" t="n">
+        <v>-0.0108</v>
+      </c>
+      <c r="F130" s="11" t="n">
+        <v>616400</v>
+      </c>
+      <c r="G130" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H130" t="n">
+        <v>31.51</v>
+      </c>
+      <c r="I130" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J130" s="9" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="K130" s="9" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" s="14" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>5296</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>MRDIY</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E131" s="10" t="n">
+        <v>-0.008100000000000001</v>
+      </c>
+      <c r="F131" s="11" t="n">
+        <v>615300</v>
+      </c>
+      <c r="G131" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H131" t="n">
+        <v>29.72</v>
+      </c>
+      <c r="I131" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J131" s="9" t="n">
+        <v>1.287</v>
+      </c>
+      <c r="K131" s="9" t="n">
+        <v>1.389</v>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" s="14" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>PCHEM</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="E132" s="10" t="n">
+        <v>-0.0118</v>
+      </c>
+      <c r="F132" s="11" t="n">
+        <v>611600</v>
+      </c>
+      <c r="G132" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H132" t="n">
+        <v>41.35</v>
+      </c>
+      <c r="I132" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J132" s="9" t="n">
+        <v>4.373</v>
+      </c>
+      <c r="K132" s="9" t="n">
+        <v>4.461</v>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" s="14" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D133" s="9" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="E133" s="10" t="n">
+        <v>-0.0265</v>
+      </c>
+      <c r="F133" s="11" t="n">
+        <v>610000</v>
+      </c>
+      <c r="G133" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H133" t="n">
+        <v>68.17</v>
+      </c>
+      <c r="I133" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J133" s="9" t="n">
+        <v>2.986</v>
+      </c>
+      <c r="K133" s="9" t="n">
+        <v>2.795</v>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" s="14" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>5301</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>CTOS</t>
+        </is>
+      </c>
+      <c r="D134" s="9" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="E134" s="10" t="n">
+        <v>-0.0177</v>
+      </c>
+      <c r="F134" s="11" t="n">
+        <v>609100</v>
+      </c>
+      <c r="G134" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H134" t="n">
+        <v>34.11</v>
+      </c>
+      <c r="I134" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J134" s="9" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="K134" s="9" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" s="14" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>7081</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="D135" s="9" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="E135" s="10" t="n">
+        <v>-0.0103</v>
+      </c>
+      <c r="F135" s="11" t="n">
+        <v>606700</v>
+      </c>
+      <c r="G135" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H135" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="I135" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J135" s="9" t="n">
+        <v>1.053</v>
+      </c>
+      <c r="K135" s="9" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" s="14" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>5142</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>WASCO</t>
+        </is>
+      </c>
+      <c r="D136" s="9" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E136" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" s="11" t="n">
+        <v>597500</v>
+      </c>
+      <c r="G136" s="12" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H136" t="n">
+        <v>58.59</v>
+      </c>
+      <c r="I136" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J136" s="9" t="n">
+        <v>0.734</v>
+      </c>
+      <c r="K136" s="9" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" s="14" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>0372</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>CHEEDING</t>
+        </is>
+      </c>
+      <c r="D137" s="9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E137" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" s="11" t="n">
+        <v>580800</v>
+      </c>
+      <c r="G137" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H137" t="n">
+        <v>52.82</v>
+      </c>
+      <c r="I137" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J137" s="9" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="K137" s="9" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" s="14" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>PENTA</t>
+        </is>
+      </c>
+      <c r="D138" s="9" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="E138" s="10" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="F138" s="11" t="n">
+        <v>577600</v>
+      </c>
+      <c r="G138" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H138" t="n">
+        <v>64.73</v>
+      </c>
+      <c r="I138" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J138" s="9" t="n">
+        <v>5.439</v>
+      </c>
+      <c r="K138" s="9" t="n">
+        <v>5.348</v>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" s="14" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>5306</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>FFB</t>
+        </is>
+      </c>
+      <c r="D139" s="9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="E139" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" s="11" t="n">
+        <v>536300</v>
+      </c>
+      <c r="G139" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H139" t="n">
+        <v>22.45</v>
+      </c>
+      <c r="I139" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J139" s="9" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="K139" s="9" t="n">
+        <v>2.022</v>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" s="14" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>CPETECH</t>
+        </is>
+      </c>
+      <c r="D140" s="9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="E140" s="15" t="n">
+        <v>0.0143</v>
+      </c>
+      <c r="F140" s="11" t="n">
+        <v>530000</v>
+      </c>
+      <c r="G140" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H140" t="n">
+        <v>65.23999999999999</v>
+      </c>
+      <c r="I140" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J140" s="9" t="n">
+        <v>1.297</v>
+      </c>
+      <c r="K140" s="9" t="n">
+        <v>1.193</v>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" s="14" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>6888</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>AXIATA</t>
+        </is>
+      </c>
+      <c r="D141" s="9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="E141" s="10" t="n">
+        <v>-0.0123</v>
+      </c>
+      <c r="F141" s="11" t="n">
+        <v>517400</v>
+      </c>
+      <c r="G141" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H141" t="n">
+        <v>35</v>
+      </c>
+      <c r="I141" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J141" s="9" t="n">
+        <v>1.676</v>
+      </c>
+      <c r="K141" s="9" t="n">
+        <v>1.791</v>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" s="14" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>0311</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>GOHUB</t>
+        </is>
+      </c>
+      <c r="D142" s="9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E142" s="15" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="F142" s="11" t="n">
+        <v>515400</v>
+      </c>
+      <c r="G142" s="12" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="H142" t="n">
+        <v>55.46</v>
+      </c>
+      <c r="I142" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J142" s="9" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="K142" s="9" t="n">
+        <v>1.156</v>
+      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" s="14" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>5302</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>ATECH</t>
+        </is>
+      </c>
+      <c r="D143" s="9" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E143" s="15" t="n">
+        <v>0.006500000000000001</v>
+      </c>
+      <c r="F143" s="11" t="n">
+        <v>512200</v>
+      </c>
+      <c r="G143" s="12" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H143" t="n">
+        <v>54.32</v>
+      </c>
+      <c r="I143" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J143" s="9" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="K143" s="9" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" s="14" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>5162</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>VSTECS</t>
+        </is>
+      </c>
+      <c r="D144" s="9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="E144" s="10" t="n">
+        <v>-0.0171</v>
+      </c>
+      <c r="F144" s="11" t="n">
+        <v>502700</v>
+      </c>
+      <c r="G144" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H144" t="n">
+        <v>57.63</v>
+      </c>
+      <c r="I144" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J144" s="9" t="n">
+        <v>1.661</v>
+      </c>
+      <c r="K144" s="9" t="n">
+        <v>1.678</v>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M112"/>
+  <autoFilter ref="A1:M144"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-08/bursa-report-2026-10-08.xlsx
+++ b/docs/downloads/2026-10-08/bursa-report-2026-10-08.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-08" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-08'!$A$1:$M$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-08'!$A$1:$M$175</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M144"/>
+  <dimension ref="A1:M175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -572,10 +572,10 @@
         <v>0.0357</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>4023900</v>
+        <v>4131000</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.99</v>
+        <v>1.02</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>55.82</v>
@@ -625,10 +625,10 @@
         <v>-0.0625</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>66238500</v>
+        <v>119015700</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>0.14</v>
+        <v>0.26</v>
       </c>
       <c r="H3" t="n">
         <v>20.64</v>
@@ -655,28 +655,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.87</v>
+        <v>0.34</v>
       </c>
       <c r="E4" s="15" t="n">
-        <v>0.0175</v>
+        <v>0.0462</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>52137400</v>
+        <v>56342500</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.72</v>
+        <v>1.05</v>
       </c>
       <c r="H4" t="n">
-        <v>69.97</v>
+        <v>77.84</v>
       </c>
       <c r="I4" s="16" t="inlineStr">
         <is>
@@ -684,10 +684,10 @@
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.775</v>
+        <v>0.273</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.706</v>
+        <v>0.242</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="14" t="inlineStr"/>
@@ -700,28 +700,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.34</v>
+        <v>0.875</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>0.0462</v>
+        <v>0.0234</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>45783700</v>
+        <v>56194900</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
       <c r="H5" t="n">
-        <v>77.84</v>
+        <v>70.47</v>
       </c>
       <c r="I5" s="16" t="inlineStr">
         <is>
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.273</v>
+        <v>0.775</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.242</v>
+        <v>0.707</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="14" t="inlineStr"/>
@@ -760,10 +760,10 @@
         <v>0.0571</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>37826800</v>
+        <v>38479300</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="H6" t="n">
         <v>62.96</v>
@@ -799,19 +799,19 @@
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>0.043</v>
+        <v>0.0323</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>28464900</v>
+        <v>33198400</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="H7" t="n">
-        <v>67.67</v>
+        <v>66.48999999999999</v>
       </c>
       <c r="I7" s="16" t="inlineStr">
         <is>
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>1.79</v>
+        <v>1.788</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>1.633</v>
+        <v>1.632</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -850,7 +850,7 @@
         <v>0.0169</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>18559100</v>
+        <v>18561300</v>
       </c>
       <c r="G8" s="12" t="n">
         <v>0.73</v>
@@ -880,28 +880,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E9" s="15" t="n">
-        <v>0.0127</v>
+        <v>0.44</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>-0.0112</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>15271800</v>
+        <v>16132300</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.36</v>
+        <v>0.62</v>
       </c>
       <c r="H9" t="n">
-        <v>73.34999999999999</v>
+        <v>62.69</v>
       </c>
       <c r="I9" s="16" t="inlineStr">
         <is>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.356</v>
+        <v>0.407</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.234</v>
+        <v>0.345</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -925,28 +925,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.445</v>
+        <v>0.395</v>
       </c>
       <c r="E10" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>14164300</v>
+        <v>15644000</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.55</v>
+        <v>0.37</v>
       </c>
       <c r="H10" t="n">
-        <v>64.36</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="I10" s="16" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.407</v>
+        <v>0.355</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.345</v>
+        <v>0.234</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -985,10 +985,10 @@
         <v>0.0337</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>11891200</v>
+        <v>12636000</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="H11" t="n">
         <v>62.6</v>
@@ -1030,10 +1030,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>10234200</v>
+        <v>11858900</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="H12" t="n">
         <v>61.53</v>
@@ -1060,39 +1060,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E13" s="15" t="n">
-        <v>0.019</v>
+        <v>0.155</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>9947100</v>
+        <v>10850800</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>1.41</v>
+        <v>0.36</v>
       </c>
       <c r="H13" t="n">
-        <v>55.08</v>
-      </c>
-      <c r="I13" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.33</v>
+      </c>
+      <c r="I13" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.521</v>
+        <v>0.156</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.53</v>
+        <v>0.157</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1105,40 +1105,33 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>SLGC Berhad</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="E14" s="15" t="n">
-        <v>0.009300000000000001</v>
+        <v>0.25</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>-0.0196</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>7304300</v>
+        <v>10252500</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H14" t="n">
-        <v>52.01</v>
+        <v>0.17</v>
       </c>
       <c r="I14" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J14" s="9" t="n">
-        <v>1.073</v>
-      </c>
-      <c r="K14" s="9" t="n">
-        <v>1.035</v>
-      </c>
+      <c r="J14" s="9" t="n"/>
+      <c r="K14" s="9" t="n"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
     </row>
@@ -1150,39 +1143,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.965</v>
+        <v>0.535</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>0.184</v>
+        <v>0.019</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>7263200</v>
+        <v>10224500</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>2.62</v>
+        <v>1.45</v>
       </c>
       <c r="H15" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.08</v>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.62</v>
+        <v>0.521</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.469</v>
+        <v>0.53</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1195,33 +1188,40 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SLGC Berhad</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.25</v>
+        <v>0.195</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>-0.0196</v>
+        <v>-0.025</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>7011500</v>
+        <v>9648600</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J16" s="9" t="n"/>
-      <c r="K16" s="9" t="n"/>
+        <v>0.4</v>
+      </c>
+      <c r="H16" t="n">
+        <v>50.82</v>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="K16" s="9" t="n">
+        <v>0.183</v>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
     </row>
@@ -1233,28 +1233,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>4.94</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>-0.0276</v>
+        <v>0.78</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>6373600</v>
+        <v>9450200</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.25</v>
+        <v>0.65</v>
       </c>
       <c r="H17" t="n">
-        <v>55.14</v>
+        <v>53.15</v>
       </c>
       <c r="I17" s="16" t="inlineStr">
         <is>
@@ -1262,10 +1262,10 @@
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>4.908</v>
+        <v>0.776</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>4.644</v>
+        <v>0.776</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1278,28 +1278,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="E18" s="17" t="n">
-        <v>0</v>
+        <v>4.93</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>-0.0295</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>6026200</v>
+        <v>8733300</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="H18" t="n">
-        <v>57.61</v>
+        <v>54.56</v>
       </c>
       <c r="I18" s="16" t="inlineStr">
         <is>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.305</v>
+        <v>4.907</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.295</v>
+        <v>4.644</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1323,28 +1323,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SYSTECH</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E19" s="15" t="n">
-        <v>0.0857</v>
+        <v>0.31</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>5829100</v>
+        <v>8626800</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>1.15</v>
+        <v>0.45</v>
       </c>
       <c r="H19" t="n">
-        <v>67.62</v>
+        <v>57.61</v>
       </c>
       <c r="I19" s="16" t="inlineStr">
         <is>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.165</v>
+        <v>0.305</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.165</v>
+        <v>0.295</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1368,28 +1368,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E20" s="17" t="n">
-        <v>0</v>
+        <v>0.99</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>0.2147</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>5639800</v>
+        <v>7792800</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.39</v>
+        <v>2.81</v>
       </c>
       <c r="H20" t="n">
-        <v>53.15</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="I20" s="16" t="inlineStr">
         <is>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.776</v>
+        <v>0.622</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.776</v>
+        <v>0.469</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1413,28 +1413,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>0.0261</v>
+        <v>0.009300000000000001</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>5450100</v>
+        <v>7543800</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.48</v>
+        <v>0.53</v>
       </c>
       <c r="H21" t="n">
-        <v>52.79</v>
+        <v>52.01</v>
       </c>
       <c r="I21" s="16" t="inlineStr">
         <is>
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>1.165</v>
+        <v>1.073</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>1.12</v>
+        <v>1.035</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1458,28 +1458,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0131</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DFX</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.14</v>
+        <v>2.72</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>-0.0345</v>
+        <v>-0.0216</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>5344600</v>
+        <v>7327600</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.71</v>
+        <v>0.43</v>
       </c>
       <c r="H22" t="n">
-        <v>70.08</v>
+        <v>59.7</v>
       </c>
       <c r="I22" s="16" t="inlineStr">
         <is>
@@ -1487,10 +1487,10 @@
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.113</v>
+        <v>2.609</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.093</v>
+        <v>2.5</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1503,39 +1503,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E23" s="17" t="n">
-        <v>0</v>
+        <v>0.795</v>
+      </c>
+      <c r="E23" s="15" t="n">
+        <v>0.08160000000000001</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>5289000</v>
+        <v>7316700</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.47</v>
+        <v>4.43</v>
       </c>
       <c r="H23" t="n">
-        <v>38.38</v>
-      </c>
-      <c r="I23" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>80.48999999999999</v>
+      </c>
+      <c r="I23" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.403</v>
+        <v>0.664</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.41</v>
+        <v>0.618</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1548,40 +1548,33 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>EVOCOM</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.535</v>
+        <v>0.115</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>0.049</v>
+        <v>0.09519999999999999</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>5146200</v>
+        <v>7053700</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="H24" t="n">
-        <v>69.7</v>
-      </c>
-      <c r="I24" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J24" s="9" t="n">
-        <v>0.469</v>
-      </c>
-      <c r="K24" s="9" t="n">
-        <v>0.449</v>
-      </c>
+        <v>0.4</v>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="n"/>
+      <c r="K24" s="9" t="n"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
     </row>
@@ -1593,39 +1586,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>SYSTECH</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>7.19</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>-0.0191</v>
+        <v>0.19</v>
+      </c>
+      <c r="E25" s="15" t="n">
+        <v>0.0857</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>4947100</v>
+        <v>6515900</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.37</v>
+        <v>1.28</v>
       </c>
       <c r="H25" t="n">
-        <v>29.57</v>
-      </c>
-      <c r="I25" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.62</v>
+      </c>
+      <c r="I25" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>7.674</v>
+        <v>0.165</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>7.741</v>
+        <v>0.165</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1638,28 +1631,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>6399</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>ASTRO</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>4.58</v>
+        <v>0.055</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>-0.0022</v>
+        <v>-0.0833</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>4665200</v>
+        <v>6361300</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.29</v>
+        <v>2.5</v>
       </c>
       <c r="H26" t="n">
-        <v>27.42</v>
+        <v>44.04</v>
       </c>
       <c r="I26" s="13" t="inlineStr">
         <is>
@@ -1667,10 +1660,10 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>4.739</v>
+        <v>0.058</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>4.896</v>
+        <v>0.06</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1683,28 +1676,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E27" s="15" t="n">
-        <v>0.0145</v>
+        <v>0.625</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>-0.031</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>4584600</v>
+        <v>6089400</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.58</v>
+        <v>0.31</v>
       </c>
       <c r="H27" t="n">
-        <v>56.39</v>
+        <v>62.14</v>
       </c>
       <c r="I27" s="16" t="inlineStr">
         <is>
@@ -1712,10 +1705,10 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.343</v>
+        <v>0.576</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.324</v>
+        <v>0.516</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1728,39 +1721,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E28" s="15" t="n">
-        <v>0.0115</v>
+        <v>4.58</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>-0.0022</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>4487700</v>
+        <v>6068900</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="H28" t="n">
-        <v>48.53</v>
-      </c>
-      <c r="I28" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.42</v>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.451</v>
+        <v>4.739</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.425</v>
+        <v>4.896</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1773,39 +1766,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E29" s="15" t="n">
-        <v>0.0152</v>
+        <v>7.19</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>-0.0191</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>4369600</v>
+        <v>5945800</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>1.04</v>
+        <v>0.44</v>
       </c>
       <c r="H29" t="n">
-        <v>88.56999999999999</v>
-      </c>
-      <c r="I29" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.57</v>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.502</v>
+        <v>7.674</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.438</v>
+        <v>7.741</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1818,28 +1811,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>TUNEPRO</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.265</v>
+        <v>0.54</v>
       </c>
       <c r="E30" s="15" t="n">
-        <v>0.0392</v>
+        <v>0.0588</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>4359000</v>
+        <v>5895300</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>5.18</v>
+        <v>1.49</v>
       </c>
       <c r="H30" t="n">
-        <v>60.23</v>
+        <v>70.44</v>
       </c>
       <c r="I30" s="16" t="inlineStr">
         <is>
@@ -1847,10 +1840,10 @@
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.25</v>
+        <v>0.469</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.259</v>
+        <v>0.45</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1863,28 +1856,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>-0.0036</v>
+        <v>1.2</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>0.0435</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>4249400</v>
+        <v>5728900</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.25</v>
+        <v>0.51</v>
       </c>
       <c r="H31" t="n">
-        <v>64</v>
+        <v>54.81</v>
       </c>
       <c r="I31" s="16" t="inlineStr">
         <is>
@@ -1892,10 +1885,10 @@
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>2.613</v>
+        <v>1.167</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>2.501</v>
+        <v>1.12</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1908,39 +1901,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E32" s="10" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3999500</v>
+        <v>5714700</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.22</v>
+        <v>0.36</v>
       </c>
       <c r="H32" t="n">
-        <v>46.72</v>
-      </c>
-      <c r="I32" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.2</v>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.868</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.869</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1953,39 +1946,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0131</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>DFX</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>7.17</v>
+        <v>0.14</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>-0.011</v>
+        <v>-0.0345</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>3997400</v>
+        <v>5657500</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.42</v>
+        <v>0.75</v>
       </c>
       <c r="H33" t="n">
-        <v>19.36</v>
-      </c>
-      <c r="I33" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.08</v>
+      </c>
+      <c r="I33" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>7.648</v>
+        <v>0.113</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>8.119999999999999</v>
+        <v>0.093</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1998,39 +1991,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E34" s="15" t="n">
-        <v>0.0222</v>
+        <v>0.43</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>-0.0115</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>3962900</v>
+        <v>5475100</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.15</v>
+        <v>0.53</v>
       </c>
       <c r="H34" t="n">
-        <v>34.28</v>
-      </c>
-      <c r="I34" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.13</v>
+      </c>
+      <c r="I34" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.252</v>
+        <v>0.45</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.305</v>
+        <v>0.425</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2043,39 +2036,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>9.84</v>
+        <v>0.865</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>-0.003</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>3746300</v>
+        <v>5467500</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="H35" t="n">
-        <v>31.69</v>
-      </c>
-      <c r="I35" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.72</v>
+      </c>
+      <c r="I35" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>10.047</v>
+        <v>0.868</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>10.219</v>
+        <v>0.869</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2088,28 +2081,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="E36" s="10" t="n">
-        <v>-0.025</v>
+        <v>0.395</v>
+      </c>
+      <c r="E36" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>3722800</v>
+        <v>5319000</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.16</v>
+        <v>0.47</v>
       </c>
       <c r="H36" t="n">
-        <v>50.82</v>
+        <v>38.38</v>
       </c>
       <c r="I36" s="13" t="inlineStr">
         <is>
@@ -2117,10 +2110,10 @@
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.196</v>
+        <v>0.403</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.183</v>
+        <v>0.41</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2133,39 +2126,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.345</v>
       </c>
       <c r="E37" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>3669700</v>
+        <v>5114100</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.23</v>
+        <v>0.65</v>
       </c>
       <c r="H37" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="I37" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.32</v>
+      </c>
+      <c r="I37" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.342</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.324</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2178,33 +2171,40 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0473</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>EVOCOM</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="E38" s="17" t="n">
-        <v>0</v>
+        <v>7.18</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>-0.0097</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>3592900</v>
+        <v>5003800</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.2</v>
+        <v>0.53</v>
+      </c>
+      <c r="H38" t="n">
+        <v>19.55</v>
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J38" s="9" t="n"/>
-      <c r="K38" s="9" t="n"/>
+      <c r="J38" s="9" t="n">
+        <v>7.649</v>
+      </c>
+      <c r="K38" s="9" t="n">
+        <v>8.121</v>
+      </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
     </row>
@@ -2216,39 +2216,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0209</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AIMFLEX</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.105</v>
+        <v>0.65</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>-0.0455</v>
+        <v>-0.0152</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>3496300</v>
+        <v>4906100</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.51</v>
+        <v>1.17</v>
       </c>
       <c r="H39" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="I39" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>84.78</v>
+      </c>
+      <c r="I39" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.115</v>
+        <v>0.5</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.123</v>
+        <v>0.438</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2261,28 +2261,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>2.13</v>
+        <v>9.83</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>-0.009300000000000001</v>
+        <v>-0.004099999999999999</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>3386800</v>
+        <v>4563600</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.23</v>
+        <v>0.37</v>
       </c>
       <c r="H40" t="n">
-        <v>39.95</v>
+        <v>31.26</v>
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
@@ -2290,10 +2290,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>2.235</v>
+        <v>10.046</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>2.227</v>
+        <v>10.219</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2306,28 +2306,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>TUNEPRO</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E41" s="17" t="n">
-        <v>0</v>
+        <v>0.265</v>
+      </c>
+      <c r="E41" s="15" t="n">
+        <v>0.0392</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>3303400</v>
+        <v>4390100</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.31</v>
+        <v>5.21</v>
       </c>
       <c r="H41" t="n">
-        <v>55.75</v>
+        <v>60.23</v>
       </c>
       <c r="I41" s="16" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.61</v>
+        <v>0.25</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.611</v>
+        <v>0.259</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2351,39 +2351,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E42" s="17" t="n">
-        <v>0</v>
+        <v>2.13</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>3165000</v>
+        <v>4287900</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.29</v>
       </c>
       <c r="H42" t="n">
-        <v>47.06</v>
-      </c>
-      <c r="I42" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.95</v>
+      </c>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.208</v>
+        <v>2.235</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.209</v>
+        <v>2.227</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2396,28 +2396,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>-0.0182</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>3013400</v>
+        <v>4238500</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.44</v>
+        <v>1.16</v>
       </c>
       <c r="H43" t="n">
-        <v>69.41</v>
+        <v>55.55</v>
       </c>
       <c r="I43" s="16" t="inlineStr">
         <is>
@@ -2425,10 +2425,10 @@
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.732</v>
+        <v>0.631</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.649</v>
+        <v>0.6</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2441,39 +2441,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E44" s="17" t="n">
-        <v>0</v>
+        <v>0.23</v>
+      </c>
+      <c r="E44" s="15" t="n">
+        <v>0.0222</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>2847000</v>
+        <v>4185300</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.78</v>
+        <v>0.16</v>
       </c>
       <c r="H44" t="n">
-        <v>57.53</v>
-      </c>
-      <c r="I44" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.28</v>
+      </c>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.632</v>
+        <v>0.252</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.601</v>
+        <v>0.305</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2486,39 +2486,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E45" s="15" t="n">
-        <v>0.068</v>
+        <v>5.53</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>-0.016</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>2832200</v>
+        <v>4023900</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>1.72</v>
+        <v>0.28</v>
       </c>
       <c r="H45" t="n">
-        <v>79.68000000000001</v>
-      </c>
-      <c r="I45" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.25</v>
+      </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.663</v>
+        <v>5.644</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.618</v>
+        <v>5.332</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2531,28 +2531,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>-0.0167</v>
+        <v>0.65</v>
+      </c>
+      <c r="E46" s="15" t="n">
+        <v>0.007800000000000001</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>2727600</v>
+        <v>3823100</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.2</v>
+        <v>1.05</v>
       </c>
       <c r="H46" t="n">
-        <v>52.62</v>
+        <v>66.64</v>
       </c>
       <c r="I46" s="16" t="inlineStr">
         <is>
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.291</v>
+        <v>0.593</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.28</v>
+        <v>0.581</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2576,39 +2576,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0209</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>AIMFLEX</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E47" s="15" t="n">
-        <v>0.0064</v>
+        <v>0.105</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>-0.0455</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>2697000</v>
+        <v>3559300</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.34</v>
+        <v>0.52</v>
       </c>
       <c r="H47" t="n">
-        <v>52.99</v>
-      </c>
-      <c r="I47" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.5</v>
+      </c>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.777</v>
+        <v>0.115</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.772</v>
+        <v>0.123</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2621,39 +2621,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E48" s="17" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>-0.0182</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>2689300</v>
+        <v>3475400</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H48" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="I48" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.41</v>
+      </c>
+      <c r="I48" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.367</v>
+        <v>0.732</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.368</v>
+        <v>0.649</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2666,28 +2666,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.65</v>
+        <v>1.18</v>
       </c>
       <c r="E49" s="15" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.0172</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>2683500</v>
+        <v>3419000</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.73</v>
+        <v>1.06</v>
       </c>
       <c r="H49" t="n">
-        <v>66.64</v>
+        <v>73.17</v>
       </c>
       <c r="I49" s="16" t="inlineStr">
         <is>
@@ -2695,10 +2695,10 @@
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.593</v>
+        <v>0.999</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.581</v>
+        <v>0.852</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2711,39 +2711,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="E50" s="10" t="n">
-        <v>-0.009399999999999999</v>
+        <v>0.205</v>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>2564600</v>
+        <v>3404700</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.16</v>
+        <v>0.74</v>
       </c>
       <c r="H50" t="n">
-        <v>56.36</v>
-      </c>
-      <c r="I50" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.06</v>
+      </c>
+      <c r="I50" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.512</v>
+        <v>0.208</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.436</v>
+        <v>0.209</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2756,28 +2756,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E51" s="10" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.62</v>
+      </c>
+      <c r="E51" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>2506400</v>
+        <v>3303400</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.13</v>
+        <v>0.31</v>
       </c>
       <c r="H51" t="n">
-        <v>65.56999999999999</v>
+        <v>55.75</v>
       </c>
       <c r="I51" s="16" t="inlineStr">
         <is>
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.577</v>
+        <v>0.61</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.516</v>
+        <v>0.611</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2801,28 +2801,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>5.54</v>
-      </c>
-      <c r="E52" s="10" t="n">
-        <v>-0.0142</v>
+        <v>0.37</v>
+      </c>
+      <c r="E52" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>2400600</v>
+        <v>3198300</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.17</v>
+        <v>0.47</v>
       </c>
       <c r="H52" t="n">
-        <v>47.65</v>
+        <v>53.6</v>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>5.645</v>
+        <v>0.367</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>5.332</v>
+        <v>0.368</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2846,39 +2846,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ITMAX</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>4.63</v>
+        <v>0.15</v>
       </c>
       <c r="E53" s="10" t="n">
-        <v>-0.0128</v>
+        <v>-0.0323</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>2260600</v>
+        <v>3076900</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>1.06</v>
+        <v>0.1</v>
       </c>
       <c r="H53" t="n">
-        <v>58.34</v>
-      </c>
-      <c r="I53" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.12</v>
+      </c>
+      <c r="I53" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>4.538</v>
+        <v>0.157</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>4.489</v>
+        <v>0.147</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2891,28 +2891,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E54" s="17" t="n">
-        <v>0</v>
+        <v>0.515</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>-0.0283</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>2178800</v>
+        <v>2975600</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.06</v>
+        <v>0.18</v>
       </c>
       <c r="H54" t="n">
-        <v>26.61</v>
+        <v>54.15</v>
       </c>
       <c r="I54" s="13" t="inlineStr">
         <is>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.556</v>
+        <v>0.511</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.755</v>
+        <v>0.436</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2936,28 +2936,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.345</v>
+        <v>0.785</v>
       </c>
       <c r="E55" s="15" t="n">
-        <v>0.0147</v>
+        <v>0.0064</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>2103400</v>
+        <v>2866200</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="H55" t="n">
-        <v>60.08</v>
+        <v>52.99</v>
       </c>
       <c r="I55" s="16" t="inlineStr">
         <is>
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.326</v>
+        <v>0.777</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.339</v>
+        <v>0.772</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2981,39 +2981,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="E56" s="17" t="n">
-        <v>0</v>
+        <v>0.29</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>-0.0333</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>2096600</v>
+        <v>2771200</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H56" t="n">
-        <v>50.11</v>
-      </c>
-      <c r="I56" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.77</v>
+      </c>
+      <c r="I56" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>1.753</v>
+        <v>0.291</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>1.782</v>
+        <v>0.28</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3026,28 +3026,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E57" s="15" t="n">
-        <v>0.0405</v>
+        <v>6</v>
+      </c>
+      <c r="E57" s="10" t="n">
+        <v>-0.0596</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>2059200</v>
+        <v>2709100</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.24</v>
+        <v>0.64</v>
       </c>
       <c r="H57" t="n">
-        <v>69.48999999999999</v>
+        <v>55.3</v>
       </c>
       <c r="I57" s="16" t="inlineStr">
         <is>
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.352</v>
+        <v>5.735</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.319</v>
+        <v>5.775</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3071,39 +3071,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="E58" s="15" t="n">
-        <v>0.0431</v>
+        <v>2.8</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>-0.0175</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>2025500</v>
+        <v>2700700</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="H58" t="n">
-        <v>66.23999999999999</v>
-      </c>
-      <c r="I58" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.65</v>
+      </c>
+      <c r="I58" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>1.066</v>
+        <v>2.793</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.819</v>
+        <v>2.698</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3116,28 +3116,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>6.05</v>
+        <v>0.705</v>
       </c>
       <c r="E59" s="10" t="n">
-        <v>-0.0517</v>
+        <v>-0.0208</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>1999700</v>
+        <v>2689000</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.47</v>
+        <v>0.29</v>
       </c>
       <c r="H59" t="n">
-        <v>56.32</v>
+        <v>61.86</v>
       </c>
       <c r="I59" s="16" t="inlineStr">
         <is>
@@ -3145,10 +3145,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>5.739</v>
+        <v>0.667</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>5.776</v>
+        <v>0.603</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3161,28 +3161,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>GREENTEC</t>
+          <t>BNASTRA</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.345</v>
+        <v>2.71</v>
       </c>
       <c r="E60" s="15" t="n">
-        <v>0.0455</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>1976600</v>
+        <v>2637900</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>2.55</v>
+        <v>2.36</v>
       </c>
       <c r="H60" t="n">
-        <v>94.69</v>
+        <v>86.66</v>
       </c>
       <c r="I60" s="16" t="inlineStr">
         <is>
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.242</v>
+        <v>2.466</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.204</v>
+        <v>2.348</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3206,28 +3206,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="E61" s="17" t="n">
-        <v>0</v>
+        <v>1.09</v>
+      </c>
+      <c r="E61" s="10" t="n">
+        <v>-0.0268</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>1839100</v>
+        <v>2536800</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="H61" t="n">
-        <v>54.63</v>
+        <v>60.11</v>
       </c>
       <c r="I61" s="16" t="inlineStr">
         <is>
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.6889999999999999</v>
+        <v>1.064</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.679</v>
+        <v>0.912</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3251,39 +3251,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E62" s="10" t="n">
-        <v>-0.0169</v>
+        <v>3.43</v>
+      </c>
+      <c r="E62" s="15" t="n">
+        <v>0.0394</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1838600</v>
+        <v>2461800</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="H62" t="n">
-        <v>33.43</v>
-      </c>
-      <c r="I62" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.49</v>
+      </c>
+      <c r="I62" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.295</v>
+        <v>3.485</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.296</v>
+        <v>3.663</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3296,28 +3296,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>7195</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BNASTRA</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>2.71</v>
+        <v>0.38</v>
       </c>
       <c r="E63" s="15" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.027</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>1801700</v>
+        <v>2461400</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>1.61</v>
+        <v>0.28</v>
       </c>
       <c r="H63" t="n">
-        <v>86.66</v>
+        <v>68.08</v>
       </c>
       <c r="I63" s="16" t="inlineStr">
         <is>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>2.466</v>
+        <v>0.351</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>2.348</v>
+        <v>0.319</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3341,28 +3341,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>UNISEM</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="E64" s="17" t="n">
-        <v>0</v>
+        <v>4.28</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>-0.0273</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>1793500</v>
+        <v>2429000</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.25</v>
+        <v>0.82</v>
       </c>
       <c r="H64" t="n">
-        <v>26.21</v>
+        <v>47.22</v>
       </c>
       <c r="I64" s="13" t="inlineStr">
         <is>
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>0.528</v>
+        <v>4.34</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.573</v>
+        <v>4.359</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3386,28 +3386,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E65" s="15" t="n">
-        <v>0.0172</v>
+        <v>0.295</v>
+      </c>
+      <c r="E65" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>1792800</v>
+        <v>2358600</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="H65" t="n">
-        <v>73.17</v>
+        <v>49.23</v>
       </c>
       <c r="I65" s="16" t="inlineStr">
         <is>
@@ -3415,10 +3415,10 @@
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>0.999</v>
+        <v>0.295</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.852</v>
+        <v>0.296</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3431,28 +3431,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>2.81</v>
+        <v>0.97</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>-0.014</v>
+        <v>-0.03</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>1787800</v>
+        <v>2339900</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.13</v>
+        <v>0.29</v>
       </c>
       <c r="H66" t="n">
-        <v>53.57</v>
+        <v>56.08</v>
       </c>
       <c r="I66" s="13" t="inlineStr">
         <is>
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>2.794</v>
+        <v>0.961</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>2.698</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3476,39 +3476,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0148</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SUNZEN</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E67" s="15" t="n">
-        <v>0.0444</v>
+        <v>1.75</v>
+      </c>
+      <c r="E67" s="10" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>1731100</v>
+        <v>2318900</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>7.52</v>
+        <v>0.44</v>
       </c>
       <c r="H67" t="n">
-        <v>65.84</v>
-      </c>
-      <c r="I67" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.61</v>
+      </c>
+      <c r="I67" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.226</v>
+        <v>1.752</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.225</v>
+        <v>1.781</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3521,28 +3521,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E68" s="10" t="n">
-        <v>-0.0089</v>
+        <v>3.13</v>
+      </c>
+      <c r="E68" s="15" t="n">
+        <v>0.0162</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>1730600</v>
+        <v>2305000</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.17</v>
+        <v>0.57</v>
       </c>
       <c r="H68" t="n">
-        <v>64.39</v>
+        <v>39.34</v>
       </c>
       <c r="I68" s="16" t="inlineStr">
         <is>
@@ -3550,10 +3550,10 @@
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>1.065</v>
+        <v>3.193</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.912</v>
+        <v>3.393</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3566,39 +3566,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E69" s="15" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E69" s="10" t="n">
+        <v>-0.024</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1726400</v>
+        <v>2301500</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.47</v>
+        <v>0.35</v>
       </c>
       <c r="H69" t="n">
-        <v>35.53</v>
-      </c>
-      <c r="I69" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.2</v>
+      </c>
+      <c r="I69" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>0.554</v>
+        <v>0.739</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>0.583</v>
+        <v>0.659</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3611,28 +3611,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>ITMAX</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="E70" s="17" t="n">
-        <v>0</v>
+        <v>4.59</v>
+      </c>
+      <c r="E70" s="10" t="n">
+        <v>-0.0213</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>1709600</v>
+        <v>2288000</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.55</v>
+        <v>1.07</v>
       </c>
       <c r="H70" t="n">
-        <v>71.09999999999999</v>
+        <v>55.14</v>
       </c>
       <c r="I70" s="16" t="inlineStr">
         <is>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>2.608</v>
+        <v>4.534</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>2.272</v>
+        <v>4.488</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3656,28 +3656,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.805</v>
+        <v>0.7</v>
       </c>
       <c r="E71" s="10" t="n">
-        <v>-0.0183</v>
+        <v>-0.0071</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1667100</v>
+        <v>2277100</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.12</v>
+        <v>0.29</v>
       </c>
       <c r="H71" t="n">
-        <v>59.45</v>
+        <v>53.39</v>
       </c>
       <c r="I71" s="16" t="inlineStr">
         <is>
@@ -3685,10 +3685,10 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.766</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.711</v>
+        <v>0.678</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3701,39 +3701,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>7943</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>GREENTEC</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>1.36</v>
+        <v>0.315</v>
       </c>
       <c r="E72" s="10" t="n">
-        <v>-0.0423</v>
+        <v>-0.0455</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>1654000</v>
+        <v>2265500</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.51</v>
+        <v>2.92</v>
       </c>
       <c r="H72" t="n">
-        <v>70.73</v>
-      </c>
-      <c r="I72" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>83.75</v>
+      </c>
+      <c r="I72" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>1.222</v>
+        <v>0.239</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0.999</v>
+        <v>0.203</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3746,28 +3746,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E73" s="17" t="n">
-        <v>0</v>
+        <v>2.69</v>
+      </c>
+      <c r="E73" s="10" t="n">
+        <v>-0.0461</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>1642400</v>
+        <v>2246600</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.27</v>
+        <v>0.4</v>
       </c>
       <c r="H73" t="n">
-        <v>70.23</v>
+        <v>56.84</v>
       </c>
       <c r="I73" s="16" t="inlineStr">
         <is>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.783</v>
+        <v>2.622</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.763</v>
+        <v>2.579</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3791,39 +3791,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="E74" s="15" t="n">
-        <v>0.013</v>
+        <v>0.475</v>
+      </c>
+      <c r="E74" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>1619900</v>
+        <v>2243500</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.4</v>
+        <v>0.06</v>
       </c>
       <c r="H74" t="n">
-        <v>38.16</v>
-      </c>
-      <c r="I74" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.61</v>
+      </c>
+      <c r="I74" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>3.192</v>
+        <v>0.556</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>3.393</v>
+        <v>0.755</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3836,39 +3836,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E75" s="15" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.805</v>
+      </c>
+      <c r="E75" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1604900</v>
+        <v>2241800</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.14</v>
+        <v>0.36</v>
       </c>
       <c r="H75" t="n">
-        <v>44.27</v>
-      </c>
-      <c r="I75" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.23</v>
+      </c>
+      <c r="I75" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>1.329</v>
+        <v>0.783</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>1.309</v>
+        <v>0.763</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3881,28 +3881,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="E76" s="15" t="n">
-        <v>0.0424</v>
+        <v>0.49</v>
+      </c>
+      <c r="E76" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1604600</v>
+        <v>2239700</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.26</v>
+        <v>0.31</v>
       </c>
       <c r="H76" t="n">
-        <v>43.32</v>
+        <v>26.21</v>
       </c>
       <c r="I76" s="13" t="inlineStr">
         <is>
@@ -3910,10 +3910,10 @@
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>3.486</v>
+        <v>0.528</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>3.663</v>
+        <v>0.573</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3926,39 +3926,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1.45</v>
+        <v>0.34</v>
       </c>
       <c r="E77" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1603000</v>
+        <v>2203600</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.74</v>
+        <v>0.39</v>
       </c>
       <c r="H77" t="n">
-        <v>28.24</v>
-      </c>
-      <c r="I77" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.95</v>
+      </c>
+      <c r="I77" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>1.509</v>
+        <v>0.326</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>1.623</v>
+        <v>0.339</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3971,28 +3971,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>7173</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>TOYOVEN</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E78" s="17" t="n">
-        <v>0</v>
+        <v>0.22</v>
+      </c>
+      <c r="E78" s="15" t="n">
+        <v>0.1282</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>1585300</v>
+        <v>2185600</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.28</v>
+        <v>15.8</v>
       </c>
       <c r="H78" t="n">
-        <v>70.68000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I78" s="16" t="inlineStr">
         <is>
@@ -4000,10 +4000,10 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.544</v>
+        <v>0.2</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.493</v>
+        <v>0.206</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4016,28 +4016,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E79" s="10" t="n">
-        <v>-0.0139</v>
+        <v>1.2</v>
+      </c>
+      <c r="E79" s="15" t="n">
+        <v>0.0345</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>1568100</v>
+        <v>2162400</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.17</v>
+        <v>0.28</v>
       </c>
       <c r="H79" t="n">
-        <v>63.19</v>
+        <v>65.72</v>
       </c>
       <c r="I79" s="16" t="inlineStr">
         <is>
@@ -4045,10 +4045,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.668</v>
+        <v>1.065</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.603</v>
+        <v>0.819</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4070,19 +4070,19 @@
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="E80" s="10" t="n">
-        <v>-0.0299</v>
+        <v>-0.0373</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>1545100</v>
+        <v>2138700</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.55</v>
+        <v>0.77</v>
       </c>
       <c r="H80" t="n">
-        <v>46.63</v>
+        <v>45.59</v>
       </c>
       <c r="I80" s="13" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>1.348</v>
+        <v>1.347</v>
       </c>
       <c r="K80" s="9" t="n">
         <v>1.231</v>
@@ -4106,39 +4106,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E81" s="10" t="n">
-        <v>-0.0167</v>
+        <v>0.345</v>
+      </c>
+      <c r="E81" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>1527900</v>
+        <v>2110900</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.25</v>
+        <v>0.55</v>
       </c>
       <c r="H81" t="n">
-        <v>59.8</v>
-      </c>
-      <c r="I81" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.93</v>
+      </c>
+      <c r="I81" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>0.288</v>
+        <v>0.365</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0.274</v>
+        <v>0.385</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4151,28 +4151,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0396</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>ADNEX</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="E82" s="10" t="n">
-        <v>-0.039</v>
+        <v>0.46</v>
+      </c>
+      <c r="E82" s="15" t="n">
+        <v>0.0222</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>1498000</v>
+        <v>2043500</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.27</v>
+        <v>3.85</v>
       </c>
       <c r="H82" t="n">
-        <v>58.65</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I82" s="16" t="inlineStr">
         <is>
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>2.624</v>
+        <v>0.43</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>2.579</v>
+        <v>0.42</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4196,39 +4196,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E83" s="17" t="n">
-        <v>0</v>
+        <v>6.1</v>
+      </c>
+      <c r="E83" s="10" t="n">
+        <v>-0.0129</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>1477800</v>
+        <v>2041400</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.15</v>
+        <v>0.47</v>
       </c>
       <c r="H83" t="n">
-        <v>55.35</v>
-      </c>
-      <c r="I83" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>22.76</v>
+      </c>
+      <c r="I83" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.276</v>
+        <v>6.512</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.304</v>
+        <v>6.852</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4241,39 +4241,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.83</v>
+        <v>5.97</v>
       </c>
       <c r="E84" s="10" t="n">
-        <v>-0.006</v>
+        <v>-0.01</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>1458400</v>
+        <v>1995900</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.22</v>
+        <v>0.16</v>
       </c>
       <c r="H84" t="n">
-        <v>73.27</v>
-      </c>
-      <c r="I84" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.19</v>
+      </c>
+      <c r="I84" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>0.741</v>
+        <v>6.173</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0.659</v>
+        <v>6.407</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4286,28 +4286,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>7173</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>TOYOVEN</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.225</v>
+        <v>2.82</v>
       </c>
       <c r="E85" s="15" t="n">
-        <v>0.1538</v>
+        <v>0.0217</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>1362100</v>
+        <v>1972200</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>9.85</v>
+        <v>0.63</v>
       </c>
       <c r="H85" t="n">
-        <v>70.16</v>
+        <v>73.86</v>
       </c>
       <c r="I85" s="16" t="inlineStr">
         <is>
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.201</v>
+        <v>2.614</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.206</v>
+        <v>2.273</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4331,39 +4331,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.475</v>
+        <v>1.36</v>
       </c>
       <c r="E86" s="10" t="n">
-        <v>-0.0104</v>
+        <v>-0.0423</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>1333300</v>
+        <v>1860200</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.4</v>
+        <v>0.57</v>
       </c>
       <c r="H86" t="n">
-        <v>73.43000000000001</v>
-      </c>
-      <c r="I86" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>70.73</v>
+      </c>
+      <c r="I86" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>0.414</v>
+        <v>1.222</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.367</v>
+        <v>0.999</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4376,39 +4376,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E87" s="10" t="n">
-        <v>-0.0227</v>
+        <v>0.355</v>
+      </c>
+      <c r="E87" s="15" t="n">
+        <v>0.029</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1330300</v>
+        <v>1845900</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.59</v>
+        <v>1.45</v>
       </c>
       <c r="H87" t="n">
-        <v>60.08</v>
-      </c>
-      <c r="I87" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.46</v>
+      </c>
+      <c r="I87" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>0.619</v>
+        <v>0.339</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>0.526</v>
+        <v>0.345</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4421,39 +4421,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="E88" s="10" t="n">
-        <v>-0.0275</v>
+        <v>1.29</v>
+      </c>
+      <c r="E88" s="15" t="n">
+        <v>0.007800000000000001</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>1306400</v>
+        <v>1818200</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.42</v>
+        <v>0.15</v>
       </c>
       <c r="H88" t="n">
-        <v>55.12</v>
-      </c>
-      <c r="I88" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.27</v>
+      </c>
+      <c r="I88" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>3.855</v>
+        <v>1.329</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>3.561</v>
+        <v>1.309</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4466,28 +4466,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>EMETALL</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E89" s="17" t="n">
-        <v>0</v>
+        <v>0.535</v>
+      </c>
+      <c r="E89" s="15" t="n">
+        <v>0.009399999999999999</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1275200</v>
+        <v>1798300</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>2.91</v>
+        <v>0.49</v>
       </c>
       <c r="H89" t="n">
-        <v>57.26</v>
+        <v>35.53</v>
       </c>
       <c r="I89" s="13" t="inlineStr">
         <is>
@@ -4495,10 +4495,10 @@
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.44</v>
+        <v>0.554</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0.437</v>
+        <v>0.583</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4511,39 +4511,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.985</v>
+        <v>0.595</v>
       </c>
       <c r="E90" s="10" t="n">
-        <v>-0.015</v>
+        <v>-0.0083</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1259600</v>
+        <v>1797000</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.15</v>
+        <v>0.31</v>
       </c>
       <c r="H90" t="n">
-        <v>58.55</v>
-      </c>
-      <c r="I90" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.73</v>
+      </c>
+      <c r="I90" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.963</v>
+        <v>0.544</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.493</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4556,39 +4556,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>MFLOUR</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E91" s="10" t="n">
-        <v>-0.0167</v>
+        <v>0.29</v>
+      </c>
+      <c r="E91" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1223600</v>
+        <v>1793800</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.55</v>
+        <v>0.18</v>
       </c>
       <c r="H91" t="n">
-        <v>32.88</v>
-      </c>
-      <c r="I91" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.35</v>
+      </c>
+      <c r="I91" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>0.619</v>
+        <v>0.276</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>0.638</v>
+        <v>0.304</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4601,28 +4601,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>6.11</v>
+        <v>0.735</v>
       </c>
       <c r="E92" s="10" t="n">
-        <v>-0.0113</v>
+        <v>-0.0392</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1221600</v>
+        <v>1773700</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.28</v>
+        <v>0.57</v>
       </c>
       <c r="H92" t="n">
-        <v>23</v>
+        <v>44.6</v>
       </c>
       <c r="I92" s="13" t="inlineStr">
         <is>
@@ -4630,10 +4630,10 @@
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>6.513</v>
+        <v>0.763</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>6.853</v>
+        <v>0.747</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4646,39 +4646,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0148</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>SUNZEN</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>1.82</v>
+        <v>0.235</v>
       </c>
       <c r="E93" s="15" t="n">
-        <v>0.0111</v>
+        <v>0.0444</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1207200</v>
+        <v>1761400</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.27</v>
+        <v>7.65</v>
       </c>
       <c r="H93" t="n">
-        <v>33.28</v>
-      </c>
-      <c r="I93" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.84</v>
+      </c>
+      <c r="I93" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>1.898</v>
+        <v>0.226</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>2.028</v>
+        <v>0.225</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4691,40 +4691,36 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ALPHA</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E94" s="17" t="n">
-        <v>0</v>
+        <v>0.265</v>
+      </c>
+      <c r="E94" s="15" t="n">
+        <v>0.0392</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1196600</v>
+        <v>1730400</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.51</v>
+        <v>0.14</v>
       </c>
       <c r="H94" t="n">
-        <v>68.48999999999999</v>
+        <v>32.4</v>
       </c>
       <c r="I94" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J94" s="9" t="n">
-        <v>0.258</v>
-      </c>
-      <c r="K94" s="9" t="n">
-        <v>0.257</v>
-      </c>
+      <c r="J94" s="9" t="n"/>
+      <c r="K94" s="9" t="n"/>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
     </row>
@@ -4736,28 +4732,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0023</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>IFCAMSC</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0.205</v>
+        <v>1.45</v>
       </c>
       <c r="E95" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1173500</v>
+        <v>1715300</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>2.11</v>
+        <v>0.79</v>
       </c>
       <c r="H95" t="n">
-        <v>48.37</v>
+        <v>28.24</v>
       </c>
       <c r="I95" s="13" t="inlineStr">
         <is>
@@ -4765,10 +4761,10 @@
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>0.205</v>
+        <v>1.509</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>0.214</v>
+        <v>1.623</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4781,39 +4777,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="E96" s="15" t="n">
-        <v>0.029</v>
+        <v>0.8</v>
+      </c>
+      <c r="E96" s="10" t="n">
+        <v>-0.0244</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1171700</v>
+        <v>1700900</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.31</v>
+        <v>0.12</v>
       </c>
       <c r="H96" t="n">
-        <v>41.09</v>
-      </c>
-      <c r="I96" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.49</v>
+      </c>
+      <c r="I96" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.366</v>
+        <v>0.766</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.385</v>
+        <v>0.711</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4826,28 +4822,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="E97" s="15" t="n">
-        <v>0.029</v>
+        <v>2.83</v>
+      </c>
+      <c r="E97" s="10" t="n">
+        <v>-0.0208</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1127000</v>
+        <v>1677500</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.89</v>
+        <v>0.17</v>
       </c>
       <c r="H97" t="n">
-        <v>57.46</v>
+        <v>56.13</v>
       </c>
       <c r="I97" s="16" t="inlineStr">
         <is>
@@ -4855,10 +4851,10 @@
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>0.339</v>
+        <v>2.769</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0.345</v>
+        <v>2.593</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4871,28 +4867,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>13.02</v>
-      </c>
-      <c r="E98" s="15" t="n">
-        <v>0.0124</v>
+        <v>3.88</v>
+      </c>
+      <c r="E98" s="10" t="n">
+        <v>-0.03</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1103400</v>
+        <v>1654100</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.13</v>
+        <v>0.53</v>
       </c>
       <c r="H98" t="n">
-        <v>44.74</v>
+        <v>54.58</v>
       </c>
       <c r="I98" s="16" t="inlineStr">
         <is>
@@ -4900,10 +4896,10 @@
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>13.053</v>
+        <v>3.854</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>13.587</v>
+        <v>3.56</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4916,39 +4912,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="E99" s="10" t="n">
-        <v>-0.021</v>
+        <v>-0.0245</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1089300</v>
+        <v>1651300</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.39</v>
+        <v>0.24</v>
       </c>
       <c r="H99" t="n">
-        <v>74.53</v>
-      </c>
-      <c r="I99" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.99</v>
+      </c>
+      <c r="I99" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>1.2</v>
+        <v>1.674</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>1.146</v>
+        <v>1.79</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4961,28 +4957,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>1.16</v>
+        <v>4.58</v>
       </c>
       <c r="E100" s="10" t="n">
-        <v>-0.0333</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1068500</v>
+        <v>1618900</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="H100" t="n">
-        <v>56.1</v>
+        <v>40.64</v>
       </c>
       <c r="I100" s="13" t="inlineStr">
         <is>
@@ -4990,10 +4986,10 @@
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>1.149</v>
+        <v>4.689</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>1.063</v>
+        <v>4.628</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -5006,39 +5002,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E101" s="17" t="n">
-        <v>0</v>
+        <v>0.385</v>
+      </c>
+      <c r="E101" s="10" t="n">
+        <v>-0.0253</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1065900</v>
+        <v>1585900</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.96</v>
+        <v>0.13</v>
       </c>
       <c r="H101" t="n">
-        <v>8.08</v>
-      </c>
-      <c r="I101" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.59</v>
+      </c>
+      <c r="I101" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>0.586</v>
+        <v>0.385</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>0.624</v>
+        <v>0.375</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5051,28 +5047,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>TALIWRK</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E102" s="10" t="n">
-        <v>-0.0392</v>
+        <v>1.82</v>
+      </c>
+      <c r="E102" s="15" t="n">
+        <v>0.0111</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1024100</v>
+        <v>1558000</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.41</v>
+        <v>0.35</v>
       </c>
       <c r="H102" t="n">
-        <v>43.51</v>
+        <v>33.28</v>
       </c>
       <c r="I102" s="13" t="inlineStr">
         <is>
@@ -5080,10 +5076,10 @@
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>0.253</v>
+        <v>1.898</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>0.262</v>
+        <v>2.028</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5096,39 +5092,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E103" s="10" t="n">
-        <v>-0.0196</v>
+        <v>12.98</v>
+      </c>
+      <c r="E103" s="15" t="n">
+        <v>0.009300000000000001</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>989900</v>
+        <v>1528300</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.32</v>
+        <v>0.17</v>
       </c>
       <c r="H103" t="n">
-        <v>47.39</v>
-      </c>
-      <c r="I103" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.04</v>
+      </c>
+      <c r="I103" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>0.765</v>
+        <v>13.049</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>0.747</v>
+        <v>13.586</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5141,39 +5137,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.905</v>
+        <v>0.295</v>
       </c>
       <c r="E104" s="10" t="n">
-        <v>-0.0109</v>
+        <v>-0.0167</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>964900</v>
+        <v>1527900</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.44</v>
+        <v>0.25</v>
       </c>
       <c r="H104" t="n">
-        <v>39.18</v>
-      </c>
-      <c r="I104" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.8</v>
+      </c>
+      <c r="I104" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.923</v>
+        <v>0.288</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.274</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5186,28 +5182,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="E105" s="15" t="n">
-        <v>0.0054</v>
+        <v>0.635</v>
+      </c>
+      <c r="E105" s="10" t="n">
+        <v>-0.0379</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>950100</v>
+        <v>1512100</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.51</v>
+        <v>0.67</v>
       </c>
       <c r="H105" t="n">
-        <v>32.53</v>
+        <v>57.69</v>
       </c>
       <c r="I105" s="13" t="inlineStr">
         <is>
@@ -5215,10 +5211,10 @@
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>0.966</v>
+        <v>0.618</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0.995</v>
+        <v>0.526</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5231,39 +5227,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>ALPHA</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="E106" s="10" t="n">
-        <v>-0.0173</v>
+        <v>0.28</v>
+      </c>
+      <c r="E106" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>938300</v>
+        <v>1475900</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.1</v>
+        <v>0.63</v>
       </c>
       <c r="H106" t="n">
-        <v>38.06</v>
-      </c>
-      <c r="I106" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.48999999999999</v>
+      </c>
+      <c r="I106" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>4.685</v>
+        <v>0.258</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>4.627</v>
+        <v>0.257</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5276,39 +5272,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>0.555</v>
+        <v>2.97</v>
       </c>
       <c r="E107" s="10" t="n">
-        <v>-0.0089</v>
+        <v>-0.0388</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>932900</v>
+        <v>1466600</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.23</v>
+        <v>0.33</v>
       </c>
       <c r="H107" t="n">
-        <v>32.96</v>
-      </c>
-      <c r="I107" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.02</v>
+      </c>
+      <c r="I107" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>0.573</v>
+        <v>2.981</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>0.583</v>
+        <v>2.821</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5321,39 +5317,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E108" s="10" t="n">
-        <v>-0.0138</v>
+        <v>4.31</v>
+      </c>
+      <c r="E108" s="15" t="n">
+        <v>0.006999999999999999</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>896100</v>
+        <v>1463000</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.09</v>
+        <v>0.29</v>
       </c>
       <c r="H108" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="I108" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.22</v>
+      </c>
+      <c r="I108" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>2.771</v>
+        <v>4.501</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>2.594</v>
+        <v>4.854</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5366,28 +5362,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E109" s="15" t="n">
-        <v>0.0053</v>
+        <v>1.15</v>
+      </c>
+      <c r="E109" s="10" t="n">
+        <v>-0.0417</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>873200</v>
+        <v>1410000</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.13</v>
+        <v>0.32</v>
       </c>
       <c r="H109" t="n">
-        <v>43.29</v>
+        <v>54.12</v>
       </c>
       <c r="I109" s="13" t="inlineStr">
         <is>
@@ -5395,10 +5391,10 @@
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>1.93</v>
+        <v>1.148</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>1.958</v>
+        <v>1.063</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5411,39 +5407,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="E110" s="15" t="n">
-        <v>0.0028</v>
+        <v>0.475</v>
+      </c>
+      <c r="E110" s="10" t="n">
+        <v>-0.0104</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>861200</v>
+        <v>1355500</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.41</v>
       </c>
       <c r="H110" t="n">
-        <v>52.92</v>
-      </c>
-      <c r="I110" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.43000000000001</v>
+      </c>
+      <c r="I110" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>3.568</v>
+        <v>0.414</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>2.71</v>
+        <v>0.367</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5456,28 +5452,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>1.37</v>
+        <v>0.27</v>
       </c>
       <c r="E111" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>844900</v>
+        <v>1337900</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.43</v>
+        <v>0.32</v>
       </c>
       <c r="H111" t="n">
-        <v>53.6</v>
+        <v>66.14</v>
       </c>
       <c r="I111" s="13" t="inlineStr">
         <is>
@@ -5485,10 +5481,10 @@
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>1.369</v>
+        <v>0.248</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>1.336</v>
+        <v>0.218</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5501,28 +5497,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="E112" s="15" t="n">
-        <v>0.014</v>
+        <v>4.16</v>
+      </c>
+      <c r="E112" s="10" t="n">
+        <v>-0.0142</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>844000</v>
+        <v>1337700</v>
       </c>
       <c r="G112" s="12" t="n">
         <v>0.17</v>
       </c>
       <c r="H112" t="n">
-        <v>32.17</v>
+        <v>41.06</v>
       </c>
       <c r="I112" s="13" t="inlineStr">
         <is>
@@ -5530,10 +5526,10 @@
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>4.504</v>
+        <v>4.372</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>4.855</v>
+        <v>4.461</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5546,28 +5542,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>EMETALL</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>5.92</v>
-      </c>
-      <c r="E113" s="10" t="n">
-        <v>-0.0182</v>
+        <v>0.44</v>
+      </c>
+      <c r="E113" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>831100</v>
+        <v>1280700</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.06</v>
+        <v>2.93</v>
       </c>
       <c r="H113" t="n">
-        <v>33.32</v>
+        <v>57.26</v>
       </c>
       <c r="I113" s="13" t="inlineStr">
         <is>
@@ -5575,10 +5571,10 @@
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>6.168</v>
+        <v>0.44</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>6.406</v>
+        <v>0.437</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5591,28 +5587,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>OSK</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>1.62</v>
+        <v>0.92</v>
       </c>
       <c r="E114" s="10" t="n">
-        <v>-0.0241</v>
+        <v>-0.0108</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>823100</v>
+        <v>1276400</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.57</v>
+        <v>0.24</v>
       </c>
       <c r="H114" t="n">
-        <v>19.34</v>
+        <v>59.26</v>
       </c>
       <c r="I114" s="13" t="inlineStr">
         <is>
@@ -5620,10 +5616,10 @@
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>1.801</v>
+        <v>0.905</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>1.928</v>
+        <v>0.861</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5636,39 +5632,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="E115" s="17" t="n">
-        <v>0</v>
+        <v>1.41</v>
+      </c>
+      <c r="E115" s="10" t="n">
+        <v>-0.014</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>820000</v>
+        <v>1276200</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.15</v>
+        <v>0.45</v>
       </c>
       <c r="H115" t="n">
-        <v>63.98</v>
-      </c>
-      <c r="I115" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.09999999999999</v>
+      </c>
+      <c r="I115" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>0.906</v>
+        <v>1.201</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>0.862</v>
+        <v>1.146</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5681,39 +5677,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>MFLOUR</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>1.14</v>
+        <v>0.59</v>
       </c>
       <c r="E116" s="10" t="n">
-        <v>-0.0256</v>
+        <v>-0.0167</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>786600</v>
+        <v>1253600</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.16</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H116" t="n">
-        <v>71.20999999999999</v>
-      </c>
-      <c r="I116" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.88</v>
+      </c>
+      <c r="I116" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>1.051</v>
+        <v>0.619</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>0.886</v>
+        <v>0.638</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5726,39 +5722,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E117" s="10" t="n">
-        <v>-0.0291</v>
+        <v>1.9</v>
+      </c>
+      <c r="E117" s="15" t="n">
+        <v>0.0053</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>770700</v>
+        <v>1215300</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="H117" t="n">
-        <v>52.6</v>
-      </c>
-      <c r="I117" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.29</v>
+      </c>
+      <c r="I117" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>2.984</v>
+        <v>1.93</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>2.822</v>
+        <v>1.958</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5780,19 +5776,19 @@
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>7.85</v>
+        <v>7.83</v>
       </c>
       <c r="E118" s="10" t="n">
-        <v>-0.0236</v>
+        <v>-0.0261</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>757900</v>
+        <v>1199100</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.19</v>
+        <v>0.3</v>
       </c>
       <c r="H118" t="n">
-        <v>69.18000000000001</v>
+        <v>68.58</v>
       </c>
       <c r="I118" s="16" t="inlineStr">
         <is>
@@ -5800,10 +5796,10 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>7.157</v>
+        <v>7.155</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>6.73</v>
+        <v>6.729</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5816,28 +5812,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0023</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>IFCAMSC</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>7.13</v>
+        <v>0.2</v>
       </c>
       <c r="E119" s="10" t="n">
-        <v>-0.0097</v>
+        <v>-0.0244</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>756800</v>
+        <v>1183600</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.1</v>
+        <v>2.13</v>
       </c>
       <c r="H119" t="n">
-        <v>29.53</v>
+        <v>41.38</v>
       </c>
       <c r="I119" s="13" t="inlineStr">
         <is>
@@ -5845,10 +5841,10 @@
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>7.432</v>
+        <v>0.204</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>7.739</v>
+        <v>0.214</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5861,28 +5857,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0285</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>MERSEC</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="E120" s="10" t="n">
-        <v>-0.0168</v>
+        <v>0.27</v>
+      </c>
+      <c r="E120" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>748700</v>
+        <v>1150000</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.24</v>
+        <v>1.13</v>
       </c>
       <c r="H120" t="n">
-        <v>44.84</v>
+        <v>41.34</v>
       </c>
       <c r="I120" s="13" t="inlineStr">
         <is>
@@ -5890,10 +5886,10 @@
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>2.979</v>
+        <v>0.274</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>3.037</v>
+        <v>0.276</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5906,39 +5902,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>7134</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>PWF</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E121" s="17" t="n">
-        <v>0</v>
+        <v>1.24</v>
+      </c>
+      <c r="E121" s="15" t="n">
+        <v>0.008100000000000001</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>719200</v>
+        <v>1147900</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>34.19</v>
+        <v>0.12</v>
       </c>
       <c r="H121" t="n">
-        <v>49.91</v>
-      </c>
-      <c r="I121" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.99</v>
+      </c>
+      <c r="I121" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>0.74</v>
+        <v>1.289</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>0.744</v>
+        <v>1.389</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5951,39 +5947,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>TALIWRK</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>0.77</v>
+        <v>0.245</v>
       </c>
       <c r="E122" s="10" t="n">
-        <v>-0.0314</v>
+        <v>-0.0392</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>706300</v>
+        <v>1147900</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.39</v>
+        <v>0.46</v>
       </c>
       <c r="H122" t="n">
-        <v>63.96</v>
-      </c>
-      <c r="I122" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.51</v>
+      </c>
+      <c r="I122" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>0.707</v>
+        <v>0.253</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.262</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -5996,39 +5992,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>7252</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>TEOSENG</t>
+          <t>OSK</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E123" s="17" t="n">
-        <v>0</v>
+        <v>1.61</v>
+      </c>
+      <c r="E123" s="10" t="n">
+        <v>-0.0301</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>704100</v>
+        <v>1138700</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>1.61</v>
+        <v>0.79</v>
       </c>
       <c r="H123" t="n">
-        <v>59.7</v>
-      </c>
-      <c r="I123" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>18.83</v>
+      </c>
+      <c r="I123" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>0.821</v>
+        <v>1.8</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>0.839</v>
+        <v>1.928</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6041,39 +6037,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>IHH</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="E124" s="15" t="n">
-        <v>0.004</v>
+        <v>7.86</v>
+      </c>
+      <c r="E124" s="10" t="n">
+        <v>-0.0051</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>701300</v>
+        <v>1134600</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.05</v>
+        <v>0.27</v>
       </c>
       <c r="H124" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="I124" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.47</v>
+      </c>
+      <c r="I124" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>2.464</v>
+        <v>7.862</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>2.351</v>
+        <v>8.013</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6086,39 +6082,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>4.19</v>
+        <v>0.92</v>
       </c>
       <c r="E125" s="10" t="n">
-        <v>-0.0071</v>
+        <v>-0.0054</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>692600</v>
+        <v>1126500</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.08</v>
+        <v>0.6</v>
       </c>
       <c r="H125" t="n">
-        <v>63.76</v>
-      </c>
-      <c r="I125" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.85</v>
+      </c>
+      <c r="I125" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>3.939</v>
+        <v>0.965</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>3.421</v>
+        <v>0.994</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6131,39 +6127,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="E126" s="10" t="n">
-        <v>-0.0098</v>
+        <v>2.1</v>
+      </c>
+      <c r="E126" s="15" t="n">
+        <v>0.0048</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>671600</v>
+        <v>1099500</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.16</v>
+        <v>0.06</v>
       </c>
       <c r="H126" t="n">
-        <v>69.97</v>
-      </c>
-      <c r="I126" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.56</v>
+      </c>
+      <c r="I126" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>2.659</v>
+        <v>2.098</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>2.016</v>
+        <v>2.081</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6176,28 +6172,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>2.1</v>
+        <v>3.54</v>
       </c>
       <c r="E127" s="15" t="n">
-        <v>0.0048</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>648900</v>
+        <v>1096700</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
       <c r="H127" t="n">
-        <v>50.56</v>
+        <v>53.39</v>
       </c>
       <c r="I127" s="13" t="inlineStr">
         <is>
@@ -6205,10 +6201,10 @@
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>2.098</v>
+        <v>3.569</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>2.081</v>
+        <v>2.71</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6221,28 +6217,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="E128" s="15" t="n">
-        <v>0.024</v>
+        <v>7.13</v>
+      </c>
+      <c r="E128" s="10" t="n">
+        <v>-0.0097</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>639000</v>
+        <v>1078100</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.63</v>
+        <v>0.14</v>
       </c>
       <c r="H128" t="n">
-        <v>41.04</v>
+        <v>29.53</v>
       </c>
       <c r="I128" s="13" t="inlineStr">
         <is>
@@ -6250,10 +6246,10 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>2.231</v>
+        <v>7.432</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>2.32</v>
+        <v>7.739</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6266,28 +6262,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E129" s="10" t="n">
-        <v>-0.008800000000000001</v>
+        <v>1.37</v>
+      </c>
+      <c r="E129" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>625100</v>
+        <v>1074200</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.11</v>
+        <v>0.54</v>
       </c>
       <c r="H129" t="n">
-        <v>46.32</v>
+        <v>53.6</v>
       </c>
       <c r="I129" s="13" t="inlineStr">
         <is>
@@ -6295,10 +6291,10 @@
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>1.148</v>
+        <v>1.369</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>1.166</v>
+        <v>1.336</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6311,28 +6307,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>JTIASA</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E130" s="10" t="n">
-        <v>-0.0108</v>
+        <v>0.5</v>
+      </c>
+      <c r="E130" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>616400</v>
+        <v>1065900</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.17</v>
+        <v>0.96</v>
       </c>
       <c r="H130" t="n">
-        <v>31.51</v>
+        <v>8.08</v>
       </c>
       <c r="I130" s="13" t="inlineStr">
         <is>
@@ -6340,10 +6336,10 @@
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>0.97</v>
+        <v>0.586</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>1.025</v>
+        <v>0.624</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6356,28 +6352,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>1.22</v>
+        <v>2.92</v>
       </c>
       <c r="E131" s="10" t="n">
-        <v>-0.008100000000000001</v>
+        <v>-0.0201</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>615300</v>
+        <v>1065300</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.06</v>
+        <v>0.34</v>
       </c>
       <c r="H131" t="n">
-        <v>29.72</v>
+        <v>44.08</v>
       </c>
       <c r="I131" s="13" t="inlineStr">
         <is>
@@ -6385,10 +6381,10 @@
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>1.287</v>
+        <v>2.978</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>1.389</v>
+        <v>3.037</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6401,39 +6397,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>7252</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>TEOSENG</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>4.17</v>
+        <v>0.825</v>
       </c>
       <c r="E132" s="10" t="n">
-        <v>-0.0118</v>
+        <v>-0.0179</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>611600</v>
+        <v>1062700</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.08</v>
+        <v>2.43</v>
       </c>
       <c r="H132" t="n">
-        <v>41.35</v>
-      </c>
-      <c r="I132" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.98</v>
+      </c>
+      <c r="I132" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>4.373</v>
+        <v>0.82</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>4.461</v>
+        <v>0.839</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6446,39 +6442,39 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>LCTITAN</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>3.31</v>
+        <v>0.32</v>
       </c>
       <c r="E133" s="10" t="n">
-        <v>-0.0265</v>
+        <v>-0.0303</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>610000</v>
+        <v>1054900</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="H133" t="n">
-        <v>68.17</v>
-      </c>
-      <c r="I133" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.35</v>
+      </c>
+      <c r="I133" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>2.986</v>
+        <v>0.333</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>2.795</v>
+        <v>0.33</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6491,28 +6487,28 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0358</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>ICTZONE</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E134" s="10" t="n">
-        <v>-0.0177</v>
+        <v>0.225</v>
+      </c>
+      <c r="E134" s="15" t="n">
+        <v>0.009000000000000001</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>609100</v>
+        <v>1046200</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.11</v>
+        <v>0.37</v>
       </c>
       <c r="H134" t="n">
-        <v>34.11</v>
+        <v>40.31</v>
       </c>
       <c r="I134" s="13" t="inlineStr">
         <is>
@@ -6520,10 +6516,10 @@
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>0.597</v>
+        <v>0.242</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>0.644</v>
+        <v>0.25</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6536,28 +6532,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>0.96</v>
+        <v>0.905</v>
       </c>
       <c r="E135" s="10" t="n">
-        <v>-0.0103</v>
+        <v>-0.0109</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>606700</v>
+        <v>1039800</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.25</v>
+        <v>0.47</v>
       </c>
       <c r="H135" t="n">
-        <v>24.25</v>
+        <v>39.18</v>
       </c>
       <c r="I135" s="13" t="inlineStr">
         <is>
@@ -6565,10 +6561,10 @@
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>1.053</v>
+        <v>0.923</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>1.125</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6581,28 +6577,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>5142</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>WASCO</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>0.76</v>
+        <v>4.22</v>
       </c>
       <c r="E136" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>597500</v>
+        <v>995900</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.37</v>
+        <v>0.12</v>
       </c>
       <c r="H136" t="n">
-        <v>58.59</v>
+        <v>65.11</v>
       </c>
       <c r="I136" s="16" t="inlineStr">
         <is>
@@ -6610,10 +6606,10 @@
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>0.734</v>
+        <v>3.942</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>0.722</v>
+        <v>3.421</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6626,39 +6622,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>JTIASA</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>0.625</v>
+        <v>0.93</v>
       </c>
       <c r="E137" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>580800</v>
+        <v>995800</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.14</v>
+        <v>0.28</v>
       </c>
       <c r="H137" t="n">
-        <v>52.82</v>
-      </c>
-      <c r="I137" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.37</v>
+      </c>
+      <c r="I137" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>0.616</v>
+        <v>0.971</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>0.609</v>
+        <v>1.025</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6671,39 +6667,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>5.93</v>
+        <v>0.555</v>
       </c>
       <c r="E138" s="10" t="n">
-        <v>-0.005</v>
+        <v>-0.0089</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>577600</v>
+        <v>966600</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="H138" t="n">
-        <v>64.73</v>
-      </c>
-      <c r="I138" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.96</v>
+      </c>
+      <c r="I138" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>5.439</v>
+        <v>0.573</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>5.348</v>
+        <v>0.583</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6716,28 +6712,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>FFB</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="E139" s="17" t="n">
-        <v>0</v>
+        <v>0.865</v>
+      </c>
+      <c r="E139" s="10" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>536300</v>
+        <v>953800</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.19</v>
+        <v>0.3</v>
       </c>
       <c r="H139" t="n">
-        <v>22.45</v>
+        <v>52.87</v>
       </c>
       <c r="I139" s="13" t="inlineStr">
         <is>
@@ -6745,10 +6741,10 @@
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>1.89</v>
+        <v>0.864</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>2.022</v>
+        <v>0.858</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6761,28 +6757,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="E140" s="15" t="n">
-        <v>0.0143</v>
+        <v>1.14</v>
+      </c>
+      <c r="E140" s="10" t="n">
+        <v>-0.0256</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>530000</v>
+        <v>931900</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.13</v>
+        <v>0.19</v>
       </c>
       <c r="H140" t="n">
-        <v>65.23999999999999</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="I140" s="16" t="inlineStr">
         <is>
@@ -6790,10 +6786,10 @@
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>1.297</v>
+        <v>1.051</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>1.193</v>
+        <v>0.886</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6806,39 +6802,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>5142</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>WASCO</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="E141" s="10" t="n">
-        <v>-0.0123</v>
+        <v>0.76</v>
+      </c>
+      <c r="E141" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>517400</v>
+        <v>899800</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.08</v>
+        <v>0.55</v>
       </c>
       <c r="H141" t="n">
-        <v>35</v>
-      </c>
-      <c r="I141" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.59</v>
+      </c>
+      <c r="I141" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>1.676</v>
+        <v>0.734</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>1.791</v>
+        <v>0.722</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6851,28 +6847,28 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0311</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>GOHUB</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E142" s="15" t="n">
-        <v>0.0625</v>
+        <v>1.12</v>
+      </c>
+      <c r="E142" s="10" t="n">
+        <v>-0.0175</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>515400</v>
+        <v>899700</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>3.64</v>
+        <v>0.15</v>
       </c>
       <c r="H142" t="n">
-        <v>55.46</v>
+        <v>44.88</v>
       </c>
       <c r="I142" s="13" t="inlineStr">
         <is>
@@ -6880,10 +6876,10 @@
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>1.163</v>
+        <v>1.147</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>1.156</v>
+        <v>1.166</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6896,39 +6892,39 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>0.78</v>
+        <v>2.51</v>
       </c>
       <c r="E143" s="15" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.004</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>512200</v>
+        <v>874300</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>0.31</v>
+        <v>0.06</v>
       </c>
       <c r="H143" t="n">
-        <v>54.32</v>
-      </c>
-      <c r="I143" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.5</v>
+      </c>
+      <c r="I143" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>0.766</v>
+        <v>2.464</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>0.76</v>
+        <v>2.351</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6941,28 +6937,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>1.72</v>
+        <v>0.77</v>
       </c>
       <c r="E144" s="10" t="n">
-        <v>-0.0171</v>
+        <v>-0.0314</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>502700</v>
+        <v>870000</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>0.3</v>
+        <v>0.49</v>
       </c>
       <c r="H144" t="n">
-        <v>57.63</v>
+        <v>63.96</v>
       </c>
       <c r="I144" s="16" t="inlineStr">
         <is>
@@ -6970,16 +6966,1411 @@
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>1.661</v>
+        <v>0.707</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>1.678</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
     </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D145" s="9" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="E145" s="10" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="F145" s="11" t="n">
+        <v>847400</v>
+      </c>
+      <c r="G145" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H145" t="n">
+        <v>55.51</v>
+      </c>
+      <c r="I145" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J145" s="9" t="n">
+        <v>0.8169999999999999</v>
+      </c>
+      <c r="K145" s="9" t="n">
+        <v>0.754</v>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" s="14" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>CPETECH</t>
+        </is>
+      </c>
+      <c r="D146" s="9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E146" s="10" t="n">
+        <v>-0.0214</v>
+      </c>
+      <c r="F146" s="11" t="n">
+        <v>845900</v>
+      </c>
+      <c r="G146" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H146" t="n">
+        <v>60.26</v>
+      </c>
+      <c r="I146" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J146" s="9" t="n">
+        <v>1.292</v>
+      </c>
+      <c r="K146" s="9" t="n">
+        <v>1.192</v>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" s="14" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>PENTA</t>
+        </is>
+      </c>
+      <c r="D147" s="9" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="E147" s="10" t="n">
+        <v>-0.008399999999999999</v>
+      </c>
+      <c r="F147" s="11" t="n">
+        <v>812900</v>
+      </c>
+      <c r="G147" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H147" t="n">
+        <v>64.08</v>
+      </c>
+      <c r="I147" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J147" s="9" t="n">
+        <v>5.437</v>
+      </c>
+      <c r="K147" s="9" t="n">
+        <v>5.347</v>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" s="14" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D148" s="9" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="E148" s="10" t="n">
+        <v>-0.0412</v>
+      </c>
+      <c r="F148" s="11" t="n">
+        <v>807200</v>
+      </c>
+      <c r="G148" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H148" t="n">
+        <v>65.29000000000001</v>
+      </c>
+      <c r="I148" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J148" s="9" t="n">
+        <v>2.981</v>
+      </c>
+      <c r="K148" s="9" t="n">
+        <v>2.794</v>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" s="14" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>0223</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>SAMAIDEN</t>
+        </is>
+      </c>
+      <c r="D149" s="9" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="E149" s="10" t="n">
+        <v>-0.0163</v>
+      </c>
+      <c r="F149" s="11" t="n">
+        <v>802200</v>
+      </c>
+      <c r="G149" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H149" t="n">
+        <v>69</v>
+      </c>
+      <c r="I149" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J149" s="9" t="n">
+        <v>2.657</v>
+      </c>
+      <c r="K149" s="9" t="n">
+        <v>2.016</v>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" s="14" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>7084</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>QL</t>
+        </is>
+      </c>
+      <c r="D150" s="9" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="E150" s="10" t="n">
+        <v>-0.0102</v>
+      </c>
+      <c r="F150" s="11" t="n">
+        <v>796500</v>
+      </c>
+      <c r="G150" s="12" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H150" t="n">
+        <v>47.06</v>
+      </c>
+      <c r="I150" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J150" s="9" t="n">
+        <v>3.929</v>
+      </c>
+      <c r="K150" s="9" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" s="14" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>6971</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>KOBAY</t>
+        </is>
+      </c>
+      <c r="D151" s="9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E151" s="15" t="n">
+        <v>0.009599999999999999</v>
+      </c>
+      <c r="F151" s="11" t="n">
+        <v>769900</v>
+      </c>
+      <c r="G151" s="12" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="H151" t="n">
+        <v>38.46</v>
+      </c>
+      <c r="I151" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J151" s="9" t="n">
+        <v>2.229</v>
+      </c>
+      <c r="K151" s="9" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" s="14" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>0372</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>CHEEDING</t>
+        </is>
+      </c>
+      <c r="D152" s="9" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="E152" s="10" t="n">
+        <v>-0.016</v>
+      </c>
+      <c r="F152" s="11" t="n">
+        <v>732100</v>
+      </c>
+      <c r="G152" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H152" t="n">
+        <v>50.32</v>
+      </c>
+      <c r="I152" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J152" s="9" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="K152" s="9" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" s="14" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>7134</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>PWF</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E153" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" s="11" t="n">
+        <v>719200</v>
+      </c>
+      <c r="G153" s="12" t="n">
+        <v>34.19</v>
+      </c>
+      <c r="H153" t="n">
+        <v>49.91</v>
+      </c>
+      <c r="I153" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J153" s="9" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="K153" s="9" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" s="14" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>3417</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>E&amp;O</t>
+        </is>
+      </c>
+      <c r="D154" s="9" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E154" s="10" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="F154" s="11" t="n">
+        <v>713700</v>
+      </c>
+      <c r="G154" s="12" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H154" t="n">
+        <v>44.45</v>
+      </c>
+      <c r="I154" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J154" s="9" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="K154" s="9" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" s="14" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>7081</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="D155" s="9" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="E155" s="10" t="n">
+        <v>-0.0103</v>
+      </c>
+      <c r="F155" s="11" t="n">
+        <v>712800</v>
+      </c>
+      <c r="G155" s="12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H155" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="I155" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J155" s="9" t="n">
+        <v>1.053</v>
+      </c>
+      <c r="K155" s="9" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" s="14" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>5323</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>JPG</t>
+        </is>
+      </c>
+      <c r="D156" s="9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="E156" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" s="11" t="n">
+        <v>697300</v>
+      </c>
+      <c r="G156" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H156" t="n">
+        <v>36.46</v>
+      </c>
+      <c r="I156" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J156" s="9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="K156" s="9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" s="14" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>5176</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>SUNREIT</t>
+        </is>
+      </c>
+      <c r="D157" s="9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="E157" s="10" t="n">
+        <v>-0.009599999999999999</v>
+      </c>
+      <c r="F157" s="11" t="n">
+        <v>682600</v>
+      </c>
+      <c r="G157" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H157" t="n">
+        <v>49.67</v>
+      </c>
+      <c r="I157" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J157" s="9" t="n">
+        <v>2.055</v>
+      </c>
+      <c r="K157" s="9" t="n">
+        <v>2.085</v>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" s="14" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>0151</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>KGB</t>
+        </is>
+      </c>
+      <c r="D158" s="9" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="E158" s="10" t="n">
+        <v>-0.0335</v>
+      </c>
+      <c r="F158" s="11" t="n">
+        <v>666900</v>
+      </c>
+      <c r="G158" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H158" t="n">
+        <v>48.38</v>
+      </c>
+      <c r="I158" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J158" s="9" t="n">
+        <v>8.746</v>
+      </c>
+      <c r="K158" s="9" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" s="14" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>5306</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>FFB</t>
+        </is>
+      </c>
+      <c r="D159" s="9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="E159" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" s="11" t="n">
+        <v>655300</v>
+      </c>
+      <c r="G159" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H159" t="n">
+        <v>22.45</v>
+      </c>
+      <c r="I159" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J159" s="9" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="K159" s="9" t="n">
+        <v>2.022</v>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" s="14" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>0233</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>PEKAT</t>
+        </is>
+      </c>
+      <c r="D160" s="9" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="E160" s="10" t="n">
+        <v>-0.0312</v>
+      </c>
+      <c r="F160" s="11" t="n">
+        <v>638700</v>
+      </c>
+      <c r="G160" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H160" t="n">
+        <v>65.98</v>
+      </c>
+      <c r="I160" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J160" s="9" t="n">
+        <v>2.595</v>
+      </c>
+      <c r="K160" s="9" t="n">
+        <v>2.122</v>
+      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" s="14" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>0099</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>SCICOM</t>
+        </is>
+      </c>
+      <c r="D161" s="9" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="E161" s="10" t="n">
+        <v>-0.0218</v>
+      </c>
+      <c r="F161" s="11" t="n">
+        <v>630300</v>
+      </c>
+      <c r="G161" s="12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="H161" t="n">
+        <v>46.42</v>
+      </c>
+      <c r="I161" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J161" s="9" t="n">
+        <v>2.288</v>
+      </c>
+      <c r="K161" s="9" t="n">
+        <v>2.226</v>
+      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" s="14" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>5185</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>AFFIN</t>
+        </is>
+      </c>
+      <c r="D162" s="9" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="E162" s="10" t="n">
+        <v>-0.0151</v>
+      </c>
+      <c r="F162" s="11" t="n">
+        <v>628400</v>
+      </c>
+      <c r="G162" s="12" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H162" t="n">
+        <v>26.98</v>
+      </c>
+      <c r="I162" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J162" s="9" t="n">
+        <v>2.017</v>
+      </c>
+      <c r="K162" s="9" t="n">
+        <v>2.084</v>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" s="14" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>5301</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>CTOS</t>
+        </is>
+      </c>
+      <c r="D163" s="9" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="E163" s="10" t="n">
+        <v>-0.0177</v>
+      </c>
+      <c r="F163" s="11" t="n">
+        <v>627800</v>
+      </c>
+      <c r="G163" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H163" t="n">
+        <v>34.11</v>
+      </c>
+      <c r="I163" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J163" s="9" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="K163" s="9" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" s="14" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>5878</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>KPJ</t>
+        </is>
+      </c>
+      <c r="D164" s="9" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="E164" s="15" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="F164" s="11" t="n">
+        <v>619700</v>
+      </c>
+      <c r="G164" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H164" t="n">
+        <v>38.47</v>
+      </c>
+      <c r="I164" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J164" s="9" t="n">
+        <v>2.623</v>
+      </c>
+      <c r="K164" s="9" t="n">
+        <v>2.787</v>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" s="14" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>5302</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>ATECH</t>
+        </is>
+      </c>
+      <c r="D165" s="9" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E165" s="15" t="n">
+        <v>0.006500000000000001</v>
+      </c>
+      <c r="F165" s="11" t="n">
+        <v>617800</v>
+      </c>
+      <c r="G165" s="12" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H165" t="n">
+        <v>54.32</v>
+      </c>
+      <c r="I165" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J165" s="9" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="K165" s="9" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" s="14" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D166" s="9" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E166" s="10" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F166" s="11" t="n">
+        <v>608600</v>
+      </c>
+      <c r="G166" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H166" t="n">
+        <v>54.22</v>
+      </c>
+      <c r="I166" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J166" s="9" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="K166" s="9" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" s="14" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>6633</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>LHI</t>
+        </is>
+      </c>
+      <c r="D167" s="9" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="E167" s="15" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="F167" s="11" t="n">
+        <v>606500</v>
+      </c>
+      <c r="G167" s="12" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H167" t="n">
+        <v>52.39</v>
+      </c>
+      <c r="I167" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J167" s="9" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="K167" s="9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" s="14" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>SIMEPROP</t>
+        </is>
+      </c>
+      <c r="D168" s="9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E168" s="10" t="n">
+        <v>-0.0161</v>
+      </c>
+      <c r="F168" s="11" t="n">
+        <v>603900</v>
+      </c>
+      <c r="G168" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H168" t="n">
+        <v>41.62</v>
+      </c>
+      <c r="I168" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J168" s="9" t="n">
+        <v>1.249</v>
+      </c>
+      <c r="K168" s="9" t="n">
+        <v>1.287</v>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" s="14" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>0392</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>KEEMING</t>
+        </is>
+      </c>
+      <c r="D169" s="9" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="E169" s="10" t="n">
+        <v>-0.0115</v>
+      </c>
+      <c r="F169" s="11" t="n">
+        <v>591700</v>
+      </c>
+      <c r="G169" s="12" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="H169" t="n">
+        <v>53.67</v>
+      </c>
+      <c r="I169" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J169" s="9" t="n">
+        <v>2.558</v>
+      </c>
+      <c r="K169" s="9" t="n">
+        <v>2.407</v>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" s="14" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>7052</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>PADINI</t>
+        </is>
+      </c>
+      <c r="D170" s="9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E170" s="10" t="n">
+        <v>-0.0095</v>
+      </c>
+      <c r="F170" s="11" t="n">
+        <v>575600</v>
+      </c>
+      <c r="G170" s="12" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H170" t="n">
+        <v>40.03</v>
+      </c>
+      <c r="I170" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J170" s="9" t="n">
+        <v>1.058</v>
+      </c>
+      <c r="K170" s="9" t="n">
+        <v>1.198</v>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" s="14" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>5162</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>VSTECS</t>
+        </is>
+      </c>
+      <c r="D171" s="9" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="E171" s="10" t="n">
+        <v>-0.0229</v>
+      </c>
+      <c r="F171" s="11" t="n">
+        <v>574700</v>
+      </c>
+      <c r="G171" s="12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H171" t="n">
+        <v>56.26</v>
+      </c>
+      <c r="I171" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J171" s="9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="K171" s="9" t="n">
+        <v>1.678</v>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" s="14" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>5212</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>PAVREIT</t>
+        </is>
+      </c>
+      <c r="D172" s="9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E172" s="10" t="n">
+        <v>-0.0127</v>
+      </c>
+      <c r="F172" s="11" t="n">
+        <v>568300</v>
+      </c>
+      <c r="G172" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H172" t="n">
+        <v>44.57</v>
+      </c>
+      <c r="I172" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J172" s="9" t="n">
+        <v>1.564</v>
+      </c>
+      <c r="K172" s="9" t="n">
+        <v>1.622</v>
+      </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" s="14" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>0311</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>GOHUB</t>
+        </is>
+      </c>
+      <c r="D173" s="9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E173" s="15" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="F173" s="11" t="n">
+        <v>544400</v>
+      </c>
+      <c r="G173" s="12" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="H173" t="n">
+        <v>55.46</v>
+      </c>
+      <c r="I173" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J173" s="9" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="K173" s="9" t="n">
+        <v>1.156</v>
+      </c>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" s="14" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>8664</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>SPSETIA</t>
+        </is>
+      </c>
+      <c r="D174" s="9" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="E174" s="15" t="n">
+        <v>0.0208</v>
+      </c>
+      <c r="F174" s="11" t="n">
+        <v>522700</v>
+      </c>
+      <c r="G174" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H174" t="n">
+        <v>38.34</v>
+      </c>
+      <c r="I174" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J174" s="9" t="n">
+        <v>0.761</v>
+      </c>
+      <c r="K174" s="9" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" s="14" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>LGMS</t>
+        </is>
+      </c>
+      <c r="D175" s="9" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="E175" s="10" t="n">
+        <v>-0.0089</v>
+      </c>
+      <c r="F175" s="11" t="n">
+        <v>508000</v>
+      </c>
+      <c r="G175" s="12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H175" t="n">
+        <v>67.31</v>
+      </c>
+      <c r="I175" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J175" s="9" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="K175" s="9" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M144"/>
+  <autoFilter ref="A1:M175"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-08/bursa-report-2026-10-08.xlsx
+++ b/docs/downloads/2026-10-08/bursa-report-2026-10-08.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-08" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-08'!$A$1:$M$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-08'!$A$1:$M$194</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,10 +38,10 @@
       <color rgb="000CA30C"/>
     </font>
     <font>
-      <color rgb="00D03B3B"/>
+      <color rgb="00898781"/>
     </font>
     <font>
-      <color rgb="00898781"/>
+      <color rgb="00D03B3B"/>
     </font>
   </fonts>
   <fills count="4">
@@ -92,7 +92,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M175"/>
+  <dimension ref="A1:M194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.145</v>
+        <v>0.15</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0357</v>
+        <v>0.07139999999999999</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>4131000</v>
+        <v>4235800</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>55.82</v>
+        <v>58.63</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多，现价0.145高于50日均线0.131，RSI 55.82处中性偏上，未超买，信号可靠性尚可。</t>
+          <t>SAR转多，RSI 58.63未超买，现价0.15高于50日均线0.131，技术面信号偏正面。</t>
         </is>
       </c>
     </row>
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>0.075</v>
+        <v>0.08</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>-0.0625</v>
+        <v>0</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>119015700</v>
+        <v>125332300</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="H3" t="n">
-        <v>20.64</v>
+        <v>21.03</v>
       </c>
       <c r="I3" s="13" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="J3" s="9" t="n">
-        <v>0.182</v>
+        <v>0.183</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>0.401</v>
@@ -655,28 +655,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.34</v>
+        <v>0.885</v>
       </c>
       <c r="E4" s="15" t="n">
-        <v>0.0462</v>
+        <v>0.0351</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>56342500</v>
+        <v>65058600</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>1.05</v>
+        <v>0.9</v>
       </c>
       <c r="H4" t="n">
-        <v>77.84</v>
+        <v>71.42</v>
       </c>
       <c r="I4" s="16" t="inlineStr">
         <is>
@@ -684,10 +684,10 @@
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.273</v>
+        <v>0.776</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.242</v>
+        <v>0.707</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="14" t="inlineStr"/>
@@ -700,28 +700,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.875</v>
+        <v>0.345</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>0.0234</v>
+        <v>0.06150000000000001</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>56194900</v>
+        <v>58586400</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.78</v>
+        <v>1.09</v>
       </c>
       <c r="H5" t="n">
-        <v>70.47</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="I5" s="16" t="inlineStr">
         <is>
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.775</v>
+        <v>0.273</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.707</v>
+        <v>0.242</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="14" t="inlineStr"/>
@@ -760,10 +760,10 @@
         <v>0.0571</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>38479300</v>
+        <v>40170800</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="H6" t="n">
         <v>62.96</v>
@@ -805,10 +805,10 @@
         <v>0.0323</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>33198400</v>
+        <v>35297200</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="H7" t="n">
         <v>66.48999999999999</v>
@@ -844,19 +844,19 @@
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.6</v>
+        <v>0.595</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>0.0169</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>18561300</v>
+        <v>20292300</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
       <c r="H8" t="n">
-        <v>66.04000000000001</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="I8" s="16" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.577</v>
+        <v>0.576</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>0.503</v>
@@ -880,28 +880,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>-0.0112</v>
+        <v>0.39</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>-0.0127</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>16132300</v>
+        <v>19885100</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.62</v>
+        <v>0.47</v>
       </c>
       <c r="H9" t="n">
-        <v>62.69</v>
+        <v>70.12</v>
       </c>
       <c r="I9" s="16" t="inlineStr">
         <is>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.407</v>
+        <v>0.355</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.345</v>
+        <v>0.234</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -925,28 +925,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E10" s="17" t="n">
-        <v>0</v>
+        <v>0.45</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>0.0112</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>15644000</v>
+        <v>19692500</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.37</v>
+        <v>0.76</v>
       </c>
       <c r="H10" t="n">
-        <v>72.45999999999999</v>
+        <v>65.29000000000001</v>
       </c>
       <c r="I10" s="16" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.355</v>
+        <v>0.408</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.234</v>
+        <v>0.345</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -970,28 +970,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>0.0337</v>
+        <v>0.505</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>-0.0098</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>12636000</v>
+        <v>14044500</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1.94</v>
+        <v>0.52</v>
       </c>
       <c r="H11" t="n">
-        <v>62.6</v>
+        <v>59.22</v>
       </c>
       <c r="I11" s="16" t="inlineStr">
         <is>
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.423</v>
+        <v>0.486</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.412</v>
+        <v>0.479</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1015,28 +1015,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>0</v>
+        <v>0.46</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>0.0337</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>11858900</v>
+        <v>12980400</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.44</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>61.53</v>
+        <v>62.6</v>
       </c>
       <c r="I12" s="16" t="inlineStr">
         <is>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.486</v>
+        <v>0.423</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.479</v>
+        <v>0.412</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1060,28 +1060,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.155</v>
+        <v>4.92</v>
       </c>
       <c r="E13" s="17" t="n">
-        <v>0</v>
+        <v>-0.0315</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>10850800</v>
+        <v>11752600</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.36</v>
+        <v>0.47</v>
       </c>
       <c r="H13" t="n">
-        <v>46.33</v>
+        <v>54</v>
       </c>
       <c r="I13" s="16" t="inlineStr">
         <is>
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.156</v>
+        <v>4.906</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.157</v>
+        <v>4.644</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1105,33 +1105,40 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SLGC Berhad</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.25</v>
+        <v>0.155</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>-0.0196</v>
+        <v>0</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>10252500</v>
+        <v>11721600</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.17</v>
+        <v>0.39</v>
+      </c>
+      <c r="H14" t="n">
+        <v>46.33</v>
       </c>
       <c r="I14" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J14" s="9" t="n"/>
-      <c r="K14" s="9" t="n"/>
+      <c r="J14" s="9" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>0.157</v>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
     </row>
@@ -1158,10 +1165,10 @@
         <v>0.019</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>10224500</v>
+        <v>11210400</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="H15" t="n">
         <v>55.08</v>
@@ -1188,39 +1195,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.195</v>
+        <v>0.78</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>-0.025</v>
+        <v>0</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>9648600</v>
+        <v>11069700</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.4</v>
+        <v>0.76</v>
       </c>
       <c r="H16" t="n">
-        <v>50.82</v>
-      </c>
-      <c r="I16" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.15</v>
+      </c>
+      <c r="I16" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.196</v>
+        <v>0.776</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.183</v>
+        <v>0.776</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1233,28 +1240,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E17" s="17" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="E17" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>9450200</v>
+        <v>10461800</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.65</v>
+        <v>0.55</v>
       </c>
       <c r="H17" t="n">
-        <v>53.15</v>
+        <v>57.61</v>
       </c>
       <c r="I17" s="16" t="inlineStr">
         <is>
@@ -1262,10 +1269,10 @@
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.776</v>
+        <v>0.305</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.776</v>
+        <v>0.295</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1278,40 +1285,33 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>SLGC Berhad</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>-0.0295</v>
+        <v>0.25</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>-0.0196</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>8733300</v>
+        <v>10344500</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="H18" t="n">
-        <v>54.56</v>
+        <v>0.18</v>
       </c>
       <c r="I18" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J18" s="9" t="n">
-        <v>4.907</v>
-      </c>
-      <c r="K18" s="9" t="n">
-        <v>4.644</v>
-      </c>
+      <c r="J18" s="9" t="n"/>
+      <c r="K18" s="9" t="n"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
     </row>
@@ -1323,39 +1323,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.31</v>
+        <v>0.195</v>
       </c>
       <c r="E19" s="17" t="n">
-        <v>0</v>
+        <v>-0.025</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>8626800</v>
+        <v>10230800</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="H19" t="n">
-        <v>57.61</v>
-      </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.82</v>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.305</v>
+        <v>0.196</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.295</v>
+        <v>0.183</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.99</v>
+        <v>1.06</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>0.2147</v>
+        <v>0.3006</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>7792800</v>
+        <v>9080400</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>2.81</v>
+        <v>3.27</v>
       </c>
       <c r="H20" t="n">
-        <v>86.29000000000001</v>
+        <v>87.72</v>
       </c>
       <c r="I20" s="16" t="inlineStr">
         <is>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.622</v>
+        <v>0.629</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.469</v>
+        <v>0.47</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1413,28 +1413,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>1.08</v>
+        <v>0.785</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>0.009300000000000001</v>
+        <v>0.068</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>7543800</v>
+        <v>8916900</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.53</v>
+        <v>5.4</v>
       </c>
       <c r="H21" t="n">
-        <v>52.01</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="I21" s="16" t="inlineStr">
         <is>
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>1.073</v>
+        <v>0.663</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>1.035</v>
+        <v>0.618</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1467,19 +1467,19 @@
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="E22" s="10" t="n">
-        <v>-0.0216</v>
+        <v>2.74</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>-0.0144</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>7327600</v>
+        <v>8325000</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.43</v>
+        <v>0.48</v>
       </c>
       <c r="H22" t="n">
-        <v>59.7</v>
+        <v>61.35</v>
       </c>
       <c r="I22" s="16" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>2.609</v>
+        <v>2.61</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>2.5</v>
@@ -1503,28 +1503,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.795</v>
+        <v>1.1</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.028</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>7316700</v>
+        <v>7920200</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>4.43</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>80.48999999999999</v>
+        <v>54.66</v>
       </c>
       <c r="I23" s="16" t="inlineStr">
         <is>
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.664</v>
+        <v>1.075</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.618</v>
+        <v>1.036</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1548,33 +1548,40 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0473</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>EVOCOM</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E24" s="15" t="n">
-        <v>0.09519999999999999</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>7053700</v>
+        <v>7769100</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.4</v>
+        <v>0.49</v>
+      </c>
+      <c r="H24" t="n">
+        <v>50.2</v>
       </c>
       <c r="I24" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J24" s="9" t="n"/>
-      <c r="K24" s="9" t="n"/>
+      <c r="J24" s="9" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="K24" s="9" t="n">
+        <v>0.8070000000000001</v>
+      </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
     </row>
@@ -1586,40 +1593,33 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SYSTECH</t>
+          <t>EVOCOM</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.19</v>
+        <v>0.11</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>0.0857</v>
+        <v>0.0476</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>6515900</v>
+        <v>7497700</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="H25" t="n">
-        <v>67.62</v>
-      </c>
-      <c r="I25" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J25" s="9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="K25" s="9" t="n">
-        <v>0.165</v>
-      </c>
+        <v>0.43</v>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="n"/>
+      <c r="K25" s="9" t="n"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
     </row>
@@ -1631,39 +1631,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>6399</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ASTRO</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>-0.0833</v>
+        <v>0.865</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>6361300</v>
+        <v>7482900</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="H26" t="n">
-        <v>44.04</v>
-      </c>
-      <c r="I26" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.72</v>
+      </c>
+      <c r="I26" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.058</v>
+        <v>0.868</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.06</v>
+        <v>0.869</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1676,28 +1676,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>SYSTECH</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>-0.031</v>
+        <v>0.19</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>0.0857</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>6089400</v>
+        <v>7429900</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.31</v>
+        <v>1.46</v>
       </c>
       <c r="H27" t="n">
-        <v>62.14</v>
+        <v>67.62</v>
       </c>
       <c r="I27" s="16" t="inlineStr">
         <is>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.576</v>
+        <v>0.165</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.516</v>
+        <v>0.165</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1721,28 +1721,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>6399</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>ASTRO</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="E28" s="10" t="n">
-        <v>-0.0022</v>
+        <v>0.055</v>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>-0.0833</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>6068900</v>
+        <v>6975300</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.38</v>
+        <v>2.74</v>
       </c>
       <c r="H28" t="n">
-        <v>27.42</v>
+        <v>44.04</v>
       </c>
       <c r="I28" s="13" t="inlineStr">
         <is>
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>4.739</v>
+        <v>0.058</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>4.896</v>
+        <v>0.06</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1766,28 +1766,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>7.19</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>-0.0191</v>
+        <v>4.56</v>
+      </c>
+      <c r="E29" s="17" t="n">
+        <v>-0.006500000000000001</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>5945800</v>
+        <v>6919500</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="H29" t="n">
-        <v>29.57</v>
+        <v>26.26</v>
       </c>
       <c r="I29" s="13" t="inlineStr">
         <is>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>7.674</v>
+        <v>4.737</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>7.741</v>
+        <v>4.896</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1811,28 +1811,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.54</v>
+        <v>1.2</v>
       </c>
       <c r="E30" s="15" t="n">
-        <v>0.0588</v>
+        <v>0.0435</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>5895300</v>
+        <v>6600500</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>1.49</v>
+        <v>0.58</v>
       </c>
       <c r="H30" t="n">
-        <v>70.44</v>
+        <v>54.81</v>
       </c>
       <c r="I30" s="16" t="inlineStr">
         <is>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.469</v>
+        <v>1.167</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.45</v>
+        <v>1.12</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1856,28 +1856,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E31" s="15" t="n">
-        <v>0.0435</v>
+        <v>0.635</v>
+      </c>
+      <c r="E31" s="17" t="n">
+        <v>-0.0155</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>5728900</v>
+        <v>6525400</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.51</v>
+        <v>0.33</v>
       </c>
       <c r="H31" t="n">
-        <v>54.81</v>
+        <v>64.39</v>
       </c>
       <c r="I31" s="16" t="inlineStr">
         <is>
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>1.167</v>
+        <v>0.577</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>1.12</v>
+        <v>0.516</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1901,28 +1901,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>7.19</v>
       </c>
       <c r="E32" s="17" t="n">
-        <v>0</v>
+        <v>-0.0191</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>5714700</v>
+        <v>6446000</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.36</v>
+        <v>0.48</v>
       </c>
       <c r="H32" t="n">
-        <v>50.2</v>
+        <v>29.57</v>
       </c>
       <c r="I32" s="13" t="inlineStr">
         <is>
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>7.674</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.8070000000000001</v>
+        <v>7.741</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1946,28 +1946,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0131</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DFX</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="E33" s="10" t="n">
-        <v>-0.0345</v>
+        <v>0.545</v>
+      </c>
+      <c r="E33" s="15" t="n">
+        <v>0.06860000000000001</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>5657500</v>
+        <v>6358800</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.75</v>
+        <v>1.61</v>
       </c>
       <c r="H33" t="n">
-        <v>70.08</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="I33" s="16" t="inlineStr">
         <is>
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.113</v>
+        <v>0.469</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.093</v>
+        <v>0.45</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -2000,19 +2000,19 @@
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.43</v>
+        <v>0.435</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>-0.0115</v>
+        <v>0</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>5475100</v>
+        <v>6324700</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.53</v>
+        <v>0.62</v>
       </c>
       <c r="H34" t="n">
-        <v>46.13</v>
+        <v>47.27</v>
       </c>
       <c r="I34" s="16" t="inlineStr">
         <is>
@@ -2036,28 +2036,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0131</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>DFX</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.14</v>
+      </c>
+      <c r="E35" s="17" t="n">
+        <v>-0.0345</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>5467500</v>
+        <v>6059500</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.29</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>46.72</v>
+        <v>70.08</v>
       </c>
       <c r="I35" s="16" t="inlineStr">
         <is>
@@ -2065,10 +2065,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.868</v>
+        <v>0.113</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.869</v>
+        <v>0.093</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2081,28 +2081,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.395</v>
+        <v>7.2</v>
       </c>
       <c r="E36" s="17" t="n">
-        <v>0</v>
+        <v>-0.0069</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>5319000</v>
+        <v>5963100</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.47</v>
+        <v>0.63</v>
       </c>
       <c r="H36" t="n">
-        <v>38.38</v>
+        <v>19.95</v>
       </c>
       <c r="I36" s="13" t="inlineStr">
         <is>
@@ -2110,10 +2110,10 @@
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.403</v>
+        <v>7.651</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.41</v>
+        <v>8.121</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2126,39 +2126,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.345</v>
+        <v>9.83</v>
       </c>
       <c r="E37" s="17" t="n">
-        <v>0</v>
+        <v>-0.004099999999999999</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>5114100</v>
+        <v>5618200</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.65</v>
+        <v>0.45</v>
       </c>
       <c r="H37" t="n">
-        <v>54.32</v>
-      </c>
-      <c r="I37" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.26</v>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.342</v>
+        <v>10.046</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.324</v>
+        <v>10.219</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2171,28 +2171,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>7.18</v>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>-0.0097</v>
+        <v>5.51</v>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>-0.0196</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>5003800</v>
+        <v>5493700</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.53</v>
+        <v>0.38</v>
       </c>
       <c r="H38" t="n">
-        <v>19.55</v>
+        <v>46.48</v>
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
@@ -2200,10 +2200,10 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>7.649</v>
+        <v>5.642</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>8.121</v>
+        <v>5.331</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2216,39 +2216,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>-0.0152</v>
+        <v>0.39</v>
+      </c>
+      <c r="E39" s="17" t="n">
+        <v>-0.0127</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>4906100</v>
+        <v>5388500</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>1.17</v>
+        <v>0.48</v>
       </c>
       <c r="H39" t="n">
-        <v>84.78</v>
-      </c>
-      <c r="I39" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.28</v>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.5</v>
+        <v>0.402</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.438</v>
+        <v>0.41</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2261,39 +2261,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>9.83</v>
+        <v>0.345</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>-0.004099999999999999</v>
+        <v>0</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>4563600</v>
+        <v>5288200</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.37</v>
+        <v>0.67</v>
       </c>
       <c r="H40" t="n">
-        <v>31.26</v>
-      </c>
-      <c r="I40" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.32</v>
+      </c>
+      <c r="I40" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>10.046</v>
+        <v>0.342</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>10.219</v>
+        <v>0.324</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2306,28 +2306,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TUNEPRO</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E41" s="15" t="n">
-        <v>0.0392</v>
+        <v>0.65</v>
+      </c>
+      <c r="E41" s="17" t="n">
+        <v>-0.0152</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>4390100</v>
+        <v>5162700</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>5.21</v>
+        <v>1.23</v>
       </c>
       <c r="H41" t="n">
-        <v>60.23</v>
+        <v>84.78</v>
       </c>
       <c r="I41" s="16" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.259</v>
+        <v>0.438</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2351,39 +2351,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="E42" s="10" t="n">
-        <v>-0.009300000000000001</v>
+        <v>0.635</v>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>-0.0155</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>4287900</v>
+        <v>5068000</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.29</v>
+        <v>1.39</v>
       </c>
       <c r="H42" t="n">
-        <v>39.95</v>
-      </c>
-      <c r="I42" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.62</v>
+      </c>
+      <c r="I42" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>2.235</v>
+        <v>0.591</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>2.227</v>
+        <v>0.581</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2396,28 +2396,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E43" s="10" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.29</v>
+      </c>
+      <c r="E43" s="17" t="n">
+        <v>-0.0333</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>4238500</v>
+        <v>4997300</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>1.16</v>
+        <v>0.36</v>
       </c>
       <c r="H43" t="n">
-        <v>55.55</v>
+        <v>50.77</v>
       </c>
       <c r="I43" s="16" t="inlineStr">
         <is>
@@ -2425,10 +2425,10 @@
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.631</v>
+        <v>0.291</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.6</v>
+        <v>0.28</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2441,39 +2441,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E44" s="15" t="n">
-        <v>0.0222</v>
+        <v>0.805</v>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>-0.0242</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>4185300</v>
+        <v>4908500</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.16</v>
+        <v>0.71</v>
       </c>
       <c r="H44" t="n">
-        <v>34.28</v>
-      </c>
-      <c r="I44" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.16</v>
+      </c>
+      <c r="I44" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.252</v>
+        <v>0.731</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.305</v>
+        <v>0.648</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2486,39 +2486,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>5.53</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>-0.016</v>
+        <v>0.64</v>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>4023900</v>
+        <v>4865200</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.28</v>
+        <v>1.33</v>
       </c>
       <c r="H45" t="n">
-        <v>47.25</v>
-      </c>
-      <c r="I45" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.55</v>
+      </c>
+      <c r="I45" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>5.644</v>
+        <v>0.631</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>5.332</v>
+        <v>0.6</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2531,39 +2531,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E46" s="15" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.515</v>
+      </c>
+      <c r="E46" s="17" t="n">
+        <v>-0.0283</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>3823100</v>
+        <v>4686800</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>1.05</v>
+        <v>0.28</v>
       </c>
       <c r="H46" t="n">
-        <v>66.64</v>
-      </c>
-      <c r="I46" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.15</v>
+      </c>
+      <c r="I46" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.593</v>
+        <v>0.511</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.581</v>
+        <v>0.436</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2576,28 +2576,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0209</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AIMFLEX</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="E47" s="10" t="n">
-        <v>-0.0455</v>
+        <v>2.13</v>
+      </c>
+      <c r="E47" s="17" t="n">
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>3559300</v>
+        <v>4678600</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.52</v>
+        <v>0.32</v>
       </c>
       <c r="H47" t="n">
-        <v>37.5</v>
+        <v>39.95</v>
       </c>
       <c r="I47" s="13" t="inlineStr">
         <is>
@@ -2605,10 +2605,10 @@
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.115</v>
+        <v>2.235</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.123</v>
+        <v>2.227</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2621,28 +2621,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>TUNEPRO</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E48" s="10" t="n">
-        <v>-0.0182</v>
+        <v>0.265</v>
+      </c>
+      <c r="E48" s="15" t="n">
+        <v>0.0392</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3475400</v>
+        <v>4395600</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.5</v>
+        <v>5.22</v>
       </c>
       <c r="H48" t="n">
-        <v>69.41</v>
+        <v>60.23</v>
       </c>
       <c r="I48" s="16" t="inlineStr">
         <is>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.732</v>
+        <v>0.25</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.649</v>
+        <v>0.259</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2666,39 +2666,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E49" s="15" t="n">
-        <v>0.0172</v>
+        <v>0.145</v>
+      </c>
+      <c r="E49" s="17" t="n">
+        <v>-0.0645</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>3419000</v>
+        <v>4251900</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>1.06</v>
+        <v>0.14</v>
       </c>
       <c r="H49" t="n">
-        <v>73.17</v>
-      </c>
-      <c r="I49" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.03</v>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.999</v>
+        <v>0.157</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.852</v>
+        <v>0.147</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2711,39 +2711,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E50" s="17" t="n">
-        <v>0</v>
+        <v>0.23</v>
+      </c>
+      <c r="E50" s="15" t="n">
+        <v>0.0222</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>3404700</v>
+        <v>4243500</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.74</v>
+        <v>0.16</v>
       </c>
       <c r="H50" t="n">
-        <v>47.06</v>
-      </c>
-      <c r="I50" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.28</v>
+      </c>
+      <c r="I50" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.208</v>
+        <v>0.252</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.209</v>
+        <v>0.305</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2756,28 +2756,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E51" s="17" t="n">
-        <v>0</v>
+        <v>1.17</v>
+      </c>
+      <c r="E51" s="15" t="n">
+        <v>0.0086</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>3303400</v>
+        <v>4190200</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.31</v>
+        <v>1.3</v>
       </c>
       <c r="H51" t="n">
-        <v>55.75</v>
+        <v>72.62</v>
       </c>
       <c r="I51" s="16" t="inlineStr">
         <is>
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.61</v>
+        <v>0.998</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.611</v>
+        <v>0.851</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2812,14 +2812,14 @@
       <c r="D52" s="9" t="n">
         <v>0.37</v>
       </c>
-      <c r="E52" s="17" t="n">
+      <c r="E52" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>3198300</v>
+        <v>4107300</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.47</v>
+        <v>0.61</v>
       </c>
       <c r="H52" t="n">
         <v>53.6</v>
@@ -2846,39 +2846,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.15</v>
+        <v>0.205</v>
       </c>
       <c r="E53" s="10" t="n">
-        <v>-0.0323</v>
+        <v>0</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>3076900</v>
+        <v>3975200</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.1</v>
+        <v>0.86</v>
       </c>
       <c r="H53" t="n">
-        <v>47.12</v>
-      </c>
-      <c r="I53" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.06</v>
+      </c>
+      <c r="I53" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.157</v>
+        <v>0.208</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.147</v>
+        <v>0.209</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2891,28 +2891,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.515</v>
+        <v>0.475</v>
       </c>
       <c r="E54" s="10" t="n">
-        <v>-0.0283</v>
+        <v>0</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>2975600</v>
+        <v>3959000</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="H54" t="n">
-        <v>54.15</v>
+        <v>26.61</v>
       </c>
       <c r="I54" s="13" t="inlineStr">
         <is>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.511</v>
+        <v>0.556</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.436</v>
+        <v>0.755</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2936,39 +2936,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.785</v>
+        <v>2.14</v>
       </c>
       <c r="E55" s="15" t="n">
-        <v>0.0064</v>
+        <v>0.0239</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>2866200</v>
+        <v>3682100</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.36</v>
+        <v>0.19</v>
       </c>
       <c r="H55" t="n">
-        <v>52.99</v>
-      </c>
-      <c r="I55" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.67</v>
+      </c>
+      <c r="I55" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.777</v>
+        <v>2.102</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.772</v>
+        <v>2.082</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2981,39 +2981,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0209</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>AIMFLEX</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E56" s="10" t="n">
-        <v>-0.0333</v>
+        <v>0.105</v>
+      </c>
+      <c r="E56" s="17" t="n">
+        <v>-0.0455</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>2771200</v>
+        <v>3586800</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.2</v>
+        <v>0.52</v>
       </c>
       <c r="H56" t="n">
-        <v>50.77</v>
-      </c>
-      <c r="I56" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.5</v>
+      </c>
+      <c r="I56" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.291</v>
+        <v>0.115</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.28</v>
+        <v>0.123</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3026,28 +3026,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>BNASTRA</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="E57" s="10" t="n">
-        <v>-0.0596</v>
+        <v>2.7</v>
+      </c>
+      <c r="E57" s="15" t="n">
+        <v>0.08</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>2709100</v>
+        <v>3426000</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.64</v>
+        <v>3.06</v>
       </c>
       <c r="H57" t="n">
-        <v>55.3</v>
+        <v>86.31</v>
       </c>
       <c r="I57" s="16" t="inlineStr">
         <is>
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>5.735</v>
+        <v>2.465</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>5.775</v>
+        <v>2.347</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3071,39 +3071,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>2.8</v>
+        <v>0.62</v>
       </c>
       <c r="E58" s="10" t="n">
-        <v>-0.0175</v>
+        <v>0</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>2700700</v>
+        <v>3303400</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.2</v>
+        <v>0.31</v>
       </c>
       <c r="H58" t="n">
-        <v>52.65</v>
-      </c>
-      <c r="I58" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.75</v>
+      </c>
+      <c r="I58" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>2.793</v>
+        <v>0.61</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>2.698</v>
+        <v>0.611</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3116,28 +3116,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="E59" s="10" t="n">
-        <v>-0.0208</v>
+        <v>0.8</v>
+      </c>
+      <c r="E59" s="17" t="n">
+        <v>-0.0244</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>2689000</v>
+        <v>3179800</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.29</v>
+        <v>0.23</v>
       </c>
       <c r="H59" t="n">
-        <v>61.86</v>
+        <v>58.49</v>
       </c>
       <c r="I59" s="16" t="inlineStr">
         <is>
@@ -3145,10 +3145,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.667</v>
+        <v>0.766</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0.603</v>
+        <v>0.711</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3161,39 +3161,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>7195</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>BNASTRA</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="E60" s="15" t="n">
-        <v>0.08400000000000001</v>
+        <v>6.1</v>
+      </c>
+      <c r="E60" s="17" t="n">
+        <v>-0.0129</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>2637900</v>
+        <v>3179100</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>2.36</v>
+        <v>0.73</v>
       </c>
       <c r="H60" t="n">
-        <v>86.66</v>
-      </c>
-      <c r="I60" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>22.76</v>
+      </c>
+      <c r="I60" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>2.466</v>
+        <v>6.512</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>2.348</v>
+        <v>6.852</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3206,28 +3206,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E61" s="10" t="n">
-        <v>-0.0268</v>
+        <v>6.06</v>
+      </c>
+      <c r="E61" s="17" t="n">
+        <v>-0.05019999999999999</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>2536800</v>
+        <v>3135900</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.25</v>
+        <v>0.74</v>
       </c>
       <c r="H61" t="n">
-        <v>60.11</v>
+        <v>56.52</v>
       </c>
       <c r="I61" s="16" t="inlineStr">
         <is>
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>1.064</v>
+        <v>5.74</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.912</v>
+        <v>5.776</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3251,39 +3251,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="E62" s="15" t="n">
-        <v>0.0394</v>
+        <v>0.78</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>2461800</v>
+        <v>3130700</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="H62" t="n">
-        <v>42.49</v>
-      </c>
-      <c r="I62" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.62</v>
+      </c>
+      <c r="I62" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>3.485</v>
+        <v>0.776</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>3.663</v>
+        <v>0.772</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3311,10 +3311,10 @@
         <v>0.027</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>2461400</v>
+        <v>3117900</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.28</v>
+        <v>0.36</v>
       </c>
       <c r="H63" t="n">
         <v>68.08</v>
@@ -3341,39 +3341,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>7943</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>UNISEM</t>
+          <t>GREENTEC</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="E64" s="10" t="n">
-        <v>-0.0273</v>
+        <v>0.3</v>
+      </c>
+      <c r="E64" s="17" t="n">
+        <v>-0.09089999999999999</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>2429000</v>
+        <v>3092700</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.82</v>
+        <v>3.98</v>
       </c>
       <c r="H64" t="n">
-        <v>47.22</v>
-      </c>
-      <c r="I64" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.48999999999999</v>
+      </c>
+      <c r="I64" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>4.34</v>
+        <v>0.237</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>4.359</v>
+        <v>0.203</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3386,40 +3386,36 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E65" s="17" t="n">
-        <v>0</v>
+        <v>0.26</v>
+      </c>
+      <c r="E65" s="15" t="n">
+        <v>0.0196</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>2358600</v>
+        <v>3020700</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.89</v>
+        <v>0.25</v>
       </c>
       <c r="H65" t="n">
-        <v>49.23</v>
+        <v>30.66</v>
       </c>
       <c r="I65" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J65" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="K65" s="9" t="n">
-        <v>0.296</v>
-      </c>
+      <c r="J65" s="9" t="n"/>
+      <c r="K65" s="9" t="n"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
     </row>
@@ -3431,39 +3427,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="E66" s="10" t="n">
-        <v>-0.03</v>
+        <v>0.7</v>
+      </c>
+      <c r="E66" s="17" t="n">
+        <v>-0.0278</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>2339900</v>
+        <v>3008200</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="H66" t="n">
-        <v>56.08</v>
-      </c>
-      <c r="I66" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.59</v>
+      </c>
+      <c r="I66" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.961</v>
+        <v>0.667</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.603</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3476,28 +3472,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="E67" s="10" t="n">
-        <v>-0.005699999999999999</v>
+        <v>2.79</v>
+      </c>
+      <c r="E67" s="17" t="n">
+        <v>-0.0211</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2318900</v>
+        <v>2980600</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.44</v>
+        <v>0.22</v>
       </c>
       <c r="H67" t="n">
-        <v>48.61</v>
+        <v>51.77</v>
       </c>
       <c r="I67" s="13" t="inlineStr">
         <is>
@@ -3505,10 +3501,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>1.752</v>
+        <v>2.792</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>1.781</v>
+        <v>2.698</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3521,28 +3517,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="E68" s="15" t="n">
-        <v>0.0162</v>
+        <v>1.09</v>
+      </c>
+      <c r="E68" s="17" t="n">
+        <v>-0.0268</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>2305000</v>
+        <v>2912600</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.57</v>
+        <v>0.29</v>
       </c>
       <c r="H68" t="n">
-        <v>39.34</v>
+        <v>60.11</v>
       </c>
       <c r="I68" s="16" t="inlineStr">
         <is>
@@ -3550,10 +3546,10 @@
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>3.193</v>
+        <v>1.064</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>3.393</v>
+        <v>0.912</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3566,28 +3562,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>CENSOF</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E69" s="10" t="n">
-        <v>-0.024</v>
+        <v>0.24</v>
+      </c>
+      <c r="E69" s="15" t="n">
+        <v>0.0213</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>2301500</v>
+        <v>2847400</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.35</v>
+        <v>2.6</v>
       </c>
       <c r="H69" t="n">
-        <v>69.2</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="I69" s="16" t="inlineStr">
         <is>
@@ -3595,10 +3591,10 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>0.739</v>
+        <v>0.218</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>0.659</v>
+        <v>0.205</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3611,39 +3607,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ITMAX</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="E70" s="10" t="n">
-        <v>-0.0213</v>
+        <v>3.41</v>
+      </c>
+      <c r="E70" s="15" t="n">
+        <v>0.0333</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>2288000</v>
+        <v>2840000</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>1.07</v>
+        <v>0.46</v>
       </c>
       <c r="H70" t="n">
-        <v>55.14</v>
-      </c>
-      <c r="I70" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.77</v>
+      </c>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>4.534</v>
+        <v>3.484</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>4.488</v>
+        <v>3.663</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3656,28 +3652,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.7</v>
+        <v>0.34</v>
       </c>
       <c r="E71" s="10" t="n">
-        <v>-0.0071</v>
+        <v>0</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>2277100</v>
+        <v>2836900</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.29</v>
+        <v>0.51</v>
       </c>
       <c r="H71" t="n">
-        <v>53.39</v>
+        <v>57.95</v>
       </c>
       <c r="I71" s="16" t="inlineStr">
         <is>
@@ -3685,10 +3681,10 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.326</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.678</v>
+        <v>0.339</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3701,28 +3697,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>GREENTEC</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="E72" s="10" t="n">
-        <v>-0.0455</v>
+        <v>3.11</v>
+      </c>
+      <c r="E72" s="15" t="n">
+        <v>0.0097</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>2265500</v>
+        <v>2772700</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>2.92</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H72" t="n">
-        <v>83.75</v>
+        <v>36.93</v>
       </c>
       <c r="I72" s="16" t="inlineStr">
         <is>
@@ -3730,10 +3726,10 @@
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.239</v>
+        <v>3.191</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0.203</v>
+        <v>3.393</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3755,19 +3751,19 @@
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="E73" s="10" t="n">
-        <v>-0.0461</v>
+        <v>2.7</v>
+      </c>
+      <c r="E73" s="17" t="n">
+        <v>-0.0426</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>2246600</v>
+        <v>2666300</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.4</v>
+        <v>0.48</v>
       </c>
       <c r="H73" t="n">
-        <v>56.84</v>
+        <v>57.73</v>
       </c>
       <c r="I73" s="16" t="inlineStr">
         <is>
@@ -3775,7 +3771,7 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>2.622</v>
+        <v>2.623</v>
       </c>
       <c r="K73" s="9" t="n">
         <v>2.579</v>
@@ -3791,39 +3787,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0.475</v>
+        <v>0.7</v>
       </c>
       <c r="E74" s="17" t="n">
-        <v>0</v>
+        <v>-0.0071</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>2243500</v>
+        <v>2616400</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.06</v>
+        <v>0.33</v>
       </c>
       <c r="H74" t="n">
-        <v>26.61</v>
-      </c>
-      <c r="I74" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.39</v>
+      </c>
+      <c r="I74" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>0.556</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>0.755</v>
+        <v>0.678</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3847,14 +3843,14 @@
       <c r="D75" s="9" t="n">
         <v>0.805</v>
       </c>
-      <c r="E75" s="17" t="n">
+      <c r="E75" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>2241800</v>
+        <v>2587700</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="H75" t="n">
         <v>70.23</v>
@@ -3881,28 +3877,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.49</v>
+        <v>0.985</v>
       </c>
       <c r="E76" s="17" t="n">
-        <v>0</v>
+        <v>-0.015</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>2239700</v>
+        <v>2564400</v>
       </c>
       <c r="G76" s="12" t="n">
         <v>0.31</v>
       </c>
       <c r="H76" t="n">
-        <v>26.21</v>
+        <v>58.55</v>
       </c>
       <c r="I76" s="13" t="inlineStr">
         <is>
@@ -3910,10 +3906,10 @@
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.528</v>
+        <v>0.963</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.573</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3926,39 +3922,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.34</v>
+        <v>0.91</v>
       </c>
       <c r="E77" s="17" t="n">
-        <v>0</v>
+        <v>-0.0215</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>2203600</v>
+        <v>2496200</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.39</v>
+        <v>0.47</v>
       </c>
       <c r="H77" t="n">
-        <v>57.95</v>
-      </c>
-      <c r="I77" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.18</v>
+      </c>
+      <c r="I77" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.326</v>
+        <v>0.904</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.339</v>
+        <v>0.861</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3971,39 +3967,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>7173</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>TOYOVEN</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E78" s="15" t="n">
-        <v>0.1282</v>
+        <v>5.96</v>
+      </c>
+      <c r="E78" s="17" t="n">
+        <v>-0.0116</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>2185600</v>
+        <v>2479700</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>15.8</v>
+        <v>0.19</v>
       </c>
       <c r="H78" t="n">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="I78" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.8</v>
+      </c>
+      <c r="I78" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.2</v>
+        <v>6.172</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.206</v>
+        <v>6.406</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4016,39 +4012,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>UNISEM</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E79" s="15" t="n">
-        <v>0.0345</v>
+        <v>4.26</v>
+      </c>
+      <c r="E79" s="17" t="n">
+        <v>-0.0318</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>2162400</v>
+        <v>2452500</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.28</v>
+        <v>0.83</v>
       </c>
       <c r="H79" t="n">
-        <v>65.72</v>
-      </c>
-      <c r="I79" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.5</v>
+      </c>
+      <c r="I79" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>1.065</v>
+        <v>4.338</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.819</v>
+        <v>4.358</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4061,28 +4057,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E80" s="10" t="n">
-        <v>-0.0373</v>
+        <v>1.75</v>
+      </c>
+      <c r="E80" s="17" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>2138700</v>
+        <v>2400200</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.77</v>
+        <v>0.46</v>
       </c>
       <c r="H80" t="n">
-        <v>45.59</v>
+        <v>48.61</v>
       </c>
       <c r="I80" s="13" t="inlineStr">
         <is>
@@ -4090,10 +4086,10 @@
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>1.347</v>
+        <v>1.752</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>1.231</v>
+        <v>1.781</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4106,28 +4102,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.345</v>
+        <v>1.31</v>
       </c>
       <c r="E81" s="17" t="n">
-        <v>0</v>
+        <v>-0.0224</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>2110900</v>
+        <v>2384900</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.55</v>
+        <v>0.85</v>
       </c>
       <c r="H81" t="n">
-        <v>33.93</v>
+        <v>47.72</v>
       </c>
       <c r="I81" s="13" t="inlineStr">
         <is>
@@ -4135,10 +4131,10 @@
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>0.365</v>
+        <v>1.349</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0.385</v>
+        <v>1.232</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4151,25 +4147,25 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0396</t>
+          <t>7173</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ADNEX</t>
+          <t>TOYOVEN</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.46</v>
+        <v>0.22</v>
       </c>
       <c r="E82" s="15" t="n">
-        <v>0.0222</v>
+        <v>0.1282</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>2043500</v>
+        <v>2372600</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>3.85</v>
+        <v>17.15</v>
       </c>
       <c r="H82" t="n">
         <v>67.59999999999999</v>
@@ -4180,10 +4176,10 @@
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.43</v>
+        <v>0.2</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.42</v>
+        <v>0.206</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4196,39 +4192,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="E83" s="10" t="n">
-        <v>-0.0129</v>
+        <v>0.595</v>
+      </c>
+      <c r="E83" s="17" t="n">
+        <v>-0.0083</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>2041400</v>
+        <v>2371000</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="H83" t="n">
-        <v>22.76</v>
-      </c>
-      <c r="I83" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.73</v>
+      </c>
+      <c r="I83" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>6.512</v>
+        <v>0.544</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>6.852</v>
+        <v>0.493</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4241,39 +4237,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>5.97</v>
-      </c>
-      <c r="E84" s="10" t="n">
-        <v>-0.01</v>
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E84" s="17" t="n">
+        <v>-0.024</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>1995900</v>
+        <v>2362900</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.16</v>
+        <v>0.35</v>
       </c>
       <c r="H84" t="n">
-        <v>35.19</v>
-      </c>
-      <c r="I84" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.2</v>
+      </c>
+      <c r="I84" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>6.173</v>
+        <v>0.739</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>6.407</v>
+        <v>0.659</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4286,28 +4282,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="E85" s="15" t="n">
-        <v>0.0217</v>
+        <v>0.295</v>
+      </c>
+      <c r="E85" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>1972200</v>
+        <v>2358600</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="H85" t="n">
-        <v>73.86</v>
+        <v>49.23</v>
       </c>
       <c r="I85" s="16" t="inlineStr">
         <is>
@@ -4315,10 +4311,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>2.614</v>
+        <v>0.295</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>2.273</v>
+        <v>0.296</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4331,39 +4327,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="E86" s="10" t="n">
-        <v>-0.0423</v>
+        <v>1.2</v>
+      </c>
+      <c r="E86" s="15" t="n">
+        <v>0.0345</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>1860200</v>
+        <v>2356000</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.57</v>
+        <v>0.31</v>
       </c>
       <c r="H86" t="n">
-        <v>70.73</v>
-      </c>
-      <c r="I86" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.72</v>
+      </c>
+      <c r="I86" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>1.222</v>
+        <v>1.065</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.999</v>
+        <v>0.819</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4376,39 +4372,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="E87" s="15" t="n">
-        <v>0.029</v>
+        <v>0.74</v>
+      </c>
+      <c r="E87" s="17" t="n">
+        <v>-0.0327</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1845900</v>
+        <v>2349800</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>1.45</v>
+        <v>0.75</v>
       </c>
       <c r="H87" t="n">
-        <v>57.46</v>
-      </c>
-      <c r="I87" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.49</v>
+      </c>
+      <c r="I87" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>0.339</v>
+        <v>0.764</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>0.345</v>
+        <v>0.747</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4421,39 +4417,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>1.29</v>
+        <v>12.94</v>
       </c>
       <c r="E88" s="15" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.0062</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>1818200</v>
+        <v>2348600</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.15</v>
+        <v>0.27</v>
       </c>
       <c r="H88" t="n">
-        <v>44.27</v>
-      </c>
-      <c r="I88" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.24</v>
+      </c>
+      <c r="I88" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>1.329</v>
+        <v>13.045</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>1.309</v>
+        <v>13.586</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4466,39 +4462,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>ITMAX</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E89" s="15" t="n">
-        <v>0.009399999999999999</v>
+        <v>4.6</v>
+      </c>
+      <c r="E89" s="17" t="n">
+        <v>-0.0192</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1798300</v>
+        <v>2337700</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.49</v>
+        <v>1.1</v>
       </c>
       <c r="H89" t="n">
-        <v>35.53</v>
-      </c>
-      <c r="I89" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.91</v>
+      </c>
+      <c r="I89" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.554</v>
+        <v>4.535</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0.583</v>
+        <v>4.488</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4511,39 +4507,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.595</v>
+        <v>0.49</v>
       </c>
       <c r="E90" s="10" t="n">
-        <v>-0.0083</v>
+        <v>0</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1797000</v>
+        <v>2327400</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="H90" t="n">
-        <v>68.73</v>
-      </c>
-      <c r="I90" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.21</v>
+      </c>
+      <c r="I90" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.544</v>
+        <v>0.528</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.493</v>
+        <v>0.573</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4556,39 +4552,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E91" s="17" t="n">
-        <v>0</v>
+        <v>0.35</v>
+      </c>
+      <c r="E91" s="15" t="n">
+        <v>0.0145</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1793800</v>
+        <v>2190600</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.18</v>
+        <v>0.57</v>
       </c>
       <c r="H91" t="n">
-        <v>55.35</v>
-      </c>
-      <c r="I91" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.71</v>
+      </c>
+      <c r="I91" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>0.276</v>
+        <v>0.366</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>0.304</v>
+        <v>0.385</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4601,39 +4597,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>ALPHA</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.735</v>
+        <v>0.28</v>
       </c>
       <c r="E92" s="10" t="n">
-        <v>-0.0392</v>
+        <v>0</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1773700</v>
+        <v>2177600</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.57</v>
+        <v>0.93</v>
       </c>
       <c r="H92" t="n">
-        <v>44.6</v>
-      </c>
-      <c r="I92" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.48999999999999</v>
+      </c>
+      <c r="I92" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>0.763</v>
+        <v>0.258</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>0.747</v>
+        <v>0.257</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4646,39 +4642,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0148</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>SUNZEN</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E93" s="15" t="n">
-        <v>0.0444</v>
+        <v>1.35</v>
+      </c>
+      <c r="E93" s="17" t="n">
+        <v>-0.0493</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1761400</v>
+        <v>2171200</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>7.65</v>
+        <v>0.67</v>
       </c>
       <c r="H93" t="n">
-        <v>65.84</v>
-      </c>
-      <c r="I93" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>69.34999999999999</v>
+      </c>
+      <c r="I93" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>0.226</v>
+        <v>1.221</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0.225</v>
+        <v>0.999</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4691,36 +4687,40 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E94" s="15" t="n">
-        <v>0.0392</v>
+        <v>4.21</v>
+      </c>
+      <c r="E94" s="17" t="n">
+        <v>-0.0024</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1730400</v>
+        <v>2116300</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.14</v>
+        <v>0.27</v>
       </c>
       <c r="H94" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="I94" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J94" s="9" t="n"/>
-      <c r="K94" s="9" t="n"/>
+        <v>42.51</v>
+      </c>
+      <c r="I94" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J94" s="9" t="n">
+        <v>4.377</v>
+      </c>
+      <c r="K94" s="9" t="n">
+        <v>4.462</v>
+      </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
     </row>
@@ -4732,39 +4732,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="E95" s="17" t="n">
-        <v>0</v>
+        <v>0.295</v>
+      </c>
+      <c r="E95" s="15" t="n">
+        <v>0.0172</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1715300</v>
+        <v>2086700</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.79</v>
+        <v>0.21</v>
       </c>
       <c r="H95" t="n">
-        <v>28.24</v>
-      </c>
-      <c r="I95" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.32</v>
+      </c>
+      <c r="I95" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>1.509</v>
+        <v>0.277</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>1.623</v>
+        <v>0.304</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4777,28 +4777,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0396</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>ADNEX</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E96" s="10" t="n">
-        <v>-0.0244</v>
+        <v>0.455</v>
+      </c>
+      <c r="E96" s="15" t="n">
+        <v>0.0111</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1700900</v>
+        <v>2082200</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.12</v>
+        <v>3.93</v>
       </c>
       <c r="H96" t="n">
-        <v>58.49</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="I96" s="16" t="inlineStr">
         <is>
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.766</v>
+        <v>0.43</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.711</v>
+        <v>0.42</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4822,28 +4822,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="E97" s="10" t="n">
-        <v>-0.0208</v>
+        <v>0.36</v>
+      </c>
+      <c r="E97" s="15" t="n">
+        <v>0.0435</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1677500</v>
+        <v>2075400</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.17</v>
+        <v>1.63</v>
       </c>
       <c r="H97" t="n">
-        <v>56.13</v>
+        <v>59.28</v>
       </c>
       <c r="I97" s="16" t="inlineStr">
         <is>
@@ -4851,10 +4851,10 @@
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>2.769</v>
+        <v>0.34</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>2.593</v>
+        <v>0.345</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4867,39 +4867,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="E98" s="10" t="n">
-        <v>-0.03</v>
+        <v>4.31</v>
+      </c>
+      <c r="E98" s="15" t="n">
+        <v>0.006999999999999999</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1654100</v>
+        <v>2046800</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.53</v>
+        <v>0.4</v>
       </c>
       <c r="H98" t="n">
-        <v>54.58</v>
-      </c>
-      <c r="I98" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.22</v>
+      </c>
+      <c r="I98" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>3.854</v>
+        <v>4.501</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>3.56</v>
+        <v>4.854</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4912,39 +4912,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="E99" s="10" t="n">
-        <v>-0.0245</v>
+        <v>2.81</v>
+      </c>
+      <c r="E99" s="15" t="n">
+        <v>0.0181</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1651300</v>
+        <v>2031200</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.24</v>
+        <v>0.65</v>
       </c>
       <c r="H99" t="n">
-        <v>32.99</v>
-      </c>
-      <c r="I99" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.44</v>
+      </c>
+      <c r="I99" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>1.674</v>
+        <v>2.613</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>1.79</v>
+        <v>2.273</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4957,28 +4957,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="E100" s="10" t="n">
-        <v>-0.008699999999999999</v>
+        <v>1.29</v>
+      </c>
+      <c r="E100" s="15" t="n">
+        <v>0.007800000000000001</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1618900</v>
+        <v>1975800</v>
       </c>
       <c r="G100" s="12" t="n">
         <v>0.17</v>
       </c>
       <c r="H100" t="n">
-        <v>40.64</v>
+        <v>44.27</v>
       </c>
       <c r="I100" s="13" t="inlineStr">
         <is>
@@ -4986,10 +4986,10 @@
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>4.689</v>
+        <v>1.329</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>4.628</v>
+        <v>1.309</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -5002,28 +5002,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E101" s="10" t="n">
-        <v>-0.0253</v>
+        <v>2.83</v>
+      </c>
+      <c r="E101" s="17" t="n">
+        <v>-0.0208</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1585900</v>
+        <v>1972100</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.13</v>
+        <v>0.21</v>
       </c>
       <c r="H101" t="n">
-        <v>51.59</v>
+        <v>56.13</v>
       </c>
       <c r="I101" s="16" t="inlineStr">
         <is>
@@ -5031,10 +5031,10 @@
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>0.385</v>
+        <v>2.769</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>0.375</v>
+        <v>2.593</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5047,39 +5047,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0148</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>SUNZEN</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>1.82</v>
+        <v>0.235</v>
       </c>
       <c r="E102" s="15" t="n">
-        <v>0.0111</v>
+        <v>0.0444</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1558000</v>
+        <v>1964900</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.35</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="H102" t="n">
-        <v>33.28</v>
-      </c>
-      <c r="I102" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.84</v>
+      </c>
+      <c r="I102" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>1.898</v>
+        <v>0.226</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>2.028</v>
+        <v>0.225</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5092,28 +5092,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>12.98</v>
-      </c>
-      <c r="E103" s="15" t="n">
-        <v>0.009300000000000001</v>
+        <v>0.475</v>
+      </c>
+      <c r="E103" s="17" t="n">
+        <v>-0.0104</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1528300</v>
+        <v>1963900</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.17</v>
+        <v>0.59</v>
       </c>
       <c r="H103" t="n">
-        <v>43.04</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="I103" s="16" t="inlineStr">
         <is>
@@ -5121,10 +5121,10 @@
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>13.049</v>
+        <v>0.414</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>13.586</v>
+        <v>0.367</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5137,39 +5137,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E104" s="10" t="n">
-        <v>-0.0167</v>
+        <v>4.58</v>
+      </c>
+      <c r="E104" s="17" t="n">
+        <v>-0.008699999999999999</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1527900</v>
+        <v>1893300</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="H104" t="n">
-        <v>59.8</v>
-      </c>
-      <c r="I104" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.64</v>
+      </c>
+      <c r="I104" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.288</v>
+        <v>4.689</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.274</v>
+        <v>4.628</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5182,39 +5182,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E105" s="10" t="n">
-        <v>-0.0379</v>
+        <v>2.95</v>
+      </c>
+      <c r="E105" s="17" t="n">
+        <v>-0.0453</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1512100</v>
+        <v>1882900</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.67</v>
+        <v>0.42</v>
       </c>
       <c r="H105" t="n">
-        <v>57.69</v>
-      </c>
-      <c r="I105" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.02</v>
+      </c>
+      <c r="I105" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>0.618</v>
+        <v>2.979</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0.526</v>
+        <v>2.821</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5227,39 +5227,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>ALPHA</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E106" s="17" t="n">
-        <v>0</v>
+        <v>0.535</v>
+      </c>
+      <c r="E106" s="15" t="n">
+        <v>0.009399999999999999</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1475900</v>
+        <v>1882200</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.63</v>
+        <v>0.52</v>
       </c>
       <c r="H106" t="n">
-        <v>68.48999999999999</v>
-      </c>
-      <c r="I106" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.53</v>
+      </c>
+      <c r="I106" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>0.258</v>
+        <v>0.554</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>0.257</v>
+        <v>0.583</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5272,28 +5272,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="E107" s="10" t="n">
-        <v>-0.0388</v>
+        <v>3.89</v>
+      </c>
+      <c r="E107" s="17" t="n">
+        <v>-0.0275</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1466600</v>
+        <v>1878200</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="H107" t="n">
-        <v>51.02</v>
+        <v>55.12</v>
       </c>
       <c r="I107" s="16" t="inlineStr">
         <is>
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>2.981</v>
+        <v>3.855</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>2.821</v>
+        <v>3.561</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5317,39 +5317,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="E108" s="15" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.3</v>
+      </c>
+      <c r="E108" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1463000</v>
+        <v>1877900</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
       <c r="H108" t="n">
-        <v>29.22</v>
-      </c>
-      <c r="I108" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.41</v>
+      </c>
+      <c r="I108" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>4.501</v>
+        <v>0.289</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>4.854</v>
+        <v>0.274</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5362,28 +5362,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1.15</v>
+        <v>1.45</v>
       </c>
       <c r="E109" s="10" t="n">
-        <v>-0.0417</v>
+        <v>0</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1410000</v>
+        <v>1857600</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.32</v>
+        <v>0.86</v>
       </c>
       <c r="H109" t="n">
-        <v>54.12</v>
+        <v>28.24</v>
       </c>
       <c r="I109" s="13" t="inlineStr">
         <is>
@@ -5391,10 +5391,10 @@
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>1.148</v>
+        <v>1.509</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>1.063</v>
+        <v>1.623</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5407,39 +5407,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>E&amp;O</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E110" s="10" t="n">
-        <v>-0.0104</v>
+        <v>0.76</v>
+      </c>
+      <c r="E110" s="17" t="n">
+        <v>-0.013</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1355500</v>
+        <v>1826100</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.41</v>
+        <v>1.16</v>
       </c>
       <c r="H110" t="n">
-        <v>73.43000000000001</v>
-      </c>
-      <c r="I110" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.45</v>
+      </c>
+      <c r="I110" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>0.414</v>
+        <v>0.771</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>0.367</v>
+        <v>0.768</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5452,39 +5452,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E111" s="17" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="E111" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1337900</v>
+        <v>1795400</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.32</v>
+        <v>0.22</v>
       </c>
       <c r="H111" t="n">
-        <v>66.14</v>
-      </c>
-      <c r="I111" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.11</v>
+      </c>
+      <c r="I111" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>0.248</v>
+        <v>3.942</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>0.218</v>
+        <v>3.421</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5497,28 +5497,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>4.16</v>
+        <v>0.27</v>
       </c>
       <c r="E112" s="10" t="n">
-        <v>-0.0142</v>
+        <v>0</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1337700</v>
+        <v>1739900</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.17</v>
+        <v>0.41</v>
       </c>
       <c r="H112" t="n">
-        <v>41.06</v>
+        <v>66.14</v>
       </c>
       <c r="I112" s="13" t="inlineStr">
         <is>
@@ -5526,10 +5526,10 @@
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>4.372</v>
+        <v>0.248</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>4.461</v>
+        <v>0.218</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5542,28 +5542,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>EMETALL</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>0.44</v>
+        <v>1.59</v>
       </c>
       <c r="E113" s="17" t="n">
-        <v>0</v>
+        <v>-0.0245</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1280700</v>
+        <v>1715200</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>2.93</v>
+        <v>0.25</v>
       </c>
       <c r="H113" t="n">
-        <v>57.26</v>
+        <v>32.99</v>
       </c>
       <c r="I113" s="13" t="inlineStr">
         <is>
@@ -5571,10 +5571,10 @@
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>0.44</v>
+        <v>1.674</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>0.437</v>
+        <v>1.79</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5587,39 +5587,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>0.92</v>
+        <v>0.395</v>
       </c>
       <c r="E114" s="10" t="n">
-        <v>-0.0108</v>
+        <v>0</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1276400</v>
+        <v>1704700</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.24</v>
+        <v>0.14</v>
       </c>
       <c r="H114" t="n">
-        <v>59.26</v>
-      </c>
-      <c r="I114" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.39</v>
+      </c>
+      <c r="I114" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>0.905</v>
+        <v>0.386</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>0.861</v>
+        <v>0.375</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5632,39 +5632,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="E115" s="10" t="n">
-        <v>-0.014</v>
+        <v>1.82</v>
+      </c>
+      <c r="E115" s="15" t="n">
+        <v>0.0111</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>1276200</v>
+        <v>1678200</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.45</v>
+        <v>0.37</v>
       </c>
       <c r="H115" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="I115" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.28</v>
+      </c>
+      <c r="I115" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>1.201</v>
+        <v>1.898</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>1.146</v>
+        <v>2.028</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5677,39 +5677,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>MFLOUR</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E116" s="10" t="n">
-        <v>-0.0167</v>
+        <v>7.82</v>
+      </c>
+      <c r="E116" s="17" t="n">
+        <v>-0.0274</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>1253600</v>
+        <v>1664400</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.41</v>
       </c>
       <c r="H116" t="n">
-        <v>32.88</v>
-      </c>
-      <c r="I116" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.29000000000001</v>
+      </c>
+      <c r="I116" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>0.619</v>
+        <v>7.154</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>0.638</v>
+        <v>6.729</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5722,39 +5722,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>IHH</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E117" s="15" t="n">
-        <v>0.0053</v>
+        <v>7.86</v>
+      </c>
+      <c r="E117" s="17" t="n">
+        <v>-0.0051</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>1215300</v>
+        <v>1664200</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="H117" t="n">
-        <v>43.29</v>
-      </c>
-      <c r="I117" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.47</v>
+      </c>
+      <c r="I117" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>1.93</v>
+        <v>7.862</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>1.958</v>
+        <v>8.013</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5767,39 +5767,39 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>7.83</v>
-      </c>
-      <c r="E118" s="10" t="n">
-        <v>-0.0261</v>
+        <v>0.635</v>
+      </c>
+      <c r="E118" s="17" t="n">
+        <v>-0.0379</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>1199100</v>
+        <v>1608900</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.3</v>
+        <v>0.72</v>
       </c>
       <c r="H118" t="n">
-        <v>68.58</v>
-      </c>
-      <c r="I118" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.69</v>
+      </c>
+      <c r="I118" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>7.155</v>
+        <v>0.618</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>6.729</v>
+        <v>0.526</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5812,28 +5812,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0023</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>IFCAMSC</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E119" s="10" t="n">
-        <v>-0.0244</v>
+        <v>1.16</v>
+      </c>
+      <c r="E119" s="17" t="n">
+        <v>-0.0333</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>1183600</v>
+        <v>1608600</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>2.13</v>
+        <v>0.37</v>
       </c>
       <c r="H119" t="n">
-        <v>41.38</v>
+        <v>56.1</v>
       </c>
       <c r="I119" s="13" t="inlineStr">
         <is>
@@ -5841,10 +5841,10 @@
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>0.204</v>
+        <v>1.149</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>0.214</v>
+        <v>1.063</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5857,28 +5857,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0285</t>
+          <t>7084</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>MERSEC</t>
+          <t>QL</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>0.27</v>
+        <v>3.91</v>
       </c>
       <c r="E120" s="17" t="n">
-        <v>0</v>
+        <v>-0.0051</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>1150000</v>
+        <v>1594700</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>1.13</v>
+        <v>0.83</v>
       </c>
       <c r="H120" t="n">
-        <v>41.34</v>
+        <v>48.59</v>
       </c>
       <c r="I120" s="13" t="inlineStr">
         <is>
@@ -5886,10 +5886,10 @@
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>0.274</v>
+        <v>3.931</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>0.276</v>
+        <v>3.931</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5902,28 +5902,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>1.24</v>
+        <v>3.55</v>
       </c>
       <c r="E121" s="15" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.0114</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>1147900</v>
+        <v>1580700</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="H121" t="n">
-        <v>33.99</v>
+        <v>53.62</v>
       </c>
       <c r="I121" s="13" t="inlineStr">
         <is>
@@ -5931,10 +5931,10 @@
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>1.289</v>
+        <v>3.57</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>1.389</v>
+        <v>2.71</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5947,39 +5947,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>TALIWRK</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E122" s="10" t="n">
-        <v>-0.0392</v>
+        <v>1.16</v>
+      </c>
+      <c r="E122" s="17" t="n">
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>1147900</v>
+        <v>1511300</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.46</v>
+        <v>0.31</v>
       </c>
       <c r="H122" t="n">
-        <v>43.51</v>
-      </c>
-      <c r="I122" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.98999999999999</v>
+      </c>
+      <c r="I122" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>0.253</v>
+        <v>1.053</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>0.262</v>
+        <v>0.886</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -5992,28 +5992,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>OSK</t>
+          <t>TIMECOM</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="E123" s="10" t="n">
-        <v>-0.0301</v>
+        <v>5.47</v>
+      </c>
+      <c r="E123" s="17" t="n">
+        <v>-0.0073</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>1138700</v>
+        <v>1505600</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.79</v>
+        <v>1.18</v>
       </c>
       <c r="H123" t="n">
-        <v>18.83</v>
+        <v>33.56</v>
       </c>
       <c r="I123" s="13" t="inlineStr">
         <is>
@@ -6021,10 +6021,10 @@
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>1.8</v>
+        <v>5.732</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>1.928</v>
+        <v>5.877</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6037,39 +6037,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>IHH</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>7.86</v>
-      </c>
-      <c r="E124" s="10" t="n">
-        <v>-0.0051</v>
+        <v>1.91</v>
+      </c>
+      <c r="E124" s="15" t="n">
+        <v>0.0106</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1134600</v>
+        <v>1470300</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.27</v>
+        <v>0.22</v>
       </c>
       <c r="H124" t="n">
-        <v>48.47</v>
-      </c>
-      <c r="I124" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.03</v>
+      </c>
+      <c r="I124" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>7.862</v>
+        <v>1.931</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>8.013</v>
+        <v>1.958</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6082,28 +6082,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E125" s="10" t="n">
-        <v>-0.0054</v>
+        <v>1.24</v>
+      </c>
+      <c r="E125" s="15" t="n">
+        <v>0.008100000000000001</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>1126500</v>
+        <v>1464300</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.6</v>
+        <v>0.15</v>
       </c>
       <c r="H125" t="n">
-        <v>28.85</v>
+        <v>33.99</v>
       </c>
       <c r="I125" s="13" t="inlineStr">
         <is>
@@ -6111,10 +6111,10 @@
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>0.965</v>
+        <v>1.289</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>0.994</v>
+        <v>1.389</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6127,28 +6127,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>2.1</v>
+        <v>2.51</v>
       </c>
       <c r="E126" s="15" t="n">
-        <v>0.0048</v>
+        <v>0.004</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>1099500</v>
+        <v>1449800</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="H126" t="n">
-        <v>50.56</v>
+        <v>59.5</v>
       </c>
       <c r="I126" s="13" t="inlineStr">
         <is>
@@ -6156,10 +6156,10 @@
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>2.098</v>
+        <v>2.464</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>2.081</v>
+        <v>2.351</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6172,28 +6172,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>OSK</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="E127" s="15" t="n">
-        <v>0.008500000000000001</v>
+        <v>1.62</v>
+      </c>
+      <c r="E127" s="17" t="n">
+        <v>-0.0241</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>1096700</v>
+        <v>1370300</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.09</v>
+        <v>0.96</v>
       </c>
       <c r="H127" t="n">
-        <v>53.39</v>
+        <v>19.34</v>
       </c>
       <c r="I127" s="13" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>3.569</v>
+        <v>1.801</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>2.71</v>
+        <v>1.928</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6217,28 +6217,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>7.13</v>
-      </c>
-      <c r="E128" s="10" t="n">
-        <v>-0.0097</v>
+        <v>0.92</v>
+      </c>
+      <c r="E128" s="17" t="n">
+        <v>-0.0054</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>1078100</v>
+        <v>1363500</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.14</v>
+        <v>0.73</v>
       </c>
       <c r="H128" t="n">
-        <v>29.53</v>
+        <v>28.85</v>
       </c>
       <c r="I128" s="13" t="inlineStr">
         <is>
@@ -6246,10 +6246,10 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>7.432</v>
+        <v>0.965</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>7.739</v>
+        <v>0.994</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6262,28 +6262,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>1.37</v>
+        <v>0.45</v>
       </c>
       <c r="E129" s="17" t="n">
-        <v>0</v>
+        <v>-0.0217</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>1074200</v>
+        <v>1353900</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.54</v>
+        <v>0.39</v>
       </c>
       <c r="H129" t="n">
-        <v>53.6</v>
+        <v>49.43</v>
       </c>
       <c r="I129" s="13" t="inlineStr">
         <is>
@@ -6291,10 +6291,10 @@
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>1.369</v>
+        <v>0.459</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>1.336</v>
+        <v>0.421</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6307,39 +6307,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="E130" s="17" t="n">
-        <v>0</v>
+        <v>-0.021</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>1065900</v>
+        <v>1330400</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.96</v>
+        <v>0.47</v>
       </c>
       <c r="H130" t="n">
-        <v>8.08</v>
-      </c>
-      <c r="I130" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.53</v>
+      </c>
+      <c r="I130" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>0.586</v>
+        <v>1.2</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>0.624</v>
+        <v>1.146</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6352,39 +6352,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>RANHILL</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="E131" s="10" t="n">
-        <v>-0.0201</v>
+        <v>3.31</v>
+      </c>
+      <c r="E131" s="17" t="n">
+        <v>-0.0178</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1065300</v>
+        <v>1327700</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.34</v>
+        <v>0.61</v>
       </c>
       <c r="H131" t="n">
-        <v>44.08</v>
-      </c>
-      <c r="I131" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.15000000000001</v>
+      </c>
+      <c r="I131" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>2.978</v>
+        <v>3.142</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>3.037</v>
+        <v>2.731</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6397,39 +6397,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>7252</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>TEOSENG</t>
+          <t>TALIWRK</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E132" s="10" t="n">
-        <v>-0.0179</v>
+        <v>0.245</v>
+      </c>
+      <c r="E132" s="17" t="n">
+        <v>-0.0392</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1062700</v>
+        <v>1325500</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>2.43</v>
+        <v>0.53</v>
       </c>
       <c r="H132" t="n">
-        <v>51.98</v>
-      </c>
-      <c r="I132" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.51</v>
+      </c>
+      <c r="I132" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>0.82</v>
+        <v>0.253</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>0.839</v>
+        <v>0.262</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6442,28 +6442,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>LCTITAN</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E133" s="10" t="n">
-        <v>-0.0303</v>
+        <v>2.93</v>
+      </c>
+      <c r="E133" s="17" t="n">
+        <v>-0.0168</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>1054900</v>
+        <v>1325300</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.5</v>
+        <v>0.42</v>
       </c>
       <c r="H133" t="n">
-        <v>42.35</v>
+        <v>44.84</v>
       </c>
       <c r="I133" s="13" t="inlineStr">
         <is>
@@ -6471,10 +6471,10 @@
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>0.333</v>
+        <v>2.979</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>0.33</v>
+        <v>3.037</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6487,28 +6487,28 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0358</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ICTZONE</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E134" s="15" t="n">
-        <v>0.009000000000000001</v>
+        <v>7.12</v>
+      </c>
+      <c r="E134" s="17" t="n">
+        <v>-0.0111</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>1046200</v>
+        <v>1318200</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.37</v>
+        <v>0.17</v>
       </c>
       <c r="H134" t="n">
-        <v>40.31</v>
+        <v>29.24</v>
       </c>
       <c r="I134" s="13" t="inlineStr">
         <is>
@@ -6516,10 +6516,10 @@
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>0.242</v>
+        <v>7.431</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>0.25</v>
+        <v>7.739</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6532,28 +6532,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>0.905</v>
+        <v>1.37</v>
       </c>
       <c r="E135" s="10" t="n">
-        <v>-0.0109</v>
+        <v>0</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>1039800</v>
+        <v>1286900</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.47</v>
+        <v>0.65</v>
       </c>
       <c r="H135" t="n">
-        <v>39.18</v>
+        <v>53.6</v>
       </c>
       <c r="I135" s="13" t="inlineStr">
         <is>
@@ -6561,10 +6561,10 @@
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>0.923</v>
+        <v>1.369</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>0.9370000000000001</v>
+        <v>1.336</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6577,39 +6577,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>EMETALL</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="E136" s="17" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E136" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>995900</v>
+        <v>1280700</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.12</v>
+        <v>2.93</v>
       </c>
       <c r="H136" t="n">
-        <v>65.11</v>
-      </c>
-      <c r="I136" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.26</v>
+      </c>
+      <c r="I136" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>3.942</v>
+        <v>0.44</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>3.421</v>
+        <v>0.437</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6631,19 +6631,19 @@
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="E137" s="17" t="n">
-        <v>0</v>
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E137" s="15" t="n">
+        <v>0.0054</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>995800</v>
+        <v>1266000</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.28</v>
+        <v>0.35</v>
       </c>
       <c r="H137" t="n">
-        <v>33.37</v>
+        <v>35.28</v>
       </c>
       <c r="I137" s="13" t="inlineStr">
         <is>
@@ -6667,28 +6667,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>MFLOUR</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E138" s="10" t="n">
-        <v>-0.0089</v>
+        <v>0.595</v>
+      </c>
+      <c r="E138" s="17" t="n">
+        <v>-0.0083</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>966600</v>
+        <v>1255600</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.23</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H138" t="n">
-        <v>32.96</v>
+        <v>34.54</v>
       </c>
       <c r="I138" s="13" t="inlineStr">
         <is>
@@ -6696,10 +6696,10 @@
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>0.573</v>
+        <v>0.62</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>0.583</v>
+        <v>0.638</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6712,28 +6712,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E139" s="10" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.55</v>
+      </c>
+      <c r="E139" s="17" t="n">
+        <v>-0.0265</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>953800</v>
+        <v>1219500</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.3</v>
+        <v>0.21</v>
       </c>
       <c r="H139" t="n">
-        <v>52.87</v>
+        <v>33.17</v>
       </c>
       <c r="I139" s="13" t="inlineStr">
         <is>
@@ -6741,10 +6741,10 @@
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>0.864</v>
+        <v>0.596</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>0.858</v>
+        <v>0.643</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6757,39 +6757,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E140" s="10" t="n">
-        <v>-0.0256</v>
+        <v>0.955</v>
+      </c>
+      <c r="E140" s="17" t="n">
+        <v>-0.0052</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>931900</v>
+        <v>1205900</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.19</v>
+        <v>0.29</v>
       </c>
       <c r="H140" t="n">
-        <v>71.20999999999999</v>
-      </c>
-      <c r="I140" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.52</v>
+      </c>
+      <c r="I140" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>1.051</v>
+        <v>1.002</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>0.886</v>
+        <v>1.074</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6802,39 +6802,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5142</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>WASCO</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>0.76</v>
+        <v>0.905</v>
       </c>
       <c r="E141" s="17" t="n">
-        <v>0</v>
+        <v>-0.0109</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>899800</v>
+        <v>1202200</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
       <c r="H141" t="n">
-        <v>58.59</v>
-      </c>
-      <c r="I141" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.18</v>
+      </c>
+      <c r="I141" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>0.734</v>
+        <v>0.923</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>0.722</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6847,39 +6847,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>7231</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>WELLCAL</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
         <v>1.12</v>
       </c>
       <c r="E142" s="10" t="n">
-        <v>-0.0175</v>
+        <v>0</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>899700</v>
+        <v>1200300</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>0.15</v>
+        <v>3.54</v>
       </c>
       <c r="H142" t="n">
-        <v>44.88</v>
-      </c>
-      <c r="I142" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.76</v>
+      </c>
+      <c r="I142" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>1.147</v>
+        <v>1.12</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>1.166</v>
+        <v>1.114</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6892,28 +6892,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="E143" s="15" t="n">
-        <v>0.004</v>
+        <v>1.12</v>
+      </c>
+      <c r="E143" s="17" t="n">
+        <v>-0.0175</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>874300</v>
+        <v>1197800</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>0.06</v>
+        <v>0.2</v>
       </c>
       <c r="H143" t="n">
-        <v>59.5</v>
+        <v>44.88</v>
       </c>
       <c r="I143" s="13" t="inlineStr">
         <is>
@@ -6921,10 +6921,10 @@
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>2.464</v>
+        <v>1.147</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>2.351</v>
+        <v>1.166</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6937,39 +6937,39 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0023</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>IFCAMSC</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E144" s="10" t="n">
-        <v>-0.0314</v>
+        <v>0.2</v>
+      </c>
+      <c r="E144" s="17" t="n">
+        <v>-0.0244</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>870000</v>
+        <v>1196600</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>0.49</v>
+        <v>2.15</v>
       </c>
       <c r="H144" t="n">
-        <v>63.96</v>
-      </c>
-      <c r="I144" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.38</v>
+      </c>
+      <c r="I144" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>0.707</v>
+        <v>0.204</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.214</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -6982,39 +6982,39 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0399</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E145" s="10" t="n">
-        <v>-0.012</v>
+        <v>0.475</v>
+      </c>
+      <c r="E145" s="17" t="n">
+        <v>-0.0206</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>847400</v>
+        <v>1188800</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.27</v>
+        <v>0.58</v>
       </c>
       <c r="H145" t="n">
-        <v>55.51</v>
-      </c>
-      <c r="I145" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.61</v>
+      </c>
+      <c r="I145" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.46</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>0.754</v>
+        <v>0.461</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7027,39 +7027,39 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0285</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>MERSEC</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>1.37</v>
+        <v>0.27</v>
       </c>
       <c r="E146" s="10" t="n">
-        <v>-0.0214</v>
+        <v>0</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>845900</v>
+        <v>1150000</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>0.21</v>
+        <v>1.13</v>
       </c>
       <c r="H146" t="n">
-        <v>60.26</v>
-      </c>
-      <c r="I146" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.34</v>
+      </c>
+      <c r="I146" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>1.292</v>
+        <v>0.274</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>1.192</v>
+        <v>0.276</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7072,39 +7072,39 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>5.91</v>
-      </c>
-      <c r="E147" s="10" t="n">
-        <v>-0.008399999999999999</v>
+        <v>2.06</v>
+      </c>
+      <c r="E147" s="17" t="n">
+        <v>-0.009599999999999999</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>812900</v>
+        <v>1122200</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>0.24</v>
+        <v>0.35</v>
       </c>
       <c r="H147" t="n">
-        <v>64.08</v>
-      </c>
-      <c r="I147" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.67</v>
+      </c>
+      <c r="I147" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>5.437</v>
+        <v>2.055</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>5.347</v>
+        <v>2.085</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7117,28 +7117,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>7252</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>TEOSENG</t>
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="E148" s="10" t="n">
-        <v>-0.0412</v>
+        <v>0.83</v>
+      </c>
+      <c r="E148" s="17" t="n">
+        <v>-0.0119</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>807200</v>
+        <v>1116900</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>0.26</v>
+        <v>2.56</v>
       </c>
       <c r="H148" t="n">
-        <v>65.29000000000001</v>
+        <v>54.32</v>
       </c>
       <c r="I148" s="16" t="inlineStr">
         <is>
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>2.981</v>
+        <v>0.82</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>2.794</v>
+        <v>0.839</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7162,28 +7162,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D149" s="9" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="E149" s="10" t="n">
-        <v>-0.0163</v>
+        <v>0.385</v>
+      </c>
+      <c r="E149" s="17" t="n">
+        <v>-0.0375</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>802200</v>
+        <v>1112900</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>0.2</v>
+        <v>0.57</v>
       </c>
       <c r="H149" t="n">
-        <v>69</v>
+        <v>49.76</v>
       </c>
       <c r="I149" s="16" t="inlineStr">
         <is>
@@ -7191,10 +7191,10 @@
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>2.657</v>
+        <v>0.385</v>
       </c>
       <c r="K149" s="9" t="n">
-        <v>2.016</v>
+        <v>0.39</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="14" t="inlineStr"/>
@@ -7207,28 +7207,28 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>7084</t>
+          <t>0358</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>QL</t>
+          <t>ICTZONE</t>
         </is>
       </c>
       <c r="D150" s="9" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="E150" s="10" t="n">
-        <v>-0.0102</v>
+        <v>0.225</v>
+      </c>
+      <c r="E150" s="15" t="n">
+        <v>0.009000000000000001</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>796500</v>
+        <v>1095500</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="H150" t="n">
-        <v>47.06</v>
+        <v>40.31</v>
       </c>
       <c r="I150" s="13" t="inlineStr">
         <is>
@@ -7236,10 +7236,10 @@
         </is>
       </c>
       <c r="J150" s="9" t="n">
-        <v>3.929</v>
+        <v>0.242</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>3.93</v>
+        <v>0.25</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -7252,28 +7252,28 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D151" s="9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E151" s="15" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.82</v>
+      </c>
+      <c r="E151" s="17" t="n">
+        <v>-0.018</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>769900</v>
+        <v>1071300</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>0.76</v>
+        <v>0.34</v>
       </c>
       <c r="H151" t="n">
-        <v>38.46</v>
+        <v>54.2</v>
       </c>
       <c r="I151" s="13" t="inlineStr">
         <is>
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>2.229</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>2.32</v>
+        <v>0.754</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="14" t="inlineStr"/>
@@ -7297,39 +7297,39 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>LCTITAN</t>
         </is>
       </c>
       <c r="D152" s="9" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="E152" s="10" t="n">
-        <v>-0.016</v>
+        <v>0.32</v>
+      </c>
+      <c r="E152" s="17" t="n">
+        <v>-0.0303</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>732100</v>
+        <v>1069900</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>0.18</v>
+        <v>0.5</v>
       </c>
       <c r="H152" t="n">
-        <v>50.32</v>
-      </c>
-      <c r="I152" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.35</v>
+      </c>
+      <c r="I152" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J152" s="9" t="n">
-        <v>0.615</v>
+        <v>0.333</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>0.609</v>
+        <v>0.33</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
@@ -7342,39 +7342,39 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>7134</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>PWF</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D153" s="9" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E153" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E153" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>719200</v>
+        <v>1065900</v>
       </c>
       <c r="G153" s="12" t="n">
-        <v>34.19</v>
+        <v>0.96</v>
       </c>
       <c r="H153" t="n">
-        <v>49.91</v>
-      </c>
-      <c r="I153" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>8.08</v>
+      </c>
+      <c r="I153" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J153" s="9" t="n">
-        <v>0.74</v>
+        <v>0.586</v>
       </c>
       <c r="K153" s="9" t="n">
-        <v>0.744</v>
+        <v>0.624</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="14" t="inlineStr"/>
@@ -7387,39 +7387,39 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>3417</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>E&amp;O</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D154" s="9" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="E154" s="10" t="n">
-        <v>-0.013</v>
+        <v>5.85</v>
+      </c>
+      <c r="E154" s="17" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>713700</v>
+        <v>1062900</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>0.45</v>
+        <v>0.31</v>
       </c>
       <c r="H154" t="n">
-        <v>44.45</v>
-      </c>
-      <c r="I154" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.19</v>
+      </c>
+      <c r="I154" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J154" s="9" t="n">
-        <v>0.771</v>
+        <v>5.431</v>
       </c>
       <c r="K154" s="9" t="n">
-        <v>0.768</v>
+        <v>5.346</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="14" t="inlineStr"/>
@@ -7432,39 +7432,39 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D155" s="9" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="E155" s="10" t="n">
-        <v>-0.0103</v>
+        <v>1.38</v>
+      </c>
+      <c r="E155" s="17" t="n">
+        <v>-0.0143</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>712800</v>
+        <v>1016900</v>
       </c>
       <c r="G155" s="12" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="H155" t="n">
-        <v>24.25</v>
-      </c>
-      <c r="I155" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.42</v>
+      </c>
+      <c r="I155" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J155" s="9" t="n">
-        <v>1.053</v>
+        <v>1.293</v>
       </c>
       <c r="K155" s="9" t="n">
-        <v>1.125</v>
+        <v>1.192</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="14" t="inlineStr"/>
@@ -7477,28 +7477,28 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D156" s="9" t="n">
-        <v>1.75</v>
+        <v>0.55</v>
       </c>
       <c r="E156" s="17" t="n">
-        <v>0</v>
+        <v>-0.0179</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>697300</v>
+        <v>1011100</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>0.11</v>
+        <v>0.24</v>
       </c>
       <c r="H156" t="n">
-        <v>36.46</v>
+        <v>30.62</v>
       </c>
       <c r="I156" s="13" t="inlineStr">
         <is>
@@ -7506,10 +7506,10 @@
         </is>
       </c>
       <c r="J156" s="9" t="n">
-        <v>1.83</v>
+        <v>0.572</v>
       </c>
       <c r="K156" s="9" t="n">
-        <v>1.93</v>
+        <v>0.583</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="14" t="inlineStr"/>
@@ -7522,28 +7522,28 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D157" s="9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="E157" s="10" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.865</v>
+      </c>
+      <c r="E157" s="17" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>682600</v>
+        <v>990800</v>
       </c>
       <c r="G157" s="12" t="n">
-        <v>0.21</v>
+        <v>0.31</v>
       </c>
       <c r="H157" t="n">
-        <v>49.67</v>
+        <v>52.87</v>
       </c>
       <c r="I157" s="13" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="J157" s="9" t="n">
-        <v>2.055</v>
+        <v>0.864</v>
       </c>
       <c r="K157" s="9" t="n">
-        <v>2.085</v>
+        <v>0.858</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="14" t="inlineStr"/>
@@ -7567,28 +7567,28 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>0151</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>KGB</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D158" s="9" t="n">
-        <v>8.65</v>
-      </c>
-      <c r="E158" s="10" t="n">
-        <v>-0.0335</v>
+        <v>0.615</v>
+      </c>
+      <c r="E158" s="17" t="n">
+        <v>-0.016</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>666900</v>
+        <v>985100</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="H158" t="n">
-        <v>48.38</v>
+        <v>50.32</v>
       </c>
       <c r="I158" s="16" t="inlineStr">
         <is>
@@ -7596,10 +7596,10 @@
         </is>
       </c>
       <c r="J158" s="9" t="n">
-        <v>8.746</v>
+        <v>0.615</v>
       </c>
       <c r="K158" s="9" t="n">
-        <v>8.68</v>
+        <v>0.609</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="14" t="inlineStr"/>
@@ -7612,39 +7612,39 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>FFB</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D159" s="9" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="E159" s="17" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="E159" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>655300</v>
+        <v>955100</v>
       </c>
       <c r="G159" s="12" t="n">
-        <v>0.24</v>
+        <v>0.33</v>
       </c>
       <c r="H159" t="n">
-        <v>22.45</v>
-      </c>
-      <c r="I159" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.8</v>
+      </c>
+      <c r="I159" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J159" s="9" t="n">
-        <v>1.89</v>
+        <v>0.612</v>
       </c>
       <c r="K159" s="9" t="n">
-        <v>2.022</v>
+        <v>0.598</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="14" t="inlineStr"/>
@@ -7657,28 +7657,28 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D160" s="9" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="E160" s="10" t="n">
-        <v>-0.0312</v>
+        <v>2.53</v>
+      </c>
+      <c r="E160" s="15" t="n">
+        <v>0.012</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>638700</v>
+        <v>952600</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>0.19</v>
+        <v>0.16</v>
       </c>
       <c r="H160" t="n">
-        <v>65.98</v>
+        <v>37.31</v>
       </c>
       <c r="I160" s="13" t="inlineStr">
         <is>
@@ -7686,10 +7686,10 @@
         </is>
       </c>
       <c r="J160" s="9" t="n">
-        <v>2.595</v>
+        <v>2.622</v>
       </c>
       <c r="K160" s="9" t="n">
-        <v>2.122</v>
+        <v>2.787</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="14" t="inlineStr"/>
@@ -7702,28 +7702,28 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>0099</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>SCICOM</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D161" s="9" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="E161" s="10" t="n">
-        <v>-0.0218</v>
+        <v>0.77</v>
+      </c>
+      <c r="E161" s="17" t="n">
+        <v>-0.0314</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>630300</v>
+        <v>948400</v>
       </c>
       <c r="G161" s="12" t="n">
-        <v>1.31</v>
+        <v>0.53</v>
       </c>
       <c r="H161" t="n">
-        <v>46.42</v>
+        <v>63.96</v>
       </c>
       <c r="I161" s="16" t="inlineStr">
         <is>
@@ -7731,10 +7731,10 @@
         </is>
       </c>
       <c r="J161" s="9" t="n">
-        <v>2.288</v>
+        <v>0.707</v>
       </c>
       <c r="K161" s="9" t="n">
-        <v>2.226</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="14" t="inlineStr"/>
@@ -7747,28 +7747,28 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>AFFIN</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D162" s="9" t="n">
-        <v>1.96</v>
+        <v>1.75</v>
       </c>
       <c r="E162" s="10" t="n">
-        <v>-0.0151</v>
+        <v>0</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>628400</v>
+        <v>940400</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>0.9</v>
+        <v>0.14</v>
       </c>
       <c r="H162" t="n">
-        <v>26.98</v>
+        <v>36.46</v>
       </c>
       <c r="I162" s="13" t="inlineStr">
         <is>
@@ -7776,10 +7776,10 @@
         </is>
       </c>
       <c r="J162" s="9" t="n">
-        <v>2.017</v>
+        <v>1.83</v>
       </c>
       <c r="K162" s="9" t="n">
-        <v>2.084</v>
+        <v>1.93</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="14" t="inlineStr"/>
@@ -7792,39 +7792,39 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5142</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>WASCO</t>
         </is>
       </c>
       <c r="D163" s="9" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E163" s="10" t="n">
-        <v>-0.0177</v>
+        <v>0.765</v>
+      </c>
+      <c r="E163" s="15" t="n">
+        <v>0.0066</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>627800</v>
+        <v>937900</v>
       </c>
       <c r="G163" s="12" t="n">
-        <v>0.11</v>
+        <v>0.57</v>
       </c>
       <c r="H163" t="n">
-        <v>34.11</v>
-      </c>
-      <c r="I163" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.82</v>
+      </c>
+      <c r="I163" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J163" s="9" t="n">
-        <v>0.597</v>
+        <v>0.734</v>
       </c>
       <c r="K163" s="9" t="n">
-        <v>0.644</v>
+        <v>0.723</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="14" t="inlineStr"/>
@@ -7837,28 +7837,28 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>FFB</t>
         </is>
       </c>
       <c r="D164" s="9" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="E164" s="15" t="n">
-        <v>0.016</v>
+        <v>1.76</v>
+      </c>
+      <c r="E164" s="17" t="n">
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>619700</v>
+        <v>884900</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>0.1</v>
+        <v>0.32</v>
       </c>
       <c r="H164" t="n">
-        <v>38.47</v>
+        <v>21.7</v>
       </c>
       <c r="I164" s="13" t="inlineStr">
         <is>
@@ -7866,10 +7866,10 @@
         </is>
       </c>
       <c r="J164" s="9" t="n">
-        <v>2.623</v>
+        <v>1.889</v>
       </c>
       <c r="K164" s="9" t="n">
-        <v>2.787</v>
+        <v>2.022</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="14" t="inlineStr"/>
@@ -7882,28 +7882,28 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D165" s="9" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E165" s="15" t="n">
-        <v>0.006500000000000001</v>
+        <v>3.04</v>
+      </c>
+      <c r="E165" s="17" t="n">
+        <v>-0.0098</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>617800</v>
+        <v>878700</v>
       </c>
       <c r="G165" s="12" t="n">
-        <v>0.37</v>
+        <v>0.22</v>
       </c>
       <c r="H165" t="n">
-        <v>54.32</v>
+        <v>69.97</v>
       </c>
       <c r="I165" s="16" t="inlineStr">
         <is>
@@ -7911,10 +7911,10 @@
         </is>
       </c>
       <c r="J165" s="9" t="n">
-        <v>0.766</v>
+        <v>2.659</v>
       </c>
       <c r="K165" s="9" t="n">
-        <v>0.76</v>
+        <v>2.016</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="14" t="inlineStr"/>
@@ -7927,28 +7927,28 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D166" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E166" s="10" t="n">
-        <v>-0.007800000000000001</v>
+        <v>2.83</v>
+      </c>
+      <c r="E166" s="17" t="n">
+        <v>-0.0174</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>608600</v>
+        <v>859400</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>0.19</v>
+        <v>0.26</v>
       </c>
       <c r="H166" t="n">
-        <v>54.22</v>
+        <v>68.67</v>
       </c>
       <c r="I166" s="13" t="inlineStr">
         <is>
@@ -7956,10 +7956,10 @@
         </is>
       </c>
       <c r="J166" s="9" t="n">
-        <v>0.639</v>
+        <v>2.599</v>
       </c>
       <c r="K166" s="9" t="n">
-        <v>0.611</v>
+        <v>2.123</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="14" t="inlineStr"/>
@@ -7972,28 +7972,28 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D167" s="9" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="E167" s="15" t="n">
-        <v>0.0068</v>
+        <v>3.26</v>
+      </c>
+      <c r="E167" s="17" t="n">
+        <v>-0.0412</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>606500</v>
+        <v>853500</v>
       </c>
       <c r="G167" s="12" t="n">
-        <v>0.36</v>
+        <v>0.27</v>
       </c>
       <c r="H167" t="n">
-        <v>52.39</v>
+        <v>65.29000000000001</v>
       </c>
       <c r="I167" s="16" t="inlineStr">
         <is>
@@ -8001,10 +8001,10 @@
         </is>
       </c>
       <c r="J167" s="9" t="n">
-        <v>0.737</v>
+        <v>2.981</v>
       </c>
       <c r="K167" s="9" t="n">
-        <v>0.75</v>
+        <v>2.794</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="14" t="inlineStr"/>
@@ -8017,39 +8017,39 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>KOBAY</t>
         </is>
       </c>
       <c r="D168" s="9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="E168" s="10" t="n">
-        <v>-0.0161</v>
+        <v>2.09</v>
+      </c>
+      <c r="E168" s="15" t="n">
+        <v>0.0048</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>603900</v>
+        <v>822000</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>0.1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H168" t="n">
-        <v>41.62</v>
-      </c>
-      <c r="I168" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.55</v>
+      </c>
+      <c r="I168" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J168" s="9" t="n">
-        <v>1.249</v>
+        <v>2.228</v>
       </c>
       <c r="K168" s="9" t="n">
-        <v>1.287</v>
+        <v>2.319</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="14" t="inlineStr"/>
@@ -8062,39 +8062,39 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>0392</t>
+          <t>0151</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>KEEMING</t>
+          <t>KGB</t>
         </is>
       </c>
       <c r="D169" s="9" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="E169" s="10" t="n">
-        <v>-0.0115</v>
+        <v>8.609999999999999</v>
+      </c>
+      <c r="E169" s="17" t="n">
+        <v>-0.038</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>591700</v>
+        <v>808800</v>
       </c>
       <c r="G169" s="12" t="n">
-        <v>0.87</v>
+        <v>0.33</v>
       </c>
       <c r="H169" t="n">
-        <v>53.67</v>
-      </c>
-      <c r="I169" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.5</v>
+      </c>
+      <c r="I169" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J169" s="9" t="n">
-        <v>2.558</v>
+        <v>8.742000000000001</v>
       </c>
       <c r="K169" s="9" t="n">
-        <v>2.407</v>
+        <v>8.68</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="14" t="inlineStr"/>
@@ -8107,28 +8107,28 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>PADINI</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D170" s="9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="E170" s="10" t="n">
-        <v>-0.0095</v>
+        <v>1.22</v>
+      </c>
+      <c r="E170" s="17" t="n">
+        <v>-0.0161</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>575600</v>
+        <v>795700</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>0.32</v>
+        <v>0.13</v>
       </c>
       <c r="H170" t="n">
-        <v>40.03</v>
+        <v>41.62</v>
       </c>
       <c r="I170" s="16" t="inlineStr">
         <is>
@@ -8136,10 +8136,10 @@
         </is>
       </c>
       <c r="J170" s="9" t="n">
-        <v>1.058</v>
+        <v>1.249</v>
       </c>
       <c r="K170" s="9" t="n">
-        <v>1.198</v>
+        <v>1.287</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="14" t="inlineStr"/>
@@ -8152,28 +8152,28 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="E171" s="10" t="n">
-        <v>-0.0229</v>
+        <v>0.78</v>
+      </c>
+      <c r="E171" s="15" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>574700</v>
+        <v>781800</v>
       </c>
       <c r="G171" s="12" t="n">
-        <v>0.35</v>
+        <v>0.47</v>
       </c>
       <c r="H171" t="n">
-        <v>56.26</v>
+        <v>54.32</v>
       </c>
       <c r="I171" s="16" t="inlineStr">
         <is>
@@ -8181,10 +8181,10 @@
         </is>
       </c>
       <c r="J171" s="9" t="n">
-        <v>1.66</v>
+        <v>0.766</v>
       </c>
       <c r="K171" s="9" t="n">
-        <v>1.678</v>
+        <v>0.76</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="14" t="inlineStr"/>
@@ -8197,28 +8197,28 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>PAVREIT</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D172" s="9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="E172" s="10" t="n">
-        <v>-0.0127</v>
+        <v>0.96</v>
+      </c>
+      <c r="E172" s="17" t="n">
+        <v>-0.0103</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>568300</v>
+        <v>764300</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>0.14</v>
+        <v>0.32</v>
       </c>
       <c r="H172" t="n">
-        <v>44.57</v>
+        <v>24.25</v>
       </c>
       <c r="I172" s="13" t="inlineStr">
         <is>
@@ -8226,10 +8226,10 @@
         </is>
       </c>
       <c r="J172" s="9" t="n">
-        <v>1.564</v>
+        <v>1.053</v>
       </c>
       <c r="K172" s="9" t="n">
-        <v>1.622</v>
+        <v>1.125</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="14" t="inlineStr"/>
@@ -8242,28 +8242,28 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>0311</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>GOHUB</t>
+          <t>AFFIN</t>
         </is>
       </c>
       <c r="D173" s="9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E173" s="15" t="n">
-        <v>0.0625</v>
+        <v>1.95</v>
+      </c>
+      <c r="E173" s="17" t="n">
+        <v>-0.0201</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>544400</v>
+        <v>743300</v>
       </c>
       <c r="G173" s="12" t="n">
-        <v>3.84</v>
+        <v>1.07</v>
       </c>
       <c r="H173" t="n">
-        <v>55.46</v>
+        <v>25.43</v>
       </c>
       <c r="I173" s="13" t="inlineStr">
         <is>
@@ -8271,10 +8271,10 @@
         </is>
       </c>
       <c r="J173" s="9" t="n">
-        <v>1.163</v>
+        <v>2.016</v>
       </c>
       <c r="K173" s="9" t="n">
-        <v>1.156</v>
+        <v>2.084</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="14" t="inlineStr"/>
@@ -8287,39 +8287,39 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D174" s="9" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="E174" s="15" t="n">
-        <v>0.0208</v>
+        <v>2.12</v>
+      </c>
+      <c r="E174" s="17" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>522700</v>
+        <v>727400</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>0.09</v>
+        <v>0.28</v>
       </c>
       <c r="H174" t="n">
-        <v>38.34</v>
-      </c>
-      <c r="I174" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.71</v>
+      </c>
+      <c r="I174" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J174" s="9" t="n">
-        <v>0.761</v>
+        <v>2.088</v>
       </c>
       <c r="K174" s="9" t="n">
-        <v>0.82</v>
+        <v>2.04</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="14" t="inlineStr"/>
@@ -8332,28 +8332,28 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>0249</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>LGMS</t>
+          <t>VSTECS</t>
         </is>
       </c>
       <c r="D175" s="9" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E175" s="10" t="n">
-        <v>-0.0089</v>
+        <v>1.69</v>
+      </c>
+      <c r="E175" s="17" t="n">
+        <v>-0.0343</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>508000</v>
+        <v>723400</v>
       </c>
       <c r="G175" s="12" t="n">
-        <v>0.6</v>
+        <v>0.44</v>
       </c>
       <c r="H175" t="n">
-        <v>67.31</v>
+        <v>53.7</v>
       </c>
       <c r="I175" s="16" t="inlineStr">
         <is>
@@ -8361,16 +8361,871 @@
         </is>
       </c>
       <c r="J175" s="9" t="n">
-        <v>0.517</v>
+        <v>1.658</v>
       </c>
       <c r="K175" s="9" t="n">
-        <v>0.502</v>
+        <v>1.678</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="14" t="inlineStr"/>
     </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>7134</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>PWF</t>
+        </is>
+      </c>
+      <c r="D176" s="9" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E176" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F176" s="11" t="n">
+        <v>720300</v>
+      </c>
+      <c r="G176" s="12" t="n">
+        <v>34.24</v>
+      </c>
+      <c r="H176" t="n">
+        <v>49.91</v>
+      </c>
+      <c r="I176" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J176" s="9" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="K176" s="9" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" s="14" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>8664</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>SPSETIA</t>
+        </is>
+      </c>
+      <c r="D177" s="9" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="E177" s="15" t="n">
+        <v>0.0139</v>
+      </c>
+      <c r="F177" s="11" t="n">
+        <v>706500</v>
+      </c>
+      <c r="G177" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H177" t="n">
+        <v>36.58</v>
+      </c>
+      <c r="I177" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J177" s="9" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="K177" s="9" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" s="14" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>0099</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>SCICOM</t>
+        </is>
+      </c>
+      <c r="D178" s="9" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="E178" s="17" t="n">
+        <v>-0.0218</v>
+      </c>
+      <c r="F178" s="11" t="n">
+        <v>702800</v>
+      </c>
+      <c r="G178" s="12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="H178" t="n">
+        <v>46.42</v>
+      </c>
+      <c r="I178" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J178" s="9" t="n">
+        <v>2.288</v>
+      </c>
+      <c r="K178" s="9" t="n">
+        <v>2.226</v>
+      </c>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" s="14" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>7052</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>PADINI</t>
+        </is>
+      </c>
+      <c r="D179" s="9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E179" s="15" t="n">
+        <v>0.0095</v>
+      </c>
+      <c r="F179" s="11" t="n">
+        <v>669500</v>
+      </c>
+      <c r="G179" s="12" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H179" t="n">
+        <v>44.36</v>
+      </c>
+      <c r="I179" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J179" s="9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="K179" s="9" t="n">
+        <v>1.198</v>
+      </c>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" s="14" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>7161</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>KERJAYA</t>
+        </is>
+      </c>
+      <c r="D180" s="9" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="E180" s="17" t="n">
+        <v>-0.0229</v>
+      </c>
+      <c r="F180" s="11" t="n">
+        <v>655200</v>
+      </c>
+      <c r="G180" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H180" t="n">
+        <v>53.75</v>
+      </c>
+      <c r="I180" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J180" s="9" t="n">
+        <v>3.423</v>
+      </c>
+      <c r="K180" s="9" t="n">
+        <v>3.062</v>
+      </c>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" s="14" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>0392</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>KEEMING</t>
+        </is>
+      </c>
+      <c r="D181" s="9" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="E181" s="17" t="n">
+        <v>-0.0115</v>
+      </c>
+      <c r="F181" s="11" t="n">
+        <v>653300</v>
+      </c>
+      <c r="G181" s="12" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H181" t="n">
+        <v>53.67</v>
+      </c>
+      <c r="I181" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J181" s="9" t="n">
+        <v>2.558</v>
+      </c>
+      <c r="K181" s="9" t="n">
+        <v>2.407</v>
+      </c>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" s="14" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>6633</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>LHI</t>
+        </is>
+      </c>
+      <c r="D182" s="9" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E182" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F182" s="11" t="n">
+        <v>633100</v>
+      </c>
+      <c r="G182" s="12" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H182" t="n">
+        <v>50.69</v>
+      </c>
+      <c r="I182" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J182" s="9" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="K182" s="9" t="n">
+        <v>0.749</v>
+      </c>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" s="14" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>5263</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>SUNCON</t>
+        </is>
+      </c>
+      <c r="D183" s="9" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="E183" s="17" t="n">
+        <v>-0.0053</v>
+      </c>
+      <c r="F183" s="11" t="n">
+        <v>632200</v>
+      </c>
+      <c r="G183" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H183" t="n">
+        <v>44.63</v>
+      </c>
+      <c r="I183" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J183" s="9" t="n">
+        <v>7.609</v>
+      </c>
+      <c r="K183" s="9" t="n">
+        <v>7.812</v>
+      </c>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" s="14" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>5212</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>PAVREIT</t>
+        </is>
+      </c>
+      <c r="D184" s="9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E184" s="17" t="n">
+        <v>-0.0127</v>
+      </c>
+      <c r="F184" s="11" t="n">
+        <v>630400</v>
+      </c>
+      <c r="G184" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H184" t="n">
+        <v>44.57</v>
+      </c>
+      <c r="I184" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J184" s="9" t="n">
+        <v>1.564</v>
+      </c>
+      <c r="K184" s="9" t="n">
+        <v>1.622</v>
+      </c>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" s="14" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>5088</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>APEX</t>
+        </is>
+      </c>
+      <c r="D185" s="9" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="E185" s="15" t="n">
+        <v>0.0431</v>
+      </c>
+      <c r="F185" s="11" t="n">
+        <v>627000</v>
+      </c>
+      <c r="G185" s="12" t="n">
+        <v>13.83</v>
+      </c>
+      <c r="H185" t="n">
+        <v>45.27</v>
+      </c>
+      <c r="I185" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J185" s="9" t="n">
+        <v>0.623</v>
+      </c>
+      <c r="K185" s="9" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" s="14" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>HIBISCS</t>
+        </is>
+      </c>
+      <c r="D186" s="9" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="E186" s="15" t="n">
+        <v>0.0186</v>
+      </c>
+      <c r="F186" s="11" t="n">
+        <v>613100</v>
+      </c>
+      <c r="G186" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H186" t="n">
+        <v>50.99</v>
+      </c>
+      <c r="I186" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J186" s="9" t="n">
+        <v>2.187</v>
+      </c>
+      <c r="K186" s="9" t="n">
+        <v>2.124</v>
+      </c>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" s="14" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>5246</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>WPRTS</t>
+        </is>
+      </c>
+      <c r="D187" s="9" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="E187" s="17" t="n">
+        <v>-0.016</v>
+      </c>
+      <c r="F187" s="11" t="n">
+        <v>610900</v>
+      </c>
+      <c r="G187" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H187" t="n">
+        <v>48.05</v>
+      </c>
+      <c r="I187" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J187" s="9" t="n">
+        <v>6.781</v>
+      </c>
+      <c r="K187" s="9" t="n">
+        <v>6.851</v>
+      </c>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" s="14" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D188" s="9" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E188" s="17" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F188" s="11" t="n">
+        <v>608600</v>
+      </c>
+      <c r="G188" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H188" t="n">
+        <v>54.22</v>
+      </c>
+      <c r="I188" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J188" s="9" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="K188" s="9" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" s="14" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>0097</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>VITROX</t>
+        </is>
+      </c>
+      <c r="D189" s="9" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="E189" s="17" t="n">
+        <v>-0.0232</v>
+      </c>
+      <c r="F189" s="11" t="n">
+        <v>604200</v>
+      </c>
+      <c r="G189" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H189" t="n">
+        <v>72.36</v>
+      </c>
+      <c r="I189" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J189" s="9" t="n">
+        <v>10.151</v>
+      </c>
+      <c r="K189" s="9" t="n">
+        <v>9.484999999999999</v>
+      </c>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" s="14" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>3069</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>MFCB</t>
+        </is>
+      </c>
+      <c r="D190" s="9" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="E190" s="17" t="n">
+        <v>-0.0211</v>
+      </c>
+      <c r="F190" s="11" t="n">
+        <v>588300</v>
+      </c>
+      <c r="G190" s="12" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="H190" t="n">
+        <v>40.05</v>
+      </c>
+      <c r="I190" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J190" s="9" t="n">
+        <v>2.894</v>
+      </c>
+      <c r="K190" s="9" t="n">
+        <v>2.862</v>
+      </c>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" s="14" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>0311</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>GOHUB</t>
+        </is>
+      </c>
+      <c r="D191" s="9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E191" s="15" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="F191" s="11" t="n">
+        <v>558400</v>
+      </c>
+      <c r="G191" s="12" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="H191" t="n">
+        <v>55.46</v>
+      </c>
+      <c r="I191" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J191" s="9" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="K191" s="9" t="n">
+        <v>1.156</v>
+      </c>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" s="14" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>0128</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>FRONTKN</t>
+        </is>
+      </c>
+      <c r="D192" s="9" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="E192" s="17" t="n">
+        <v>-0.0115</v>
+      </c>
+      <c r="F192" s="11" t="n">
+        <v>556500</v>
+      </c>
+      <c r="G192" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H192" t="n">
+        <v>56.86</v>
+      </c>
+      <c r="I192" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J192" s="9" t="n">
+        <v>5.052</v>
+      </c>
+      <c r="K192" s="9" t="n">
+        <v>5.061</v>
+      </c>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" s="14" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>LGMS</t>
+        </is>
+      </c>
+      <c r="D193" s="9" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E193" s="17" t="n">
+        <v>-0.0179</v>
+      </c>
+      <c r="F193" s="11" t="n">
+        <v>551500</v>
+      </c>
+      <c r="G193" s="12" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H193" t="n">
+        <v>64.91</v>
+      </c>
+      <c r="I193" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J193" s="9" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="K193" s="9" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" s="14" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>0338</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>KOPI</t>
+        </is>
+      </c>
+      <c r="D194" s="9" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="E194" s="17" t="n">
+        <v>-0.005600000000000001</v>
+      </c>
+      <c r="F194" s="11" t="n">
+        <v>525200</v>
+      </c>
+      <c r="G194" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H194" t="n">
+        <v>34.41</v>
+      </c>
+      <c r="I194" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J194" s="9" t="n">
+        <v>0.911</v>
+      </c>
+      <c r="K194" s="9" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M175"/>
+  <autoFilter ref="A1:M194"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>